--- a/Capstone/Fase 1/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Carta Gantt.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7907524E-7212-43D1-8000-19E854B9CFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB75C006-40F6-43BF-B43C-50B679BE1844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="110">
   <si>
     <t>Cree una programación para un proyecto en esta hoja de cálculo.
 Escriba el título de este proyecto en la celda B1. 
@@ -180,12 +180,6 @@
     <t xml:space="preserve">    1.1.1  Descripción proyecto APT</t>
   </si>
   <si>
-    <t xml:space="preserve">    1..1.2 Fundamentación</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    1.1.3 Objetivos</t>
-  </si>
-  <si>
     <t>1.2. Creación de Backlog</t>
   </si>
   <si>
@@ -288,16 +282,10 @@
     <t xml:space="preserve">    2.1.2 Implementación del flujo de interfaces</t>
   </si>
   <si>
-    <t xml:space="preserve">    2.1.4 Simulación de datos </t>
-  </si>
-  <si>
     <t xml:space="preserve">    2.3.1 Pruebas unitarias</t>
   </si>
   <si>
     <t xml:space="preserve">    2.3.2 Pruebas de usabilidad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    2.1.5 Integración con Backend</t>
   </si>
   <si>
     <t xml:space="preserve">    1.7.2 Refinación de backlog</t>
@@ -336,16 +324,34 @@
     <t>3.1 Fase cierre del proyecto</t>
   </si>
   <si>
-    <t>3.1.2 Marcha blanca</t>
-  </si>
-  <si>
-    <t>3.2.3 Capacitación</t>
-  </si>
-  <si>
     <t>3.1.4 Acta cierre de proyecto</t>
   </si>
   <si>
     <t>3.1.1  Desarrollo de manuales de usuario</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">          1.1.2 Entregable Documento Descripción proyecto APT</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1.1.3 Fundamentación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1.1.4 Documento fundamentación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1.1.5 Objetivos</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.1.6 Metodología</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.1.7 Roles y Responsabilidades</t>
   </si>
   <si>
     <r>
@@ -356,7 +362,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1.1.5 Evidencias</t>
+      <t xml:space="preserve"> 1.1.8 Evidencias</t>
     </r>
     <r>
       <rPr>
@@ -381,22 +387,46 @@
     </r>
   </si>
   <si>
-    <t>1.1.4.1 Roles y Responsabilidades</t>
+    <t xml:space="preserve"> 1.1.9 Documento Acta firmada</t>
   </si>
   <si>
-    <t>1.1.4 Metodología</t>
+    <t xml:space="preserve"> 1.1.10 Plan de trabajo</t>
   </si>
   <si>
-    <t>1.1.6 Plan de trabajo</t>
+    <t xml:space="preserve"> 1.1.11 Carta Gantt</t>
   </si>
   <si>
-    <t>1.1.7 Carta Gantt</t>
+    <t xml:space="preserve">    1.4.3 Entregable Historias de usuarios documentadas </t>
   </si>
   <si>
-    <t>1.7.4 Diseño de base de datos</t>
+    <t xml:space="preserve">   1.7.4 Entregable diseño en Draw.io</t>
   </si>
   <si>
-    <t>1.7.5 Arquitecura</t>
+    <t>1.7.5 Diseño de base de datos</t>
+  </si>
+  <si>
+    <t>1.7.6 Arquitecura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2.1.5 Simulación de datos </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2.1.6 Integración con Backend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2.1.4 Entregable informe de validación </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2.3.3 Entregable Reporte de pruebas</t>
+  </si>
+  <si>
+    <t>3.1.3 Marcha blanca</t>
+  </si>
+  <si>
+    <t>3.2.4 Capacitación</t>
+  </si>
+  <si>
+    <t>3.1.2 Entregable manual de usuario en y guia de uso en pdf</t>
   </si>
 </sst>
 </file>
@@ -684,7 +714,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="51">
+  <fills count="53">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -969,6 +999,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1331,7 +1373,7 @@
     <xf numFmtId="0" fontId="9" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1617,51 +1659,6 @@
     <xf numFmtId="0" fontId="22" fillId="42" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1707,15 +1704,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="50" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="50" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="50" borderId="0" xfId="0" applyFill="1"/>
@@ -1765,14 +1753,83 @@
     <xf numFmtId="0" fontId="6" fillId="49" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="12" applyFill="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="12" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="52" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="12" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="54">
@@ -2382,7 +2439,7 @@
   <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ68"/>
+  <dimension ref="A1:DQ76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="40" customWidth="1"/>
@@ -2394,8 +2451,26 @@
     <col min="7" max="7" width="2.140625" customWidth="1"/>
     <col min="8" max="8" width="0.28515625" style="71" customWidth="1"/>
     <col min="9" max="15" width="4.7109375" customWidth="1"/>
-    <col min="16" max="20" width="4.7109375" style="3" customWidth="1"/>
-    <col min="21" max="85" width="4.7109375" customWidth="1"/>
+    <col min="16" max="19" width="4.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="6.7109375" style="3" customWidth="1"/>
+    <col min="21" max="24" width="4.7109375" customWidth="1"/>
+    <col min="25" max="25" width="5.7109375" customWidth="1"/>
+    <col min="26" max="29" width="4.7109375" customWidth="1"/>
+    <col min="30" max="30" width="8.7109375" customWidth="1"/>
+    <col min="31" max="33" width="4.7109375" customWidth="1"/>
+    <col min="34" max="34" width="5" customWidth="1"/>
+    <col min="35" max="35" width="8.140625" customWidth="1"/>
+    <col min="36" max="39" width="4.7109375" customWidth="1"/>
+    <col min="40" max="40" width="8" customWidth="1"/>
+    <col min="41" max="41" width="4.7109375" customWidth="1"/>
+    <col min="42" max="42" width="5.140625" customWidth="1"/>
+    <col min="43" max="69" width="4.7109375" customWidth="1"/>
+    <col min="70" max="70" width="8.28515625" customWidth="1"/>
+    <col min="71" max="74" width="4.7109375" customWidth="1"/>
+    <col min="75" max="75" width="9.5703125" customWidth="1"/>
+    <col min="76" max="79" width="4.7109375" customWidth="1"/>
+    <col min="80" max="80" width="7.7109375" customWidth="1"/>
+    <col min="81" max="85" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.45">
@@ -2417,149 +2492,149 @@
         <v>1</v>
       </c>
       <c r="B2" s="45"/>
-      <c r="C2" s="101" t="s">
+      <c r="C2" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="102"/>
-      <c r="E2" s="106">
+      <c r="D2" s="154"/>
+      <c r="E2" s="155">
         <f>DATE(2025,8,22)</f>
         <v>45891</v>
       </c>
-      <c r="F2" s="106"/>
+      <c r="F2" s="155"/>
     </row>
     <row r="3" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="101" t="s">
+      <c r="C3" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="102"/>
+      <c r="D3" s="154"/>
       <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="I3" s="107">
+      <c r="I3" s="150">
         <f>I4</f>
         <v>45890</v>
       </c>
-      <c r="J3" s="108"/>
-      <c r="K3" s="108"/>
-      <c r="L3" s="108"/>
-      <c r="M3" s="108"/>
-      <c r="N3" s="108"/>
-      <c r="O3" s="109"/>
-      <c r="P3" s="103">
+      <c r="J3" s="151"/>
+      <c r="K3" s="151"/>
+      <c r="L3" s="151"/>
+      <c r="M3" s="151"/>
+      <c r="N3" s="151"/>
+      <c r="O3" s="152"/>
+      <c r="P3" s="147">
         <f>P4</f>
         <v>45901</v>
       </c>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="104"/>
-      <c r="S3" s="104"/>
-      <c r="T3" s="105"/>
-      <c r="U3" s="103">
-        <f t="shared" ref="U3" si="0">U4</f>
+      <c r="Q3" s="148"/>
+      <c r="R3" s="148"/>
+      <c r="S3" s="148"/>
+      <c r="T3" s="149"/>
+      <c r="U3" s="147">
+        <f>U4</f>
         <v>45908</v>
       </c>
-      <c r="V3" s="104"/>
-      <c r="W3" s="104"/>
-      <c r="X3" s="104"/>
-      <c r="Y3" s="105"/>
-      <c r="Z3" s="103">
-        <f t="shared" ref="Z3" si="1">Z4</f>
+      <c r="V3" s="148"/>
+      <c r="W3" s="148"/>
+      <c r="X3" s="148"/>
+      <c r="Y3" s="149"/>
+      <c r="Z3" s="147">
+        <f t="shared" ref="Z3" si="0">Z4</f>
         <v>45915</v>
       </c>
-      <c r="AA3" s="104"/>
-      <c r="AB3" s="104"/>
-      <c r="AC3" s="104"/>
-      <c r="AD3" s="105"/>
-      <c r="AE3" s="107">
-        <f t="shared" ref="AE3" si="2">AE4</f>
+      <c r="AA3" s="148"/>
+      <c r="AB3" s="148"/>
+      <c r="AC3" s="148"/>
+      <c r="AD3" s="149"/>
+      <c r="AE3" s="150">
+        <f t="shared" ref="AE3" si="1">AE4</f>
         <v>45922</v>
       </c>
-      <c r="AF3" s="108"/>
-      <c r="AG3" s="108"/>
-      <c r="AH3" s="108"/>
-      <c r="AI3" s="109"/>
-      <c r="AJ3" s="103">
-        <f t="shared" ref="AJ3" si="3">AJ4</f>
+      <c r="AF3" s="151"/>
+      <c r="AG3" s="151"/>
+      <c r="AH3" s="151"/>
+      <c r="AI3" s="152"/>
+      <c r="AJ3" s="147">
+        <f t="shared" ref="AJ3" si="2">AJ4</f>
         <v>45929</v>
       </c>
-      <c r="AK3" s="104"/>
-      <c r="AL3" s="104"/>
-      <c r="AM3" s="104"/>
-      <c r="AN3" s="105"/>
-      <c r="AO3" s="103">
-        <f t="shared" ref="AO3" si="4">AO4</f>
+      <c r="AK3" s="148"/>
+      <c r="AL3" s="148"/>
+      <c r="AM3" s="148"/>
+      <c r="AN3" s="149"/>
+      <c r="AO3" s="147">
+        <f>AO4</f>
         <v>45936</v>
       </c>
-      <c r="AP3" s="104"/>
-      <c r="AQ3" s="104"/>
-      <c r="AR3" s="104"/>
-      <c r="AS3" s="105"/>
-      <c r="AT3" s="103">
-        <f t="shared" ref="AT3" si="5">AT4</f>
+      <c r="AP3" s="148"/>
+      <c r="AQ3" s="148"/>
+      <c r="AR3" s="148"/>
+      <c r="AS3" s="149"/>
+      <c r="AT3" s="147">
+        <f t="shared" ref="AT3" si="3">AT4</f>
         <v>45943</v>
       </c>
-      <c r="AU3" s="104"/>
-      <c r="AV3" s="104"/>
-      <c r="AW3" s="104"/>
-      <c r="AX3" s="105"/>
-      <c r="AY3" s="103">
-        <f t="shared" ref="AY3" si="6">AY4</f>
+      <c r="AU3" s="148"/>
+      <c r="AV3" s="148"/>
+      <c r="AW3" s="148"/>
+      <c r="AX3" s="149"/>
+      <c r="AY3" s="147">
+        <f t="shared" ref="AY3" si="4">AY4</f>
         <v>45950</v>
       </c>
-      <c r="AZ3" s="104"/>
-      <c r="BA3" s="104"/>
-      <c r="BB3" s="104"/>
-      <c r="BC3" s="105"/>
-      <c r="BD3" s="103">
-        <f t="shared" ref="BD3" si="7">BD4</f>
+      <c r="AZ3" s="148"/>
+      <c r="BA3" s="148"/>
+      <c r="BB3" s="148"/>
+      <c r="BC3" s="149"/>
+      <c r="BD3" s="147">
+        <f t="shared" ref="BD3" si="5">BD4</f>
         <v>45957</v>
       </c>
-      <c r="BE3" s="104"/>
-      <c r="BF3" s="104"/>
-      <c r="BG3" s="104"/>
-      <c r="BH3" s="105"/>
-      <c r="BI3" s="103">
-        <f t="shared" ref="BI3" si="8">BI4</f>
+      <c r="BE3" s="148"/>
+      <c r="BF3" s="148"/>
+      <c r="BG3" s="148"/>
+      <c r="BH3" s="149"/>
+      <c r="BI3" s="147">
+        <f t="shared" ref="BI3" si="6">BI4</f>
         <v>45964</v>
       </c>
-      <c r="BJ3" s="104"/>
-      <c r="BK3" s="104"/>
-      <c r="BL3" s="104"/>
-      <c r="BM3" s="105"/>
-      <c r="BN3" s="103">
-        <f t="shared" ref="BN3" si="9">BN4</f>
+      <c r="BJ3" s="148"/>
+      <c r="BK3" s="148"/>
+      <c r="BL3" s="148"/>
+      <c r="BM3" s="149"/>
+      <c r="BN3" s="147">
+        <f t="shared" ref="BN3" si="7">BN4</f>
         <v>45971</v>
       </c>
-      <c r="BO3" s="104"/>
-      <c r="BP3" s="104"/>
-      <c r="BQ3" s="104"/>
-      <c r="BR3" s="105"/>
-      <c r="BS3" s="103">
-        <f t="shared" ref="BS3" si="10">BS4</f>
+      <c r="BO3" s="148"/>
+      <c r="BP3" s="148"/>
+      <c r="BQ3" s="148"/>
+      <c r="BR3" s="149"/>
+      <c r="BS3" s="147">
+        <f t="shared" ref="BS3" si="8">BS4</f>
         <v>45978</v>
       </c>
-      <c r="BT3" s="104"/>
-      <c r="BU3" s="104"/>
-      <c r="BV3" s="104"/>
-      <c r="BW3" s="105"/>
-      <c r="BX3" s="103">
-        <f t="shared" ref="BX3" si="11">BX4</f>
+      <c r="BT3" s="148"/>
+      <c r="BU3" s="148"/>
+      <c r="BV3" s="148"/>
+      <c r="BW3" s="149"/>
+      <c r="BX3" s="147">
+        <f t="shared" ref="BX3" si="9">BX4</f>
         <v>45985</v>
       </c>
-      <c r="BY3" s="104"/>
-      <c r="BZ3" s="104"/>
-      <c r="CA3" s="104"/>
-      <c r="CB3" s="105"/>
-      <c r="CC3" s="103">
-        <f t="shared" ref="CC3" si="12">CC4</f>
+      <c r="BY3" s="148"/>
+      <c r="BZ3" s="148"/>
+      <c r="CA3" s="148"/>
+      <c r="CB3" s="149"/>
+      <c r="CC3" s="147">
+        <f t="shared" ref="CC3" si="10">CC4</f>
         <v>45992</v>
       </c>
-      <c r="CD3" s="104"/>
-      <c r="CE3" s="104"/>
-      <c r="CF3" s="104"/>
-      <c r="CG3" s="105"/>
+      <c r="CD3" s="148"/>
+      <c r="CE3" s="148"/>
+      <c r="CF3" s="148"/>
+      <c r="CG3" s="149"/>
     </row>
     <row r="4" spans="1:121" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="41" t="s">
@@ -2572,311 +2647,311 @@
       <c r="F4" s="54"/>
       <c r="G4" s="54"/>
       <c r="I4" s="69">
-        <f t="shared" ref="I4:AN4" si="13">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(A1)-1)</f>
+        <f t="shared" ref="I4:AN4" si="11">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(A1)-1)</f>
         <v>45890</v>
       </c>
       <c r="J4" s="69">
+        <f t="shared" si="11"/>
+        <v>45891</v>
+      </c>
+      <c r="K4" s="69">
+        <f>WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(C1)-1)</f>
+        <v>45894</v>
+      </c>
+      <c r="L4" s="69">
+        <f t="shared" si="11"/>
+        <v>45895</v>
+      </c>
+      <c r="M4" s="69">
+        <f t="shared" si="11"/>
+        <v>45896</v>
+      </c>
+      <c r="N4" s="69">
+        <f t="shared" si="11"/>
+        <v>45897</v>
+      </c>
+      <c r="O4" s="69">
+        <f t="shared" si="11"/>
+        <v>45898</v>
+      </c>
+      <c r="P4" s="63">
+        <f t="shared" si="11"/>
+        <v>45901</v>
+      </c>
+      <c r="Q4" s="63">
+        <f t="shared" si="11"/>
+        <v>45902</v>
+      </c>
+      <c r="R4" s="63">
+        <f t="shared" si="11"/>
+        <v>45903</v>
+      </c>
+      <c r="S4" s="63">
+        <f t="shared" si="11"/>
+        <v>45904</v>
+      </c>
+      <c r="T4" s="63">
+        <f t="shared" si="11"/>
+        <v>45905</v>
+      </c>
+      <c r="U4" s="63">
+        <f t="shared" si="11"/>
+        <v>45908</v>
+      </c>
+      <c r="V4" s="63">
+        <f t="shared" si="11"/>
+        <v>45909</v>
+      </c>
+      <c r="W4" s="63">
+        <f t="shared" si="11"/>
+        <v>45910</v>
+      </c>
+      <c r="X4" s="63">
+        <f t="shared" si="11"/>
+        <v>45911</v>
+      </c>
+      <c r="Y4" s="63">
+        <f t="shared" si="11"/>
+        <v>45912</v>
+      </c>
+      <c r="Z4" s="63">
+        <f t="shared" si="11"/>
+        <v>45915</v>
+      </c>
+      <c r="AA4" s="63">
+        <f t="shared" si="11"/>
+        <v>45916</v>
+      </c>
+      <c r="AB4" s="63">
+        <f t="shared" si="11"/>
+        <v>45917</v>
+      </c>
+      <c r="AC4" s="96">
+        <f t="shared" si="11"/>
+        <v>45918</v>
+      </c>
+      <c r="AD4" s="96">
+        <f t="shared" si="11"/>
+        <v>45919</v>
+      </c>
+      <c r="AE4" s="63">
+        <f t="shared" si="11"/>
+        <v>45922</v>
+      </c>
+      <c r="AF4" s="63">
+        <f t="shared" si="11"/>
+        <v>45923</v>
+      </c>
+      <c r="AG4" s="63">
+        <f t="shared" si="11"/>
+        <v>45924</v>
+      </c>
+      <c r="AH4" s="63">
+        <f t="shared" si="11"/>
+        <v>45925</v>
+      </c>
+      <c r="AI4" s="63">
+        <f t="shared" si="11"/>
+        <v>45926</v>
+      </c>
+      <c r="AJ4" s="63">
+        <f t="shared" si="11"/>
+        <v>45929</v>
+      </c>
+      <c r="AK4" s="63">
+        <f t="shared" si="11"/>
+        <v>45930</v>
+      </c>
+      <c r="AL4" s="63">
+        <f t="shared" si="11"/>
+        <v>45931</v>
+      </c>
+      <c r="AM4" s="63">
+        <f t="shared" si="11"/>
+        <v>45932</v>
+      </c>
+      <c r="AN4" s="63">
+        <f t="shared" si="11"/>
+        <v>45933</v>
+      </c>
+      <c r="AO4" s="63">
+        <f t="shared" ref="AO4:BT4" si="12">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(AG1)-1)</f>
+        <v>45936</v>
+      </c>
+      <c r="AP4" s="63">
+        <f t="shared" si="12"/>
+        <v>45937</v>
+      </c>
+      <c r="AQ4" s="63">
+        <f t="shared" si="12"/>
+        <v>45938</v>
+      </c>
+      <c r="AR4" s="63">
+        <f t="shared" si="12"/>
+        <v>45939</v>
+      </c>
+      <c r="AS4" s="63">
+        <f t="shared" si="12"/>
+        <v>45940</v>
+      </c>
+      <c r="AT4" s="63">
+        <f t="shared" si="12"/>
+        <v>45943</v>
+      </c>
+      <c r="AU4" s="63">
+        <f t="shared" si="12"/>
+        <v>45944</v>
+      </c>
+      <c r="AV4" s="63">
+        <f t="shared" si="12"/>
+        <v>45945</v>
+      </c>
+      <c r="AW4" s="63">
+        <f t="shared" si="12"/>
+        <v>45946</v>
+      </c>
+      <c r="AX4" s="63">
+        <f t="shared" si="12"/>
+        <v>45947</v>
+      </c>
+      <c r="AY4" s="63">
+        <f t="shared" si="12"/>
+        <v>45950</v>
+      </c>
+      <c r="AZ4" s="63">
+        <f t="shared" si="12"/>
+        <v>45951</v>
+      </c>
+      <c r="BA4" s="63">
+        <f t="shared" si="12"/>
+        <v>45952</v>
+      </c>
+      <c r="BB4" s="63">
+        <f t="shared" si="12"/>
+        <v>45953</v>
+      </c>
+      <c r="BC4" s="63">
+        <f t="shared" si="12"/>
+        <v>45954</v>
+      </c>
+      <c r="BD4" s="63">
+        <f t="shared" si="12"/>
+        <v>45957</v>
+      </c>
+      <c r="BE4" s="63">
+        <f t="shared" si="12"/>
+        <v>45958</v>
+      </c>
+      <c r="BF4" s="63">
+        <f t="shared" si="12"/>
+        <v>45959</v>
+      </c>
+      <c r="BG4" s="63">
+        <f t="shared" si="12"/>
+        <v>45960</v>
+      </c>
+      <c r="BH4" s="63">
+        <f t="shared" si="12"/>
+        <v>45961</v>
+      </c>
+      <c r="BI4" s="63">
+        <f t="shared" si="12"/>
+        <v>45964</v>
+      </c>
+      <c r="BJ4" s="63">
+        <f t="shared" si="12"/>
+        <v>45965</v>
+      </c>
+      <c r="BK4" s="63">
+        <f t="shared" si="12"/>
+        <v>45966</v>
+      </c>
+      <c r="BL4" s="63">
+        <f t="shared" si="12"/>
+        <v>45967</v>
+      </c>
+      <c r="BM4" s="63">
+        <f t="shared" si="12"/>
+        <v>45968</v>
+      </c>
+      <c r="BN4" s="63">
+        <f t="shared" si="12"/>
+        <v>45971</v>
+      </c>
+      <c r="BO4" s="63">
+        <f t="shared" si="12"/>
+        <v>45972</v>
+      </c>
+      <c r="BP4" s="63">
+        <f t="shared" si="12"/>
+        <v>45973</v>
+      </c>
+      <c r="BQ4" s="63">
+        <f t="shared" si="12"/>
+        <v>45974</v>
+      </c>
+      <c r="BR4" s="63">
+        <f t="shared" si="12"/>
+        <v>45975</v>
+      </c>
+      <c r="BS4" s="63">
+        <f t="shared" si="12"/>
+        <v>45978</v>
+      </c>
+      <c r="BT4" s="63">
+        <f t="shared" si="12"/>
+        <v>45979</v>
+      </c>
+      <c r="BU4" s="63">
+        <f t="shared" ref="BU4:CG4" si="13">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(BM1)-1)</f>
+        <v>45980</v>
+      </c>
+      <c r="BV4" s="63">
         <f t="shared" si="13"/>
-        <v>45891</v>
-      </c>
-      <c r="K4" s="69">
+        <v>45981</v>
+      </c>
+      <c r="BW4" s="63">
         <f t="shared" si="13"/>
-        <v>45894</v>
-      </c>
-      <c r="L4" s="69">
+        <v>45982</v>
+      </c>
+      <c r="BX4" s="63">
         <f t="shared" si="13"/>
-        <v>45895</v>
-      </c>
-      <c r="M4" s="69">
+        <v>45985</v>
+      </c>
+      <c r="BY4" s="63">
         <f t="shared" si="13"/>
-        <v>45896</v>
-      </c>
-      <c r="N4" s="69">
+        <v>45986</v>
+      </c>
+      <c r="BZ4" s="63">
         <f t="shared" si="13"/>
-        <v>45897</v>
-      </c>
-      <c r="O4" s="69">
+        <v>45987</v>
+      </c>
+      <c r="CA4" s="63">
         <f t="shared" si="13"/>
-        <v>45898</v>
-      </c>
-      <c r="P4" s="63">
+        <v>45988</v>
+      </c>
+      <c r="CB4" s="63">
         <f t="shared" si="13"/>
-        <v>45901</v>
-      </c>
-      <c r="Q4" s="63">
+        <v>45989</v>
+      </c>
+      <c r="CC4" s="63">
         <f t="shared" si="13"/>
-        <v>45902</v>
-      </c>
-      <c r="R4" s="63">
+        <v>45992</v>
+      </c>
+      <c r="CD4" s="63">
         <f t="shared" si="13"/>
-        <v>45903</v>
-      </c>
-      <c r="S4" s="63">
+        <v>45993</v>
+      </c>
+      <c r="CE4" s="63">
         <f t="shared" si="13"/>
-        <v>45904</v>
-      </c>
-      <c r="T4" s="63">
+        <v>45994</v>
+      </c>
+      <c r="CF4" s="63">
         <f t="shared" si="13"/>
-        <v>45905</v>
-      </c>
-      <c r="U4" s="63">
+        <v>45995</v>
+      </c>
+      <c r="CG4" s="63">
         <f t="shared" si="13"/>
-        <v>45908</v>
-      </c>
-      <c r="V4" s="63">
-        <f t="shared" si="13"/>
-        <v>45909</v>
-      </c>
-      <c r="W4" s="63">
-        <f t="shared" si="13"/>
-        <v>45910</v>
-      </c>
-      <c r="X4" s="63">
-        <f t="shared" si="13"/>
-        <v>45911</v>
-      </c>
-      <c r="Y4" s="63">
-        <f t="shared" si="13"/>
-        <v>45912</v>
-      </c>
-      <c r="Z4" s="63">
-        <f t="shared" si="13"/>
-        <v>45915</v>
-      </c>
-      <c r="AA4" s="63">
-        <f t="shared" si="13"/>
-        <v>45916</v>
-      </c>
-      <c r="AB4" s="63">
-        <f t="shared" si="13"/>
-        <v>45917</v>
-      </c>
-      <c r="AC4" s="96">
-        <f t="shared" si="13"/>
-        <v>45918</v>
-      </c>
-      <c r="AD4" s="96">
-        <f t="shared" si="13"/>
-        <v>45919</v>
-      </c>
-      <c r="AE4" s="63">
-        <f t="shared" si="13"/>
-        <v>45922</v>
-      </c>
-      <c r="AF4" s="63">
-        <f t="shared" si="13"/>
-        <v>45923</v>
-      </c>
-      <c r="AG4" s="63">
-        <f t="shared" si="13"/>
-        <v>45924</v>
-      </c>
-      <c r="AH4" s="63">
-        <f t="shared" si="13"/>
-        <v>45925</v>
-      </c>
-      <c r="AI4" s="63">
-        <f t="shared" si="13"/>
-        <v>45926</v>
-      </c>
-      <c r="AJ4" s="63">
-        <f t="shared" si="13"/>
-        <v>45929</v>
-      </c>
-      <c r="AK4" s="63">
-        <f t="shared" si="13"/>
-        <v>45930</v>
-      </c>
-      <c r="AL4" s="63">
-        <f t="shared" si="13"/>
-        <v>45931</v>
-      </c>
-      <c r="AM4" s="63">
-        <f t="shared" si="13"/>
-        <v>45932</v>
-      </c>
-      <c r="AN4" s="63">
-        <f t="shared" si="13"/>
-        <v>45933</v>
-      </c>
-      <c r="AO4" s="63">
-        <f t="shared" ref="AO4:BT4" si="14">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(AG1)-1)</f>
-        <v>45936</v>
-      </c>
-      <c r="AP4" s="63">
-        <f t="shared" si="14"/>
-        <v>45937</v>
-      </c>
-      <c r="AQ4" s="63">
-        <f t="shared" si="14"/>
-        <v>45938</v>
-      </c>
-      <c r="AR4" s="63">
-        <f t="shared" si="14"/>
-        <v>45939</v>
-      </c>
-      <c r="AS4" s="63">
-        <f t="shared" si="14"/>
-        <v>45940</v>
-      </c>
-      <c r="AT4" s="63">
-        <f t="shared" si="14"/>
-        <v>45943</v>
-      </c>
-      <c r="AU4" s="63">
-        <f t="shared" si="14"/>
-        <v>45944</v>
-      </c>
-      <c r="AV4" s="63">
-        <f t="shared" si="14"/>
-        <v>45945</v>
-      </c>
-      <c r="AW4" s="63">
-        <f t="shared" si="14"/>
-        <v>45946</v>
-      </c>
-      <c r="AX4" s="63">
-        <f t="shared" si="14"/>
-        <v>45947</v>
-      </c>
-      <c r="AY4" s="63">
-        <f t="shared" si="14"/>
-        <v>45950</v>
-      </c>
-      <c r="AZ4" s="63">
-        <f t="shared" si="14"/>
-        <v>45951</v>
-      </c>
-      <c r="BA4" s="63">
-        <f t="shared" si="14"/>
-        <v>45952</v>
-      </c>
-      <c r="BB4" s="63">
-        <f t="shared" si="14"/>
-        <v>45953</v>
-      </c>
-      <c r="BC4" s="63">
-        <f t="shared" si="14"/>
-        <v>45954</v>
-      </c>
-      <c r="BD4" s="63">
-        <f t="shared" si="14"/>
-        <v>45957</v>
-      </c>
-      <c r="BE4" s="63">
-        <f t="shared" si="14"/>
-        <v>45958</v>
-      </c>
-      <c r="BF4" s="63">
-        <f t="shared" si="14"/>
-        <v>45959</v>
-      </c>
-      <c r="BG4" s="63">
-        <f t="shared" si="14"/>
-        <v>45960</v>
-      </c>
-      <c r="BH4" s="63">
-        <f t="shared" si="14"/>
-        <v>45961</v>
-      </c>
-      <c r="BI4" s="63">
-        <f t="shared" si="14"/>
-        <v>45964</v>
-      </c>
-      <c r="BJ4" s="63">
-        <f t="shared" si="14"/>
-        <v>45965</v>
-      </c>
-      <c r="BK4" s="63">
-        <f t="shared" si="14"/>
-        <v>45966</v>
-      </c>
-      <c r="BL4" s="63">
-        <f t="shared" si="14"/>
-        <v>45967</v>
-      </c>
-      <c r="BM4" s="63">
-        <f t="shared" si="14"/>
-        <v>45968</v>
-      </c>
-      <c r="BN4" s="63">
-        <f t="shared" si="14"/>
-        <v>45971</v>
-      </c>
-      <c r="BO4" s="63">
-        <f t="shared" si="14"/>
-        <v>45972</v>
-      </c>
-      <c r="BP4" s="63">
-        <f t="shared" si="14"/>
-        <v>45973</v>
-      </c>
-      <c r="BQ4" s="63">
-        <f t="shared" si="14"/>
-        <v>45974</v>
-      </c>
-      <c r="BR4" s="63">
-        <f t="shared" si="14"/>
-        <v>45975</v>
-      </c>
-      <c r="BS4" s="63">
-        <f t="shared" si="14"/>
-        <v>45978</v>
-      </c>
-      <c r="BT4" s="63">
-        <f t="shared" si="14"/>
-        <v>45979</v>
-      </c>
-      <c r="BU4" s="63">
-        <f t="shared" ref="BU4:CG4" si="15">WORKDAY(Inicio_del_proyecto-1, (Semana_para_mostrar-1)*5 + COLUMN(BM1)-1)</f>
-        <v>45980</v>
-      </c>
-      <c r="BV4" s="63">
-        <f t="shared" si="15"/>
-        <v>45981</v>
-      </c>
-      <c r="BW4" s="63">
-        <f t="shared" si="15"/>
-        <v>45982</v>
-      </c>
-      <c r="BX4" s="63">
-        <f t="shared" si="15"/>
-        <v>45985</v>
-      </c>
-      <c r="BY4" s="63">
-        <f t="shared" si="15"/>
-        <v>45986</v>
-      </c>
-      <c r="BZ4" s="63">
-        <f t="shared" si="15"/>
-        <v>45987</v>
-      </c>
-      <c r="CA4" s="63">
-        <f t="shared" si="15"/>
-        <v>45988</v>
-      </c>
-      <c r="CB4" s="63">
-        <f t="shared" si="15"/>
-        <v>45989</v>
-      </c>
-      <c r="CC4" s="63">
-        <f t="shared" si="15"/>
-        <v>45992</v>
-      </c>
-      <c r="CD4" s="63">
-        <f t="shared" si="15"/>
-        <v>45993</v>
-      </c>
-      <c r="CE4" s="63">
-        <f t="shared" si="15"/>
-        <v>45994</v>
-      </c>
-      <c r="CF4" s="63">
-        <f t="shared" si="15"/>
-        <v>45995</v>
-      </c>
-      <c r="CG4" s="63">
-        <f t="shared" si="15"/>
         <v>45996</v>
       </c>
     </row>
@@ -2904,31 +2979,31 @@
         <v>17</v>
       </c>
       <c r="I5" s="10" t="str">
-        <f t="shared" ref="I5" si="16">LEFT(TEXT(I4,"ddd"),1)</f>
+        <f t="shared" ref="I5" si="14">LEFT(TEXT(I4,"ddd"),1)</f>
         <v>j</v>
       </c>
       <c r="J5" s="10" t="str">
-        <f t="shared" ref="J5:AR5" si="17">LEFT(TEXT(J4,"ddd"),1)</f>
+        <f t="shared" ref="J5:AR5" si="15">LEFT(TEXT(J4,"ddd"),1)</f>
         <v>v</v>
       </c>
       <c r="K5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="L5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="M5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="N5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="O5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>v</v>
       </c>
       <c r="P5" s="10" t="str">
@@ -2952,264 +3027,267 @@
         <v>v</v>
       </c>
       <c r="U5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="V5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="W5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="X5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="Y5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>v</v>
       </c>
       <c r="Z5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="AA5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AB5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AC5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="AD5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>v</v>
       </c>
       <c r="AE5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="AF5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AG5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AH5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="AI5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>v</v>
       </c>
       <c r="AJ5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="AK5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AL5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AM5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="AN5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>v</v>
       </c>
       <c r="AO5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>l</v>
       </c>
       <c r="AP5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AQ5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>m</v>
       </c>
       <c r="AR5" s="10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="15"/>
         <v>j</v>
       </c>
       <c r="AS5" s="10" t="str">
-        <f t="shared" ref="AS5:CG5" si="18">LEFT(TEXT(AS4,"ddd"),1)</f>
+        <f t="shared" ref="AS5:CG5" si="16">LEFT(TEXT(AS4,"ddd"),1)</f>
         <v>v</v>
       </c>
       <c r="AT5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="AU5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="AV5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="AW5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="AX5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="AY5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="AZ5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BA5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BB5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="BC5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="BD5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="BE5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BF5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BG5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="BH5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="BI5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="BJ5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BK5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BL5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="BM5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="BN5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="BO5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BP5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BQ5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="BR5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="BS5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="BT5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BU5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BV5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="BW5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="BX5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="BY5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="BZ5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="CA5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="CB5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
       </c>
       <c r="CC5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>l</v>
       </c>
       <c r="CD5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="CE5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>m</v>
       </c>
       <c r="CF5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>j</v>
       </c>
       <c r="CG5" s="10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="16"/>
         <v>v</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:121" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3300,267 +3378,267 @@
       <c r="CF6" s="26"/>
       <c r="CG6" s="26"/>
     </row>
-    <row r="7" spans="1:121" s="137" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:121" s="119" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="100"/>
-      <c r="B7" s="127" t="s">
+      <c r="B7" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="128"/>
-      <c r="D7" s="129"/>
-      <c r="E7" s="130"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="132"/>
-      <c r="H7" s="132" t="str">
-        <f t="shared" ref="H7:H64" si="19">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
+      <c r="C7" s="113"/>
+      <c r="D7" s="114"/>
+      <c r="E7" s="115"/>
+      <c r="F7" s="116"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117" t="str">
+        <f t="shared" ref="H7:H72" si="17">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="133"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="134"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="134"/>
-      <c r="N7" s="134"/>
-      <c r="O7" s="134"/>
-      <c r="P7" s="134"/>
-      <c r="Q7" s="134"/>
-      <c r="R7" s="134"/>
-      <c r="S7" s="134"/>
-      <c r="T7" s="134"/>
-      <c r="U7" s="134"/>
-      <c r="V7" s="134"/>
-      <c r="W7" s="134"/>
-      <c r="X7" s="134"/>
-      <c r="Y7" s="134"/>
-      <c r="Z7" s="134"/>
-      <c r="AA7" s="134"/>
-      <c r="AB7" s="134"/>
-      <c r="AC7" s="134"/>
-      <c r="AD7" s="134"/>
-      <c r="AE7" s="134"/>
-      <c r="AF7" s="134"/>
-      <c r="AG7" s="134"/>
-      <c r="AH7" s="134"/>
-      <c r="AI7" s="134"/>
-      <c r="AJ7" s="134"/>
-      <c r="AK7" s="134"/>
-      <c r="AL7" s="134"/>
-      <c r="AM7" s="134"/>
-      <c r="AN7" s="134"/>
-      <c r="AO7" s="134"/>
-      <c r="AP7" s="134"/>
-      <c r="AQ7" s="134"/>
-      <c r="AR7" s="134"/>
-      <c r="AS7" s="134"/>
-      <c r="AT7" s="134"/>
-      <c r="AU7" s="134"/>
-      <c r="AV7" s="134"/>
-      <c r="AW7" s="134"/>
-      <c r="AX7" s="134"/>
-      <c r="AY7" s="134"/>
-      <c r="AZ7" s="134"/>
-      <c r="BA7" s="134"/>
-      <c r="BB7" s="134"/>
-      <c r="BC7" s="134"/>
-      <c r="BD7" s="134"/>
-      <c r="BE7" s="134"/>
-      <c r="BF7" s="134"/>
-      <c r="BG7" s="134"/>
-      <c r="BH7" s="134"/>
-      <c r="BI7" s="134"/>
-      <c r="BJ7" s="134"/>
-      <c r="BK7" s="134"/>
-      <c r="BL7" s="134"/>
-      <c r="BM7" s="134"/>
-      <c r="BN7" s="134"/>
-      <c r="BO7" s="134"/>
-      <c r="BP7" s="134"/>
-      <c r="BQ7" s="134"/>
-      <c r="BR7" s="134"/>
-      <c r="BS7" s="134"/>
-      <c r="BT7" s="134"/>
-      <c r="BU7" s="134"/>
-      <c r="BV7" s="134"/>
-      <c r="BW7" s="134"/>
-      <c r="BX7" s="134"/>
-      <c r="BY7" s="134"/>
-      <c r="BZ7" s="134"/>
-      <c r="CA7" s="134"/>
-      <c r="CB7" s="134"/>
-      <c r="CC7" s="134"/>
-      <c r="CD7" s="134"/>
-      <c r="CE7" s="134"/>
-      <c r="CF7" s="134"/>
-      <c r="CG7" s="135"/>
-      <c r="CH7" s="136"/>
-      <c r="CI7" s="136"/>
-      <c r="CJ7" s="136"/>
-      <c r="CK7" s="136"/>
-      <c r="CL7" s="136"/>
-      <c r="CM7" s="136"/>
-      <c r="CN7" s="136"/>
-      <c r="CO7" s="136"/>
-      <c r="CP7" s="136"/>
-      <c r="CQ7" s="136"/>
-      <c r="CR7" s="136"/>
-      <c r="CS7" s="136"/>
-      <c r="CT7" s="136"/>
-      <c r="CU7" s="136"/>
-      <c r="CV7" s="136"/>
-      <c r="CW7" s="136"/>
-      <c r="CX7" s="136"/>
-      <c r="CY7" s="136"/>
-      <c r="CZ7" s="136"/>
-      <c r="DA7" s="136"/>
-      <c r="DB7" s="136"/>
-      <c r="DC7" s="136"/>
-      <c r="DD7" s="136"/>
-      <c r="DE7" s="136"/>
-      <c r="DF7" s="136"/>
-      <c r="DG7" s="136"/>
-      <c r="DH7" s="136"/>
-      <c r="DI7" s="136"/>
-      <c r="DJ7" s="136"/>
-      <c r="DK7" s="136"/>
-      <c r="DL7" s="136"/>
-      <c r="DM7" s="136"/>
-      <c r="DN7" s="136"/>
-      <c r="DO7" s="136"/>
-      <c r="DP7" s="136"/>
-      <c r="DQ7" s="136"/>
-    </row>
-    <row r="8" spans="1:121" s="126" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="138"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="139"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="139"/>
+      <c r="Y7" s="139"/>
+      <c r="Z7" s="139"/>
+      <c r="AA7" s="139"/>
+      <c r="AB7" s="139"/>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="139"/>
+      <c r="AE7" s="139"/>
+      <c r="AF7" s="139"/>
+      <c r="AG7" s="139"/>
+      <c r="AH7" s="139"/>
+      <c r="AI7" s="139"/>
+      <c r="AJ7" s="139"/>
+      <c r="AK7" s="139"/>
+      <c r="AL7" s="139"/>
+      <c r="AM7" s="139"/>
+      <c r="AN7" s="139"/>
+      <c r="AO7" s="139"/>
+      <c r="AP7" s="139"/>
+      <c r="AQ7" s="139"/>
+      <c r="AR7" s="139"/>
+      <c r="AS7" s="139"/>
+      <c r="AT7" s="139"/>
+      <c r="AU7" s="139"/>
+      <c r="AV7" s="139"/>
+      <c r="AW7" s="139"/>
+      <c r="AX7" s="139"/>
+      <c r="AY7" s="139"/>
+      <c r="AZ7" s="139"/>
+      <c r="BA7" s="139"/>
+      <c r="BB7" s="139"/>
+      <c r="BC7" s="139"/>
+      <c r="BD7" s="139"/>
+      <c r="BE7" s="139"/>
+      <c r="BF7" s="139"/>
+      <c r="BG7" s="139"/>
+      <c r="BH7" s="139"/>
+      <c r="BI7" s="139"/>
+      <c r="BJ7" s="139"/>
+      <c r="BK7" s="139"/>
+      <c r="BL7" s="139"/>
+      <c r="BM7" s="139"/>
+      <c r="BN7" s="139"/>
+      <c r="BO7" s="139"/>
+      <c r="BP7" s="139"/>
+      <c r="BQ7" s="139"/>
+      <c r="BR7" s="139"/>
+      <c r="BS7" s="139"/>
+      <c r="BT7" s="139"/>
+      <c r="BU7" s="139"/>
+      <c r="BV7" s="139"/>
+      <c r="BW7" s="139"/>
+      <c r="BX7" s="139"/>
+      <c r="BY7" s="139"/>
+      <c r="BZ7" s="139"/>
+      <c r="CA7" s="139"/>
+      <c r="CB7" s="139"/>
+      <c r="CC7" s="139"/>
+      <c r="CD7" s="139"/>
+      <c r="CE7" s="139"/>
+      <c r="CF7" s="139"/>
+      <c r="CG7" s="140"/>
+      <c r="CH7" s="118"/>
+      <c r="CI7" s="118"/>
+      <c r="CJ7" s="118"/>
+      <c r="CK7" s="118"/>
+      <c r="CL7" s="118"/>
+      <c r="CM7" s="118"/>
+      <c r="CN7" s="118"/>
+      <c r="CO7" s="118"/>
+      <c r="CP7" s="118"/>
+      <c r="CQ7" s="118"/>
+      <c r="CR7" s="118"/>
+      <c r="CS7" s="118"/>
+      <c r="CT7" s="118"/>
+      <c r="CU7" s="118"/>
+      <c r="CV7" s="118"/>
+      <c r="CW7" s="118"/>
+      <c r="CX7" s="118"/>
+      <c r="CY7" s="118"/>
+      <c r="CZ7" s="118"/>
+      <c r="DA7" s="118"/>
+      <c r="DB7" s="118"/>
+      <c r="DC7" s="118"/>
+      <c r="DD7" s="118"/>
+      <c r="DE7" s="118"/>
+      <c r="DF7" s="118"/>
+      <c r="DG7" s="118"/>
+      <c r="DH7" s="118"/>
+      <c r="DI7" s="118"/>
+      <c r="DJ7" s="118"/>
+      <c r="DK7" s="118"/>
+      <c r="DL7" s="118"/>
+      <c r="DM7" s="118"/>
+      <c r="DN7" s="118"/>
+      <c r="DO7" s="118"/>
+      <c r="DP7" s="118"/>
+      <c r="DQ7" s="118"/>
+    </row>
+    <row r="8" spans="1:121" s="111" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="100"/>
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="120"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="122"/>
-      <c r="F8" s="122"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123" t="str">
-        <f t="shared" si="19"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="106"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="107"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="108" t="str">
+        <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I8" s="124"/>
-      <c r="J8" s="124"/>
-      <c r="K8" s="124"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="124"/>
-      <c r="U8" s="124"/>
-      <c r="V8" s="124"/>
-      <c r="W8" s="124"/>
-      <c r="X8" s="124"/>
-      <c r="Y8" s="124"/>
-      <c r="Z8" s="124"/>
-      <c r="AA8" s="124"/>
-      <c r="AB8" s="124"/>
-      <c r="AC8" s="124"/>
-      <c r="AD8" s="124"/>
-      <c r="AE8" s="124"/>
-      <c r="AF8" s="124"/>
-      <c r="AG8" s="124"/>
-      <c r="AH8" s="124"/>
-      <c r="AI8" s="124"/>
-      <c r="AJ8" s="124"/>
-      <c r="AK8" s="124"/>
-      <c r="AL8" s="124"/>
-      <c r="AM8" s="124"/>
-      <c r="AN8" s="124"/>
-      <c r="AO8" s="124"/>
-      <c r="AP8" s="124"/>
-      <c r="AQ8" s="124"/>
-      <c r="AR8" s="124"/>
-      <c r="AS8" s="124"/>
-      <c r="AT8" s="124"/>
-      <c r="AU8" s="124"/>
-      <c r="AV8" s="124"/>
-      <c r="AW8" s="124"/>
-      <c r="AX8" s="124"/>
-      <c r="AY8" s="124"/>
-      <c r="AZ8" s="124"/>
-      <c r="BA8" s="124"/>
-      <c r="BB8" s="124"/>
-      <c r="BC8" s="124"/>
-      <c r="BD8" s="124"/>
-      <c r="BE8" s="124"/>
-      <c r="BF8" s="124"/>
-      <c r="BG8" s="124"/>
-      <c r="BH8" s="124"/>
-      <c r="BI8" s="124"/>
-      <c r="BJ8" s="124"/>
-      <c r="BK8" s="124"/>
-      <c r="BL8" s="124"/>
-      <c r="BM8" s="124"/>
-      <c r="BN8" s="124"/>
-      <c r="BO8" s="124"/>
-      <c r="BP8" s="124"/>
-      <c r="BQ8" s="124"/>
-      <c r="BR8" s="124"/>
-      <c r="BS8" s="124"/>
-      <c r="BT8" s="124"/>
-      <c r="BU8" s="124"/>
-      <c r="BV8" s="124"/>
-      <c r="BW8" s="124"/>
-      <c r="BX8" s="124"/>
-      <c r="BY8" s="124"/>
-      <c r="BZ8" s="124"/>
-      <c r="CA8" s="124"/>
-      <c r="CB8" s="124"/>
-      <c r="CC8" s="124"/>
-      <c r="CD8" s="124"/>
-      <c r="CE8" s="124"/>
-      <c r="CF8" s="124"/>
-      <c r="CG8" s="124"/>
-      <c r="CH8" s="125"/>
-      <c r="CI8" s="125"/>
-      <c r="CJ8" s="125"/>
-      <c r="CK8" s="125"/>
-      <c r="CL8" s="125"/>
-      <c r="CM8" s="125"/>
-      <c r="CN8" s="125"/>
-      <c r="CO8" s="125"/>
-      <c r="CP8" s="125"/>
-      <c r="CQ8" s="125"/>
-      <c r="CR8" s="125"/>
-      <c r="CS8" s="125"/>
-      <c r="CT8" s="125"/>
-      <c r="CU8" s="125"/>
-      <c r="CV8" s="125"/>
-      <c r="CW8" s="125"/>
-      <c r="CX8" s="125"/>
-      <c r="CY8" s="125"/>
-      <c r="CZ8" s="125"/>
-      <c r="DA8" s="125"/>
-      <c r="DB8" s="125"/>
-      <c r="DC8" s="125"/>
-      <c r="DD8" s="125"/>
-      <c r="DE8" s="125"/>
-      <c r="DF8" s="125"/>
-      <c r="DG8" s="125"/>
-      <c r="DH8" s="125"/>
-      <c r="DI8" s="125"/>
-      <c r="DJ8" s="125"/>
-      <c r="DK8" s="125"/>
-      <c r="DL8" s="125"/>
-      <c r="DM8" s="125"/>
-      <c r="DN8" s="125"/>
-      <c r="DO8" s="125"/>
-      <c r="DP8" s="125"/>
-      <c r="DQ8" s="125"/>
+      <c r="I8" s="109"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+      <c r="N8" s="109"/>
+      <c r="O8" s="109"/>
+      <c r="P8" s="109"/>
+      <c r="Q8" s="109"/>
+      <c r="R8" s="109"/>
+      <c r="S8" s="109"/>
+      <c r="T8" s="109"/>
+      <c r="U8" s="109"/>
+      <c r="V8" s="109"/>
+      <c r="W8" s="109"/>
+      <c r="X8" s="109"/>
+      <c r="Y8" s="109"/>
+      <c r="Z8" s="109"/>
+      <c r="AA8" s="109"/>
+      <c r="AB8" s="109"/>
+      <c r="AC8" s="109"/>
+      <c r="AD8" s="109"/>
+      <c r="AE8" s="109"/>
+      <c r="AF8" s="109"/>
+      <c r="AG8" s="109"/>
+      <c r="AH8" s="109"/>
+      <c r="AI8" s="109"/>
+      <c r="AJ8" s="109"/>
+      <c r="AK8" s="109"/>
+      <c r="AL8" s="109"/>
+      <c r="AM8" s="109"/>
+      <c r="AN8" s="109"/>
+      <c r="AO8" s="109"/>
+      <c r="AP8" s="109"/>
+      <c r="AQ8" s="109"/>
+      <c r="AR8" s="109"/>
+      <c r="AS8" s="109"/>
+      <c r="AT8" s="109"/>
+      <c r="AU8" s="109"/>
+      <c r="AV8" s="109"/>
+      <c r="AW8" s="109"/>
+      <c r="AX8" s="109"/>
+      <c r="AY8" s="109"/>
+      <c r="AZ8" s="109"/>
+      <c r="BA8" s="109"/>
+      <c r="BB8" s="109"/>
+      <c r="BC8" s="109"/>
+      <c r="BD8" s="109"/>
+      <c r="BE8" s="109"/>
+      <c r="BF8" s="109"/>
+      <c r="BG8" s="109"/>
+      <c r="BH8" s="109"/>
+      <c r="BI8" s="109"/>
+      <c r="BJ8" s="109"/>
+      <c r="BK8" s="109"/>
+      <c r="BL8" s="109"/>
+      <c r="BM8" s="109"/>
+      <c r="BN8" s="109"/>
+      <c r="BO8" s="109"/>
+      <c r="BP8" s="109"/>
+      <c r="BQ8" s="109"/>
+      <c r="BR8" s="109"/>
+      <c r="BS8" s="109"/>
+      <c r="BT8" s="109"/>
+      <c r="BU8" s="109"/>
+      <c r="BV8" s="109"/>
+      <c r="BW8" s="109"/>
+      <c r="BX8" s="109"/>
+      <c r="BY8" s="109"/>
+      <c r="BZ8" s="109"/>
+      <c r="CA8" s="109"/>
+      <c r="CB8" s="109"/>
+      <c r="CC8" s="109"/>
+      <c r="CD8" s="109"/>
+      <c r="CE8" s="109"/>
+      <c r="CF8" s="109"/>
+      <c r="CG8" s="109"/>
+      <c r="CH8" s="110"/>
+      <c r="CI8" s="110"/>
+      <c r="CJ8" s="110"/>
+      <c r="CK8" s="110"/>
+      <c r="CL8" s="110"/>
+      <c r="CM8" s="110"/>
+      <c r="CN8" s="110"/>
+      <c r="CO8" s="110"/>
+      <c r="CP8" s="110"/>
+      <c r="CQ8" s="110"/>
+      <c r="CR8" s="110"/>
+      <c r="CS8" s="110"/>
+      <c r="CT8" s="110"/>
+      <c r="CU8" s="110"/>
+      <c r="CV8" s="110"/>
+      <c r="CW8" s="110"/>
+      <c r="CX8" s="110"/>
+      <c r="CY8" s="110"/>
+      <c r="CZ8" s="110"/>
+      <c r="DA8" s="110"/>
+      <c r="DB8" s="110"/>
+      <c r="DC8" s="110"/>
+      <c r="DD8" s="110"/>
+      <c r="DE8" s="110"/>
+      <c r="DF8" s="110"/>
+      <c r="DG8" s="110"/>
+      <c r="DH8" s="110"/>
+      <c r="DI8" s="110"/>
+      <c r="DJ8" s="110"/>
+      <c r="DK8" s="110"/>
+      <c r="DL8" s="110"/>
+      <c r="DM8" s="110"/>
+      <c r="DN8" s="110"/>
+      <c r="DO8" s="110"/>
+      <c r="DP8" s="110"/>
+      <c r="DQ8" s="110"/>
     </row>
     <row r="9" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="153" t="s">
+      <c r="B9" s="135" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="46"/>
@@ -3694,24 +3772,24 @@
     </row>
     <row r="10" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="41"/>
-      <c r="B10" s="153" t="s">
-        <v>37</v>
+      <c r="B10" s="156" t="s">
+        <v>88</v>
       </c>
       <c r="C10" s="46"/>
       <c r="D10" s="15">
         <v>1</v>
       </c>
       <c r="E10" s="64">
-        <v>45895</v>
+        <v>45894</v>
       </c>
       <c r="F10" s="64">
-        <v>45895</v>
+        <v>45894</v>
       </c>
       <c r="G10" s="90"/>
       <c r="H10" s="14"/>
       <c r="I10" s="26"/>
       <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
+      <c r="K10" s="157"/>
       <c r="L10" s="26"/>
       <c r="M10" s="26"/>
       <c r="N10" s="26"/>
@@ -3824,9 +3902,9 @@
       <c r="DQ10"/>
     </row>
     <row r="11" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="40"/>
-      <c r="B11" s="153" t="s">
-        <v>38</v>
+      <c r="A11" s="41"/>
+      <c r="B11" s="135" t="s">
+        <v>90</v>
       </c>
       <c r="C11" s="46"/>
       <c r="D11" s="15">
@@ -3836,14 +3914,10 @@
         <v>45895</v>
       </c>
       <c r="F11" s="64">
-        <f>E11+1</f>
-        <v>45896</v>
+        <v>45895</v>
       </c>
       <c r="G11" s="90"/>
-      <c r="H11" s="14">
-        <f t="shared" si="19"/>
-        <v>2</v>
-      </c>
+      <c r="H11" s="14"/>
       <c r="I11" s="26"/>
       <c r="J11" s="26"/>
       <c r="K11" s="26"/>
@@ -3856,8 +3930,8 @@
       <c r="R11" s="26"/>
       <c r="S11" s="26"/>
       <c r="T11" s="26"/>
-      <c r="U11" s="26"/>
-      <c r="V11" s="26"/>
+      <c r="U11" s="27"/>
+      <c r="V11" s="27"/>
       <c r="W11" s="26"/>
       <c r="X11" s="26"/>
       <c r="Y11" s="26"/>
@@ -3912,8 +3986,8 @@
       <c r="BV11" s="67"/>
       <c r="BW11" s="67"/>
       <c r="BX11" s="67"/>
-      <c r="BY11" s="67"/>
-      <c r="BZ11" s="67"/>
+      <c r="BY11" s="68"/>
+      <c r="BZ11" s="68"/>
       <c r="CA11" s="67"/>
       <c r="CB11" s="67"/>
       <c r="CC11" s="67"/>
@@ -3959,20 +4033,19 @@
       <c r="DQ11"/>
     </row>
     <row r="12" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="40"/>
-      <c r="B12" s="154" t="s">
-        <v>95</v>
+      <c r="A12" s="41"/>
+      <c r="B12" s="135" t="s">
+        <v>91</v>
       </c>
       <c r="C12" s="46"/>
       <c r="D12" s="15">
         <v>1</v>
       </c>
       <c r="E12" s="64">
-        <v>45896</v>
+        <v>45895</v>
       </c>
       <c r="F12" s="64">
-        <f>E12+1</f>
-        <v>45897</v>
+        <v>45895</v>
       </c>
       <c r="G12" s="90"/>
       <c r="H12" s="14"/>
@@ -3988,8 +4061,8 @@
       <c r="R12" s="26"/>
       <c r="S12" s="26"/>
       <c r="T12" s="26"/>
-      <c r="U12" s="26"/>
-      <c r="V12" s="26"/>
+      <c r="U12" s="27"/>
+      <c r="V12" s="27"/>
       <c r="W12" s="26"/>
       <c r="X12" s="26"/>
       <c r="Y12" s="26"/>
@@ -4044,8 +4117,8 @@
       <c r="BV12" s="67"/>
       <c r="BW12" s="67"/>
       <c r="BX12" s="67"/>
-      <c r="BY12" s="67"/>
-      <c r="BZ12" s="67"/>
+      <c r="BY12" s="68"/>
+      <c r="BZ12" s="68"/>
       <c r="CA12" s="67"/>
       <c r="CB12" s="67"/>
       <c r="CC12" s="67"/>
@@ -4092,22 +4165,25 @@
     </row>
     <row r="13" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="40"/>
-      <c r="B13" s="154" t="s">
-        <v>94</v>
+      <c r="B13" s="135" t="s">
+        <v>92</v>
       </c>
       <c r="C13" s="46"/>
       <c r="D13" s="15">
         <v>1</v>
       </c>
       <c r="E13" s="64">
-        <v>45896</v>
+        <v>45895</v>
       </c>
       <c r="F13" s="64">
         <f>E13+1</f>
-        <v>45897</v>
+        <v>45896</v>
       </c>
       <c r="G13" s="90"/>
-      <c r="H13" s="14"/>
+      <c r="H13" s="14">
+        <f t="shared" si="17"/>
+        <v>2</v>
+      </c>
       <c r="I13" s="26"/>
       <c r="J13" s="26"/>
       <c r="K13" s="26"/>
@@ -4224,24 +4300,22 @@
     </row>
     <row r="14" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="40"/>
-      <c r="B14" s="149" t="s">
+      <c r="B14" s="136" t="s">
         <v>93</v>
       </c>
       <c r="C14" s="46"/>
       <c r="D14" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="64">
-        <v>45898</v>
+        <v>45896</v>
       </c>
       <c r="F14" s="64">
-        <v>45904</v>
+        <f>E14+1</f>
+        <v>45897</v>
       </c>
       <c r="G14" s="90"/>
-      <c r="H14" s="14">
-        <f t="shared" si="19"/>
-        <v>7</v>
-      </c>
+      <c r="H14" s="14"/>
       <c r="I14" s="26"/>
       <c r="J14" s="26"/>
       <c r="K14" s="26"/>
@@ -4258,7 +4332,7 @@
       <c r="V14" s="26"/>
       <c r="W14" s="26"/>
       <c r="X14" s="26"/>
-      <c r="Y14" s="27"/>
+      <c r="Y14" s="26"/>
       <c r="Z14" s="26"/>
       <c r="AA14" s="26"/>
       <c r="AB14" s="26"/>
@@ -4314,7 +4388,7 @@
       <c r="BZ14" s="67"/>
       <c r="CA14" s="67"/>
       <c r="CB14" s="67"/>
-      <c r="CC14" s="68"/>
+      <c r="CC14" s="67"/>
       <c r="CD14" s="67"/>
       <c r="CE14" s="67"/>
       <c r="CF14" s="67"/>
@@ -4358,18 +4432,19 @@
     </row>
     <row r="15" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="40"/>
-      <c r="B15" s="154" t="s">
-        <v>96</v>
+      <c r="B15" s="136" t="s">
+        <v>94</v>
       </c>
       <c r="C15" s="46"/>
       <c r="D15" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="64">
-        <v>45898</v>
+        <v>45896</v>
       </c>
       <c r="F15" s="64">
-        <v>45904</v>
+        <f>E15+1</f>
+        <v>45897</v>
       </c>
       <c r="G15" s="90"/>
       <c r="H15" s="14"/>
@@ -4389,7 +4464,7 @@
       <c r="V15" s="26"/>
       <c r="W15" s="26"/>
       <c r="X15" s="26"/>
-      <c r="Y15" s="27"/>
+      <c r="Y15" s="26"/>
       <c r="Z15" s="26"/>
       <c r="AA15" s="26"/>
       <c r="AB15" s="26"/>
@@ -4445,7 +4520,7 @@
       <c r="BZ15" s="67"/>
       <c r="CA15" s="67"/>
       <c r="CB15" s="67"/>
-      <c r="CC15" s="68"/>
+      <c r="CC15" s="67"/>
       <c r="CD15" s="67"/>
       <c r="CE15" s="67"/>
       <c r="CF15" s="67"/>
@@ -4489,21 +4564,24 @@
     </row>
     <row r="16" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="40"/>
-      <c r="B16" s="154" t="s">
-        <v>97</v>
+      <c r="B16" s="131" t="s">
+        <v>95</v>
       </c>
       <c r="C16" s="46"/>
       <c r="D16" s="15">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="E16" s="64">
         <v>45898</v>
       </c>
       <c r="F16" s="64">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="G16" s="90"/>
-      <c r="H16" s="14"/>
+      <c r="H16" s="14">
+        <f t="shared" si="17"/>
+        <v>7</v>
+      </c>
       <c r="I16" s="26"/>
       <c r="J16" s="26"/>
       <c r="K16" s="26"/>
@@ -4620,24 +4698,21 @@
     </row>
     <row r="17" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="40"/>
-      <c r="B17" s="150" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="72"/>
+      <c r="B17" s="158" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" s="46"/>
       <c r="D17" s="15">
         <v>0</v>
       </c>
       <c r="E17" s="64">
-        <v>45901</v>
+        <v>45904</v>
       </c>
       <c r="F17" s="64">
         <v>45904</v>
       </c>
       <c r="G17" s="90"/>
-      <c r="H17" s="14">
-        <f t="shared" si="19"/>
-        <v>4</v>
-      </c>
+      <c r="H17" s="14"/>
       <c r="I17" s="26"/>
       <c r="J17" s="26"/>
       <c r="K17" s="26"/>
@@ -4654,7 +4729,7 @@
       <c r="V17" s="26"/>
       <c r="W17" s="26"/>
       <c r="X17" s="26"/>
-      <c r="Y17" s="26"/>
+      <c r="Y17" s="27"/>
       <c r="Z17" s="26"/>
       <c r="AA17" s="26"/>
       <c r="AB17" s="26"/>
@@ -4710,7 +4785,7 @@
       <c r="BZ17" s="67"/>
       <c r="CA17" s="67"/>
       <c r="CB17" s="67"/>
-      <c r="CC17" s="67"/>
+      <c r="CC17" s="68"/>
       <c r="CD17" s="67"/>
       <c r="CE17" s="67"/>
       <c r="CF17" s="67"/>
@@ -4754,15 +4829,15 @@
     </row>
     <row r="18" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="40"/>
-      <c r="B18" s="150" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="72"/>
+      <c r="B18" s="136" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" s="46"/>
       <c r="D18" s="15">
         <v>0</v>
       </c>
       <c r="E18" s="64">
-        <v>45901</v>
+        <v>45898</v>
       </c>
       <c r="F18" s="64">
         <v>45904</v>
@@ -4785,7 +4860,7 @@
       <c r="V18" s="26"/>
       <c r="W18" s="26"/>
       <c r="X18" s="26"/>
-      <c r="Y18" s="26"/>
+      <c r="Y18" s="27"/>
       <c r="Z18" s="26"/>
       <c r="AA18" s="26"/>
       <c r="AB18" s="26"/>
@@ -4841,7 +4916,7 @@
       <c r="BZ18" s="67"/>
       <c r="CA18" s="67"/>
       <c r="CB18" s="67"/>
-      <c r="CC18" s="67"/>
+      <c r="CC18" s="68"/>
       <c r="CD18" s="67"/>
       <c r="CE18" s="67"/>
       <c r="CF18" s="67"/>
@@ -4885,18 +4960,18 @@
     </row>
     <row r="19" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="40"/>
-      <c r="B19" s="150" t="s">
-        <v>41</v>
-      </c>
-      <c r="C19" s="72"/>
+      <c r="B19" s="136" t="s">
+        <v>98</v>
+      </c>
+      <c r="C19" s="46"/>
       <c r="D19" s="15">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="E19" s="64">
-        <v>45905</v>
+        <v>45898</v>
       </c>
       <c r="F19" s="64">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="G19" s="90"/>
       <c r="H19" s="14"/>
@@ -4916,7 +4991,7 @@
       <c r="V19" s="26"/>
       <c r="W19" s="26"/>
       <c r="X19" s="26"/>
-      <c r="Y19" s="26"/>
+      <c r="Y19" s="27"/>
       <c r="Z19" s="26"/>
       <c r="AA19" s="26"/>
       <c r="AB19" s="26"/>
@@ -4972,7 +5047,7 @@
       <c r="BZ19" s="67"/>
       <c r="CA19" s="67"/>
       <c r="CB19" s="67"/>
-      <c r="CC19" s="67"/>
+      <c r="CC19" s="68"/>
       <c r="CD19" s="67"/>
       <c r="CE19" s="67"/>
       <c r="CF19" s="67"/>
@@ -5016,21 +5091,24 @@
     </row>
     <row r="20" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="40"/>
-      <c r="B20" s="151" t="s">
-        <v>42</v>
+      <c r="B20" s="132" t="s">
+        <v>37</v>
       </c>
       <c r="C20" s="72"/>
       <c r="D20" s="15">
         <v>0</v>
       </c>
       <c r="E20" s="64">
-        <v>45908</v>
+        <v>45901</v>
       </c>
       <c r="F20" s="64">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="G20" s="90"/>
-      <c r="H20" s="14"/>
+      <c r="H20" s="14">
+        <f t="shared" si="17"/>
+        <v>4</v>
+      </c>
       <c r="I20" s="26"/>
       <c r="J20" s="26"/>
       <c r="K20" s="26"/>
@@ -5147,18 +5225,18 @@
     </row>
     <row r="21" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="40"/>
-      <c r="B21" s="151" t="s">
-        <v>43</v>
+      <c r="B21" s="132" t="s">
+        <v>38</v>
       </c>
       <c r="C21" s="72"/>
       <c r="D21" s="15">
         <v>0</v>
       </c>
       <c r="E21" s="64">
-        <v>45910</v>
+        <v>45901</v>
       </c>
       <c r="F21" s="64">
-        <v>45911</v>
+        <v>45904</v>
       </c>
       <c r="G21" s="90"/>
       <c r="H21" s="14"/>
@@ -5278,18 +5356,18 @@
     </row>
     <row r="22" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="40"/>
-      <c r="B22" s="150" t="s">
-        <v>44</v>
+      <c r="B22" s="132" t="s">
+        <v>39</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="15">
         <v>0</v>
       </c>
       <c r="E22" s="64">
-        <v>45912</v>
+        <v>45905</v>
       </c>
       <c r="F22" s="64">
-        <v>45917</v>
+        <v>45909</v>
       </c>
       <c r="G22" s="90"/>
       <c r="H22" s="14"/>
@@ -5409,18 +5487,18 @@
     </row>
     <row r="23" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="40"/>
-      <c r="B23" s="151" t="s">
-        <v>45</v>
+      <c r="B23" s="133" t="s">
+        <v>40</v>
       </c>
       <c r="C23" s="72"/>
       <c r="D23" s="15">
         <v>0</v>
       </c>
       <c r="E23" s="64">
-        <v>45916</v>
+        <v>45908</v>
       </c>
       <c r="F23" s="64">
-        <v>45917</v>
+        <v>45911</v>
       </c>
       <c r="G23" s="90"/>
       <c r="H23" s="14"/>
@@ -5540,18 +5618,18 @@
     </row>
     <row r="24" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="40"/>
-      <c r="B24" s="150" t="s">
-        <v>46</v>
+      <c r="B24" s="133" t="s">
+        <v>41</v>
       </c>
       <c r="C24" s="72"/>
       <c r="D24" s="15">
         <v>0</v>
       </c>
       <c r="E24" s="64">
-        <v>45922</v>
+        <v>45910</v>
       </c>
       <c r="F24" s="64">
-        <v>45923</v>
+        <v>45911</v>
       </c>
       <c r="G24" s="90"/>
       <c r="H24" s="14"/>
@@ -5669,145 +5747,151 @@
       <c r="DP24"/>
       <c r="DQ24"/>
     </row>
-    <row r="25" spans="1:121" s="126" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="138"/>
-      <c r="B25" s="152" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="139"/>
-      <c r="D25" s="121"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="122"/>
-      <c r="G25" s="123"/>
-      <c r="H25" s="123"/>
-      <c r="I25" s="124"/>
-      <c r="J25" s="124"/>
-      <c r="K25" s="124"/>
-      <c r="L25" s="124"/>
-      <c r="M25" s="124"/>
-      <c r="N25" s="124"/>
-      <c r="O25" s="124"/>
-      <c r="P25" s="124"/>
-      <c r="Q25" s="124"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
-      <c r="T25" s="124"/>
-      <c r="U25" s="124"/>
-      <c r="V25" s="124"/>
-      <c r="W25" s="124"/>
-      <c r="X25" s="124"/>
-      <c r="Y25" s="124"/>
-      <c r="Z25" s="124"/>
-      <c r="AA25" s="124"/>
-      <c r="AB25" s="124"/>
-      <c r="AC25" s="124"/>
-      <c r="AD25" s="124"/>
-      <c r="AE25" s="124"/>
-      <c r="AF25" s="124"/>
-      <c r="AG25" s="124"/>
-      <c r="AH25" s="124"/>
-      <c r="AI25" s="124"/>
-      <c r="AJ25" s="124"/>
-      <c r="AK25" s="124"/>
-      <c r="AL25" s="124"/>
-      <c r="AM25" s="124"/>
-      <c r="AN25" s="124"/>
-      <c r="AO25" s="124"/>
-      <c r="AP25" s="124"/>
-      <c r="AQ25" s="124"/>
-      <c r="AR25" s="124"/>
-      <c r="AS25" s="124"/>
-      <c r="AT25" s="124"/>
-      <c r="AU25" s="124"/>
-      <c r="AV25" s="124"/>
-      <c r="AW25" s="124"/>
-      <c r="AX25" s="124"/>
-      <c r="AY25" s="124"/>
-      <c r="AZ25" s="124"/>
-      <c r="BA25" s="124"/>
-      <c r="BB25" s="124"/>
-      <c r="BC25" s="124"/>
-      <c r="BD25" s="124"/>
-      <c r="BE25" s="124"/>
-      <c r="BF25" s="124"/>
-      <c r="BG25" s="124"/>
-      <c r="BH25" s="124"/>
-      <c r="BI25" s="124"/>
-      <c r="BJ25" s="124"/>
-      <c r="BK25" s="124"/>
-      <c r="BL25" s="124"/>
-      <c r="BM25" s="124"/>
-      <c r="BN25" s="124"/>
-      <c r="BO25" s="124"/>
-      <c r="BP25" s="124"/>
-      <c r="BQ25" s="124"/>
-      <c r="BR25" s="124"/>
-      <c r="BS25" s="124"/>
-      <c r="BT25" s="124"/>
-      <c r="BU25" s="124"/>
-      <c r="BV25" s="124"/>
-      <c r="BW25" s="124"/>
-      <c r="BX25" s="124"/>
-      <c r="BY25" s="124"/>
-      <c r="BZ25" s="124"/>
-      <c r="CA25" s="124"/>
-      <c r="CB25" s="124"/>
-      <c r="CC25" s="124"/>
-      <c r="CD25" s="124"/>
-      <c r="CE25" s="124"/>
-      <c r="CF25" s="124"/>
-      <c r="CG25" s="124"/>
-      <c r="CH25" s="125"/>
-      <c r="CI25" s="125"/>
-      <c r="CJ25" s="125"/>
-      <c r="CK25" s="125"/>
-      <c r="CL25" s="125"/>
-      <c r="CM25" s="125"/>
-      <c r="CN25" s="125"/>
-      <c r="CO25" s="125"/>
-      <c r="CP25" s="125"/>
-      <c r="CQ25" s="125"/>
-      <c r="CR25" s="125"/>
-      <c r="CS25" s="125"/>
-      <c r="CT25" s="125"/>
-      <c r="CU25" s="125"/>
-      <c r="CV25" s="125"/>
-      <c r="CW25" s="125"/>
-      <c r="CX25" s="125"/>
-      <c r="CY25" s="125"/>
-      <c r="CZ25" s="125"/>
-      <c r="DA25" s="125"/>
-      <c r="DB25" s="125"/>
-      <c r="DC25" s="125"/>
-      <c r="DD25" s="125"/>
-      <c r="DE25" s="125"/>
-      <c r="DF25" s="125"/>
-      <c r="DG25" s="125"/>
-      <c r="DH25" s="125"/>
-      <c r="DI25" s="125"/>
-      <c r="DJ25" s="125"/>
-      <c r="DK25" s="125"/>
-      <c r="DL25" s="125"/>
-      <c r="DM25" s="125"/>
-      <c r="DN25" s="125"/>
-      <c r="DO25" s="125"/>
-      <c r="DP25" s="125"/>
-      <c r="DQ25" s="125"/>
+    <row r="25" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="40"/>
+      <c r="B25" s="133" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="72"/>
+      <c r="D25" s="15">
+        <v>0</v>
+      </c>
+      <c r="E25" s="64">
+        <v>45911</v>
+      </c>
+      <c r="F25" s="64">
+        <v>45911</v>
+      </c>
+      <c r="G25" s="90"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="26"/>
+      <c r="V25" s="26"/>
+      <c r="W25" s="26"/>
+      <c r="X25" s="159"/>
+      <c r="Y25" s="26"/>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="26"/>
+      <c r="AB25" s="26"/>
+      <c r="AC25" s="97"/>
+      <c r="AD25" s="97"/>
+      <c r="AE25" s="26"/>
+      <c r="AF25" s="26"/>
+      <c r="AG25" s="26"/>
+      <c r="AH25" s="26"/>
+      <c r="AI25" s="26"/>
+      <c r="AJ25" s="26"/>
+      <c r="AK25" s="26"/>
+      <c r="AL25" s="26"/>
+      <c r="AM25" s="26"/>
+      <c r="AN25" s="26"/>
+      <c r="AO25" s="26"/>
+      <c r="AP25" s="26"/>
+      <c r="AQ25" s="26"/>
+      <c r="AR25" s="26"/>
+      <c r="AS25" s="26"/>
+      <c r="AT25" s="26"/>
+      <c r="AU25" s="26"/>
+      <c r="AV25" s="26"/>
+      <c r="AW25" s="26"/>
+      <c r="AX25" s="26"/>
+      <c r="AY25" s="26"/>
+      <c r="AZ25" s="26"/>
+      <c r="BA25" s="26"/>
+      <c r="BB25" s="26"/>
+      <c r="BC25" s="26"/>
+      <c r="BD25" s="26"/>
+      <c r="BE25" s="26"/>
+      <c r="BF25" s="26"/>
+      <c r="BG25" s="26"/>
+      <c r="BH25" s="26"/>
+      <c r="BI25" s="26"/>
+      <c r="BJ25" s="26"/>
+      <c r="BK25" s="26"/>
+      <c r="BL25" s="26"/>
+      <c r="BM25" s="26"/>
+      <c r="BN25" s="26"/>
+      <c r="BO25" s="26"/>
+      <c r="BP25" s="26"/>
+      <c r="BQ25" s="67"/>
+      <c r="BR25" s="67"/>
+      <c r="BS25" s="67"/>
+      <c r="BT25" s="67"/>
+      <c r="BU25" s="67"/>
+      <c r="BV25" s="67"/>
+      <c r="BW25" s="67"/>
+      <c r="BX25" s="67"/>
+      <c r="BY25" s="67"/>
+      <c r="BZ25" s="67"/>
+      <c r="CA25" s="67"/>
+      <c r="CB25" s="67"/>
+      <c r="CC25" s="67"/>
+      <c r="CD25" s="67"/>
+      <c r="CE25" s="67"/>
+      <c r="CF25" s="67"/>
+      <c r="CG25" s="67"/>
+      <c r="CH25"/>
+      <c r="CI25"/>
+      <c r="CJ25"/>
+      <c r="CK25"/>
+      <c r="CL25"/>
+      <c r="CM25"/>
+      <c r="CN25"/>
+      <c r="CO25"/>
+      <c r="CP25"/>
+      <c r="CQ25"/>
+      <c r="CR25"/>
+      <c r="CS25"/>
+      <c r="CT25"/>
+      <c r="CU25"/>
+      <c r="CV25"/>
+      <c r="CW25"/>
+      <c r="CX25"/>
+      <c r="CY25"/>
+      <c r="CZ25"/>
+      <c r="DA25"/>
+      <c r="DB25"/>
+      <c r="DC25"/>
+      <c r="DD25"/>
+      <c r="DE25"/>
+      <c r="DF25"/>
+      <c r="DG25"/>
+      <c r="DH25"/>
+      <c r="DI25"/>
+      <c r="DJ25"/>
+      <c r="DK25"/>
+      <c r="DL25"/>
+      <c r="DM25"/>
+      <c r="DN25"/>
+      <c r="DO25"/>
+      <c r="DP25"/>
+      <c r="DQ25"/>
     </row>
     <row r="26" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="40"/>
-      <c r="B26" s="151" t="s">
-        <v>85</v>
+      <c r="B26" s="132" t="s">
+        <v>42</v>
       </c>
       <c r="C26" s="72"/>
       <c r="D26" s="15">
         <v>0</v>
       </c>
       <c r="E26" s="64">
-        <v>45923</v>
+        <v>45912</v>
       </c>
       <c r="F26" s="64">
-        <v>45925</v>
+        <v>45917</v>
       </c>
       <c r="G26" s="90"/>
       <c r="H26" s="14"/>
@@ -5927,18 +6011,18 @@
     </row>
     <row r="27" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="40"/>
-      <c r="B27" s="151" t="s">
-        <v>77</v>
+      <c r="B27" s="133" t="s">
+        <v>43</v>
       </c>
       <c r="C27" s="72"/>
       <c r="D27" s="15">
         <v>0</v>
       </c>
       <c r="E27" s="64">
-        <v>45924</v>
+        <v>45916</v>
       </c>
       <c r="F27" s="64">
-        <v>45924</v>
+        <v>45917</v>
       </c>
       <c r="G27" s="90"/>
       <c r="H27" s="14"/>
@@ -6058,18 +6142,18 @@
     </row>
     <row r="28" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="40"/>
-      <c r="B28" s="151" t="s">
-        <v>78</v>
+      <c r="B28" s="132" t="s">
+        <v>44</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="15">
         <v>0</v>
       </c>
       <c r="E28" s="64">
-        <v>45925</v>
+        <v>45922</v>
       </c>
       <c r="F28" s="64">
-        <v>45926</v>
+        <v>45923</v>
       </c>
       <c r="G28" s="90"/>
       <c r="H28" s="14"/>
@@ -6187,151 +6271,145 @@
       <c r="DP28"/>
       <c r="DQ28"/>
     </row>
-    <row r="29" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="40"/>
-      <c r="B29" s="155" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="15">
-        <v>0</v>
-      </c>
-      <c r="E29" s="64">
-        <v>45926</v>
-      </c>
-      <c r="F29" s="64">
-        <v>45929</v>
-      </c>
-      <c r="G29" s="90"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
-      <c r="M29" s="26"/>
-      <c r="N29" s="26"/>
-      <c r="O29" s="26"/>
-      <c r="P29" s="26"/>
-      <c r="Q29" s="26"/>
-      <c r="R29" s="26"/>
-      <c r="S29" s="26"/>
-      <c r="T29" s="26"/>
-      <c r="U29" s="26"/>
-      <c r="V29" s="26"/>
-      <c r="W29" s="26"/>
-      <c r="X29" s="26"/>
-      <c r="Y29" s="26"/>
-      <c r="Z29" s="26"/>
-      <c r="AA29" s="26"/>
-      <c r="AB29" s="26"/>
-      <c r="AC29" s="97"/>
-      <c r="AD29" s="97"/>
-      <c r="AE29" s="26"/>
-      <c r="AF29" s="26"/>
-      <c r="AG29" s="26"/>
-      <c r="AH29" s="26"/>
-      <c r="AI29" s="26"/>
-      <c r="AJ29" s="26"/>
-      <c r="AK29" s="26"/>
-      <c r="AL29" s="26"/>
-      <c r="AM29" s="26"/>
-      <c r="AN29" s="26"/>
-      <c r="AO29" s="26"/>
-      <c r="AP29" s="26"/>
-      <c r="AQ29" s="26"/>
-      <c r="AR29" s="26"/>
-      <c r="AS29" s="26"/>
-      <c r="AT29" s="26"/>
-      <c r="AU29" s="26"/>
-      <c r="AV29" s="26"/>
-      <c r="AW29" s="26"/>
-      <c r="AX29" s="26"/>
-      <c r="AY29" s="26"/>
-      <c r="AZ29" s="26"/>
-      <c r="BA29" s="26"/>
-      <c r="BB29" s="26"/>
-      <c r="BC29" s="26"/>
-      <c r="BD29" s="26"/>
-      <c r="BE29" s="26"/>
-      <c r="BF29" s="26"/>
-      <c r="BG29" s="26"/>
-      <c r="BH29" s="26"/>
-      <c r="BI29" s="26"/>
-      <c r="BJ29" s="26"/>
-      <c r="BK29" s="26"/>
-      <c r="BL29" s="26"/>
-      <c r="BM29" s="26"/>
-      <c r="BN29" s="26"/>
-      <c r="BO29" s="26"/>
-      <c r="BP29" s="26"/>
-      <c r="BQ29" s="67"/>
-      <c r="BR29" s="67"/>
-      <c r="BS29" s="67"/>
-      <c r="BT29" s="67"/>
-      <c r="BU29" s="67"/>
-      <c r="BV29" s="67"/>
-      <c r="BW29" s="67"/>
-      <c r="BX29" s="67"/>
-      <c r="BY29" s="67"/>
-      <c r="BZ29" s="67"/>
-      <c r="CA29" s="67"/>
-      <c r="CB29" s="67"/>
-      <c r="CC29" s="67"/>
-      <c r="CD29" s="67"/>
-      <c r="CE29" s="67"/>
-      <c r="CF29" s="67"/>
-      <c r="CG29" s="67"/>
-      <c r="CH29"/>
-      <c r="CI29"/>
-      <c r="CJ29"/>
-      <c r="CK29"/>
-      <c r="CL29"/>
-      <c r="CM29"/>
-      <c r="CN29"/>
-      <c r="CO29"/>
-      <c r="CP29"/>
-      <c r="CQ29"/>
-      <c r="CR29"/>
-      <c r="CS29"/>
-      <c r="CT29"/>
-      <c r="CU29"/>
-      <c r="CV29"/>
-      <c r="CW29"/>
-      <c r="CX29"/>
-      <c r="CY29"/>
-      <c r="CZ29"/>
-      <c r="DA29"/>
-      <c r="DB29"/>
-      <c r="DC29"/>
-      <c r="DD29"/>
-      <c r="DE29"/>
-      <c r="DF29"/>
-      <c r="DG29"/>
-      <c r="DH29"/>
-      <c r="DI29"/>
-      <c r="DJ29"/>
-      <c r="DK29"/>
-      <c r="DL29"/>
-      <c r="DM29"/>
-      <c r="DN29"/>
-      <c r="DO29"/>
-      <c r="DP29"/>
-      <c r="DQ29"/>
+    <row r="29" spans="1:121" s="111" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="120"/>
+      <c r="B29" s="134" t="s">
+        <v>45</v>
+      </c>
+      <c r="C29" s="121"/>
+      <c r="D29" s="106"/>
+      <c r="E29" s="107"/>
+      <c r="F29" s="107"/>
+      <c r="G29" s="108"/>
+      <c r="H29" s="108"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="109"/>
+      <c r="O29" s="109"/>
+      <c r="P29" s="109"/>
+      <c r="Q29" s="109"/>
+      <c r="R29" s="109"/>
+      <c r="S29" s="109"/>
+      <c r="T29" s="109"/>
+      <c r="U29" s="109"/>
+      <c r="V29" s="109"/>
+      <c r="W29" s="109"/>
+      <c r="X29" s="109"/>
+      <c r="Y29" s="109"/>
+      <c r="Z29" s="109"/>
+      <c r="AA29" s="109"/>
+      <c r="AB29" s="109"/>
+      <c r="AC29" s="109"/>
+      <c r="AD29" s="109"/>
+      <c r="AE29" s="109"/>
+      <c r="AF29" s="109"/>
+      <c r="AG29" s="109"/>
+      <c r="AH29" s="109"/>
+      <c r="AI29" s="109"/>
+      <c r="AJ29" s="109"/>
+      <c r="AK29" s="109"/>
+      <c r="AL29" s="109"/>
+      <c r="AM29" s="109"/>
+      <c r="AN29" s="109"/>
+      <c r="AO29" s="109"/>
+      <c r="AP29" s="109"/>
+      <c r="AQ29" s="109"/>
+      <c r="AR29" s="109"/>
+      <c r="AS29" s="109"/>
+      <c r="AT29" s="109"/>
+      <c r="AU29" s="109"/>
+      <c r="AV29" s="109"/>
+      <c r="AW29" s="109"/>
+      <c r="AX29" s="109"/>
+      <c r="AY29" s="109"/>
+      <c r="AZ29" s="109"/>
+      <c r="BA29" s="109"/>
+      <c r="BB29" s="109"/>
+      <c r="BC29" s="109"/>
+      <c r="BD29" s="109"/>
+      <c r="BE29" s="109"/>
+      <c r="BF29" s="109"/>
+      <c r="BG29" s="109"/>
+      <c r="BH29" s="109"/>
+      <c r="BI29" s="109"/>
+      <c r="BJ29" s="109"/>
+      <c r="BK29" s="109"/>
+      <c r="BL29" s="109"/>
+      <c r="BM29" s="109"/>
+      <c r="BN29" s="109"/>
+      <c r="BO29" s="109"/>
+      <c r="BP29" s="109"/>
+      <c r="BQ29" s="109"/>
+      <c r="BR29" s="109"/>
+      <c r="BS29" s="109"/>
+      <c r="BT29" s="109"/>
+      <c r="BU29" s="109"/>
+      <c r="BV29" s="109"/>
+      <c r="BW29" s="109"/>
+      <c r="BX29" s="109"/>
+      <c r="BY29" s="109"/>
+      <c r="BZ29" s="109"/>
+      <c r="CA29" s="109"/>
+      <c r="CB29" s="109"/>
+      <c r="CC29" s="109"/>
+      <c r="CD29" s="109"/>
+      <c r="CE29" s="109"/>
+      <c r="CF29" s="109"/>
+      <c r="CG29" s="109"/>
+      <c r="CH29" s="110"/>
+      <c r="CI29" s="110"/>
+      <c r="CJ29" s="110"/>
+      <c r="CK29" s="110"/>
+      <c r="CL29" s="110"/>
+      <c r="CM29" s="110"/>
+      <c r="CN29" s="110"/>
+      <c r="CO29" s="110"/>
+      <c r="CP29" s="110"/>
+      <c r="CQ29" s="110"/>
+      <c r="CR29" s="110"/>
+      <c r="CS29" s="110"/>
+      <c r="CT29" s="110"/>
+      <c r="CU29" s="110"/>
+      <c r="CV29" s="110"/>
+      <c r="CW29" s="110"/>
+      <c r="CX29" s="110"/>
+      <c r="CY29" s="110"/>
+      <c r="CZ29" s="110"/>
+      <c r="DA29" s="110"/>
+      <c r="DB29" s="110"/>
+      <c r="DC29" s="110"/>
+      <c r="DD29" s="110"/>
+      <c r="DE29" s="110"/>
+      <c r="DF29" s="110"/>
+      <c r="DG29" s="110"/>
+      <c r="DH29" s="110"/>
+      <c r="DI29" s="110"/>
+      <c r="DJ29" s="110"/>
+      <c r="DK29" s="110"/>
+      <c r="DL29" s="110"/>
+      <c r="DM29" s="110"/>
+      <c r="DN29" s="110"/>
+      <c r="DO29" s="110"/>
+      <c r="DP29" s="110"/>
+      <c r="DQ29" s="110"/>
     </row>
     <row r="30" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="40"/>
-      <c r="B30" s="153" t="s">
-        <v>99</v>
+      <c r="B30" s="133" t="s">
+        <v>81</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="15">
         <v>0</v>
       </c>
       <c r="E30" s="64">
-        <v>45929</v>
+        <v>45923</v>
       </c>
       <c r="F30" s="64">
-        <v>45930</v>
+        <v>45925</v>
       </c>
       <c r="G30" s="90"/>
       <c r="H30" s="14"/>
@@ -6450,98 +6528,99 @@
       <c r="DQ30"/>
     </row>
     <row r="31" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="47"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I31" s="110"/>
-      <c r="J31" s="111"/>
-      <c r="K31" s="111"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="111"/>
-      <c r="N31" s="111"/>
-      <c r="O31" s="111"/>
-      <c r="P31" s="111"/>
-      <c r="Q31" s="111"/>
-      <c r="R31" s="111"/>
-      <c r="S31" s="111"/>
-      <c r="T31" s="111"/>
-      <c r="U31" s="111"/>
-      <c r="V31" s="111"/>
-      <c r="W31" s="111"/>
-      <c r="X31" s="111"/>
-      <c r="Y31" s="111"/>
-      <c r="Z31" s="111"/>
-      <c r="AA31" s="111"/>
-      <c r="AB31" s="111"/>
-      <c r="AC31" s="111"/>
-      <c r="AD31" s="111"/>
-      <c r="AE31" s="111"/>
-      <c r="AF31" s="111"/>
-      <c r="AG31" s="111"/>
-      <c r="AH31" s="111"/>
-      <c r="AI31" s="111"/>
-      <c r="AJ31" s="111"/>
-      <c r="AK31" s="111"/>
-      <c r="AL31" s="111"/>
-      <c r="AM31" s="111"/>
-      <c r="AN31" s="111"/>
-      <c r="AO31" s="111"/>
-      <c r="AP31" s="111"/>
-      <c r="AQ31" s="111"/>
-      <c r="AR31" s="111"/>
-      <c r="AS31" s="111"/>
-      <c r="AT31" s="111"/>
-      <c r="AU31" s="111"/>
-      <c r="AV31" s="111"/>
-      <c r="AW31" s="111"/>
-      <c r="AX31" s="111"/>
-      <c r="AY31" s="111"/>
-      <c r="AZ31" s="111"/>
-      <c r="BA31" s="111"/>
-      <c r="BB31" s="111"/>
-      <c r="BC31" s="111"/>
-      <c r="BD31" s="111"/>
-      <c r="BE31" s="111"/>
-      <c r="BF31" s="111"/>
-      <c r="BG31" s="111"/>
-      <c r="BH31" s="111"/>
-      <c r="BI31" s="111"/>
-      <c r="BJ31" s="111"/>
-      <c r="BK31" s="111"/>
-      <c r="BL31" s="111"/>
-      <c r="BM31" s="111"/>
-      <c r="BN31" s="111"/>
-      <c r="BO31" s="111"/>
-      <c r="BP31" s="111"/>
-      <c r="BQ31" s="111"/>
-      <c r="BR31" s="111"/>
-      <c r="BS31" s="111"/>
-      <c r="BT31" s="111"/>
-      <c r="BU31" s="111"/>
-      <c r="BV31" s="111"/>
-      <c r="BW31" s="111"/>
-      <c r="BX31" s="111"/>
-      <c r="BY31" s="111"/>
-      <c r="BZ31" s="111"/>
-      <c r="CA31" s="111"/>
-      <c r="CB31" s="111"/>
-      <c r="CC31" s="111"/>
-      <c r="CD31" s="111"/>
-      <c r="CE31" s="111"/>
-      <c r="CF31" s="111"/>
-      <c r="CG31" s="112"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="133" t="s">
+        <v>73</v>
+      </c>
+      <c r="C31" s="72"/>
+      <c r="D31" s="15">
+        <v>0</v>
+      </c>
+      <c r="E31" s="64">
+        <v>45924</v>
+      </c>
+      <c r="F31" s="64">
+        <v>45924</v>
+      </c>
+      <c r="G31" s="90"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="26"/>
+      <c r="X31" s="26"/>
+      <c r="Y31" s="26"/>
+      <c r="Z31" s="26"/>
+      <c r="AA31" s="26"/>
+      <c r="AB31" s="26"/>
+      <c r="AC31" s="97"/>
+      <c r="AD31" s="97"/>
+      <c r="AE31" s="26"/>
+      <c r="AF31" s="26"/>
+      <c r="AG31" s="26"/>
+      <c r="AH31" s="26"/>
+      <c r="AI31" s="26"/>
+      <c r="AJ31" s="26"/>
+      <c r="AK31" s="26"/>
+      <c r="AL31" s="26"/>
+      <c r="AM31" s="26"/>
+      <c r="AN31" s="26"/>
+      <c r="AO31" s="26"/>
+      <c r="AP31" s="26"/>
+      <c r="AQ31" s="26"/>
+      <c r="AR31" s="26"/>
+      <c r="AS31" s="26"/>
+      <c r="AT31" s="26"/>
+      <c r="AU31" s="26"/>
+      <c r="AV31" s="26"/>
+      <c r="AW31" s="26"/>
+      <c r="AX31" s="26"/>
+      <c r="AY31" s="26"/>
+      <c r="AZ31" s="26"/>
+      <c r="BA31" s="26"/>
+      <c r="BB31" s="26"/>
+      <c r="BC31" s="26"/>
+      <c r="BD31" s="26"/>
+      <c r="BE31" s="26"/>
+      <c r="BF31" s="26"/>
+      <c r="BG31" s="26"/>
+      <c r="BH31" s="26"/>
+      <c r="BI31" s="26"/>
+      <c r="BJ31" s="26"/>
+      <c r="BK31" s="26"/>
+      <c r="BL31" s="26"/>
+      <c r="BM31" s="26"/>
+      <c r="BN31" s="26"/>
+      <c r="BO31" s="26"/>
+      <c r="BP31" s="26"/>
+      <c r="BQ31" s="67"/>
+      <c r="BR31" s="67"/>
+      <c r="BS31" s="67"/>
+      <c r="BT31" s="67"/>
+      <c r="BU31" s="67"/>
+      <c r="BV31" s="67"/>
+      <c r="BW31" s="67"/>
+      <c r="BX31" s="67"/>
+      <c r="BY31" s="67"/>
+      <c r="BZ31" s="67"/>
+      <c r="CA31" s="67"/>
+      <c r="CB31" s="67"/>
+      <c r="CC31" s="67"/>
+      <c r="CD31" s="67"/>
+      <c r="CE31" s="67"/>
+      <c r="CF31" s="67"/>
+      <c r="CG31" s="67"/>
       <c r="CH31"/>
       <c r="CI31"/>
       <c r="CJ31"/>
@@ -6579,277 +6658,284 @@
       <c r="DP31"/>
       <c r="DQ31"/>
     </row>
-    <row r="32" spans="1:121" s="99" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="100"/>
-      <c r="B32" s="140" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="48"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="141"/>
-      <c r="F32" s="142"/>
-      <c r="G32" s="92"/>
-      <c r="H32" s="143"/>
-      <c r="I32" s="144"/>
-      <c r="J32" s="145"/>
-      <c r="K32" s="145"/>
-      <c r="L32" s="145"/>
-      <c r="M32" s="145"/>
-      <c r="N32" s="145"/>
-      <c r="O32" s="145"/>
-      <c r="P32" s="145"/>
-      <c r="Q32" s="145"/>
-      <c r="R32" s="145"/>
-      <c r="S32" s="145"/>
-      <c r="T32" s="145"/>
-      <c r="U32" s="145"/>
-      <c r="V32" s="145"/>
-      <c r="W32" s="145"/>
-      <c r="X32" s="145"/>
-      <c r="Y32" s="145"/>
-      <c r="Z32" s="145"/>
-      <c r="AA32" s="145"/>
-      <c r="AB32" s="145"/>
-      <c r="AC32" s="145"/>
-      <c r="AD32" s="145"/>
-      <c r="AE32" s="145"/>
-      <c r="AF32" s="145"/>
-      <c r="AG32" s="145"/>
-      <c r="AH32" s="145"/>
-      <c r="AI32" s="145"/>
-      <c r="AJ32" s="145"/>
-      <c r="AK32" s="145"/>
-      <c r="AL32" s="145"/>
-      <c r="AM32" s="145"/>
-      <c r="AN32" s="145"/>
-      <c r="AO32" s="145"/>
-      <c r="AP32" s="145"/>
-      <c r="AQ32" s="145"/>
-      <c r="AR32" s="145"/>
-      <c r="AS32" s="145"/>
-      <c r="AT32" s="145"/>
-      <c r="AU32" s="145"/>
-      <c r="AV32" s="145"/>
-      <c r="AW32" s="145"/>
-      <c r="AX32" s="145"/>
-      <c r="AY32" s="145"/>
-      <c r="AZ32" s="145"/>
-      <c r="BA32" s="145"/>
-      <c r="BB32" s="145"/>
-      <c r="BC32" s="145"/>
-      <c r="BD32" s="145"/>
-      <c r="BE32" s="145"/>
-      <c r="BF32" s="145"/>
-      <c r="BG32" s="145"/>
-      <c r="BH32" s="145"/>
-      <c r="BI32" s="145"/>
-      <c r="BJ32" s="145"/>
-      <c r="BK32" s="145"/>
-      <c r="BL32" s="145"/>
-      <c r="BM32" s="145"/>
-      <c r="BN32" s="145"/>
-      <c r="BO32" s="145"/>
-      <c r="BP32" s="145"/>
-      <c r="BQ32" s="145"/>
-      <c r="BR32" s="145"/>
-      <c r="BS32" s="145"/>
-      <c r="BT32" s="145"/>
-      <c r="BU32" s="145"/>
-      <c r="BV32" s="145"/>
-      <c r="BW32" s="145"/>
-      <c r="BX32" s="145"/>
-      <c r="BY32" s="145"/>
-      <c r="BZ32" s="145"/>
-      <c r="CA32" s="145"/>
-      <c r="CB32" s="145"/>
-      <c r="CC32" s="145"/>
-      <c r="CD32" s="145"/>
-      <c r="CE32" s="145"/>
-      <c r="CF32" s="145"/>
-      <c r="CG32" s="146"/>
-      <c r="CH32" s="98"/>
-      <c r="CI32" s="98"/>
-      <c r="CJ32" s="98"/>
-      <c r="CK32" s="98"/>
-      <c r="CL32" s="98"/>
-      <c r="CM32" s="98"/>
-      <c r="CN32" s="98"/>
-      <c r="CO32" s="98"/>
-      <c r="CP32" s="98"/>
-      <c r="CQ32" s="98"/>
-      <c r="CR32" s="98"/>
-      <c r="CS32" s="98"/>
-      <c r="CT32" s="98"/>
-      <c r="CU32" s="98"/>
-      <c r="CV32" s="98"/>
-      <c r="CW32" s="98"/>
-      <c r="CX32" s="98"/>
-      <c r="CY32" s="98"/>
-      <c r="CZ32" s="98"/>
-      <c r="DA32" s="98"/>
-      <c r="DB32" s="98"/>
-      <c r="DC32" s="98"/>
-      <c r="DD32" s="98"/>
-      <c r="DE32" s="98"/>
-      <c r="DF32" s="98"/>
-      <c r="DG32" s="98"/>
-      <c r="DH32" s="98"/>
-      <c r="DI32" s="98"/>
-      <c r="DJ32" s="98"/>
-      <c r="DK32" s="98"/>
-      <c r="DL32" s="98"/>
-      <c r="DM32" s="98"/>
-      <c r="DN32" s="98"/>
-      <c r="DO32" s="98"/>
-      <c r="DP32" s="98"/>
-      <c r="DQ32" s="98"/>
-    </row>
-    <row r="33" spans="1:121" s="118" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="100"/>
-      <c r="B33" s="73" t="s">
-        <v>67</v>
-      </c>
-      <c r="C33" s="48"/>
-      <c r="D33" s="18">
+    <row r="32" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="40"/>
+      <c r="B32" s="133" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" s="72"/>
+      <c r="D32" s="15">
         <v>0</v>
       </c>
-      <c r="E33" s="65"/>
-      <c r="F33" s="65"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="92" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I33" s="116"/>
-      <c r="J33" s="116"/>
-      <c r="K33" s="116"/>
-      <c r="L33" s="116"/>
-      <c r="M33" s="116"/>
-      <c r="N33" s="116"/>
-      <c r="O33" s="116"/>
-      <c r="P33" s="116"/>
-      <c r="Q33" s="116"/>
-      <c r="R33" s="116"/>
-      <c r="S33" s="116"/>
-      <c r="T33" s="116"/>
-      <c r="U33" s="116"/>
-      <c r="V33" s="116"/>
-      <c r="W33" s="116"/>
-      <c r="X33" s="116"/>
-      <c r="Y33" s="116"/>
-      <c r="Z33" s="116"/>
-      <c r="AA33" s="116"/>
-      <c r="AB33" s="116"/>
-      <c r="AC33" s="116"/>
-      <c r="AD33" s="116"/>
-      <c r="AE33" s="116"/>
-      <c r="AF33" s="116"/>
-      <c r="AG33" s="116"/>
-      <c r="AH33" s="116"/>
-      <c r="AI33" s="116"/>
-      <c r="AJ33" s="116"/>
-      <c r="AK33" s="116"/>
-      <c r="AL33" s="116"/>
-      <c r="AM33" s="116"/>
-      <c r="AN33" s="116"/>
-      <c r="AO33" s="116"/>
-      <c r="AP33" s="116"/>
-      <c r="AQ33" s="116"/>
-      <c r="AR33" s="116"/>
-      <c r="AS33" s="116"/>
-      <c r="AT33" s="116"/>
-      <c r="AU33" s="116"/>
-      <c r="AV33" s="116"/>
-      <c r="AW33" s="116"/>
-      <c r="AX33" s="116"/>
-      <c r="AY33" s="116"/>
-      <c r="AZ33" s="116"/>
-      <c r="BA33" s="116"/>
-      <c r="BB33" s="116"/>
-      <c r="BC33" s="116"/>
-      <c r="BD33" s="116"/>
-      <c r="BE33" s="116"/>
-      <c r="BF33" s="116"/>
-      <c r="BG33" s="116"/>
-      <c r="BH33" s="116"/>
-      <c r="BI33" s="116"/>
-      <c r="BJ33" s="116"/>
-      <c r="BK33" s="116"/>
-      <c r="BL33" s="116"/>
-      <c r="BM33" s="116"/>
-      <c r="BN33" s="116"/>
-      <c r="BO33" s="116"/>
-      <c r="BP33" s="116"/>
-      <c r="BQ33" s="116"/>
-      <c r="BR33" s="116"/>
-      <c r="BS33" s="116"/>
-      <c r="BT33" s="116"/>
-      <c r="BU33" s="116"/>
-      <c r="BV33" s="116"/>
-      <c r="BW33" s="116"/>
-      <c r="BX33" s="116"/>
-      <c r="BY33" s="116"/>
-      <c r="BZ33" s="116"/>
-      <c r="CA33" s="116"/>
-      <c r="CB33" s="116"/>
-      <c r="CC33" s="116"/>
-      <c r="CD33" s="116"/>
-      <c r="CE33" s="116"/>
-      <c r="CF33" s="116"/>
-      <c r="CG33" s="116"/>
-      <c r="CH33" s="117"/>
-      <c r="CI33" s="117"/>
-      <c r="CJ33" s="117"/>
-      <c r="CK33" s="117"/>
-      <c r="CL33" s="117"/>
-      <c r="CM33" s="117"/>
-      <c r="CN33" s="117"/>
-      <c r="CO33" s="117"/>
-      <c r="CP33" s="117"/>
-      <c r="CQ33" s="117"/>
-      <c r="CR33" s="117"/>
-      <c r="CS33" s="117"/>
-      <c r="CT33" s="117"/>
-      <c r="CU33" s="117"/>
-      <c r="CV33" s="117"/>
-      <c r="CW33" s="117"/>
-      <c r="CX33" s="117"/>
-      <c r="CY33" s="117"/>
-      <c r="CZ33" s="117"/>
-      <c r="DA33" s="117"/>
-      <c r="DB33" s="117"/>
-      <c r="DC33" s="117"/>
-      <c r="DD33" s="117"/>
-      <c r="DE33" s="117"/>
-      <c r="DF33" s="117"/>
-      <c r="DG33" s="117"/>
-      <c r="DH33" s="117"/>
-      <c r="DI33" s="117"/>
-      <c r="DJ33" s="117"/>
-      <c r="DK33" s="117"/>
-      <c r="DL33" s="117"/>
-      <c r="DM33" s="117"/>
-      <c r="DN33" s="117"/>
-      <c r="DO33" s="117"/>
-      <c r="DP33" s="117"/>
-      <c r="DQ33" s="117"/>
+      <c r="E32" s="64">
+        <v>45925</v>
+      </c>
+      <c r="F32" s="64">
+        <v>45926</v>
+      </c>
+      <c r="G32" s="90"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="26"/>
+      <c r="V32" s="26"/>
+      <c r="W32" s="26"/>
+      <c r="X32" s="26"/>
+      <c r="Y32" s="26"/>
+      <c r="Z32" s="26"/>
+      <c r="AA32" s="26"/>
+      <c r="AB32" s="26"/>
+      <c r="AC32" s="97"/>
+      <c r="AD32" s="97"/>
+      <c r="AE32" s="26"/>
+      <c r="AF32" s="26"/>
+      <c r="AG32" s="26"/>
+      <c r="AH32" s="26"/>
+      <c r="AI32" s="26"/>
+      <c r="AJ32" s="26"/>
+      <c r="AK32" s="26"/>
+      <c r="AL32" s="26"/>
+      <c r="AM32" s="26"/>
+      <c r="AN32" s="26"/>
+      <c r="AO32" s="26"/>
+      <c r="AP32" s="26"/>
+      <c r="AQ32" s="26"/>
+      <c r="AR32" s="26"/>
+      <c r="AS32" s="26"/>
+      <c r="AT32" s="26"/>
+      <c r="AU32" s="26"/>
+      <c r="AV32" s="26"/>
+      <c r="AW32" s="26"/>
+      <c r="AX32" s="26"/>
+      <c r="AY32" s="26"/>
+      <c r="AZ32" s="26"/>
+      <c r="BA32" s="26"/>
+      <c r="BB32" s="26"/>
+      <c r="BC32" s="26"/>
+      <c r="BD32" s="26"/>
+      <c r="BE32" s="26"/>
+      <c r="BF32" s="26"/>
+      <c r="BG32" s="26"/>
+      <c r="BH32" s="26"/>
+      <c r="BI32" s="26"/>
+      <c r="BJ32" s="26"/>
+      <c r="BK32" s="26"/>
+      <c r="BL32" s="26"/>
+      <c r="BM32" s="26"/>
+      <c r="BN32" s="26"/>
+      <c r="BO32" s="26"/>
+      <c r="BP32" s="26"/>
+      <c r="BQ32" s="67"/>
+      <c r="BR32" s="67"/>
+      <c r="BS32" s="67"/>
+      <c r="BT32" s="67"/>
+      <c r="BU32" s="67"/>
+      <c r="BV32" s="67"/>
+      <c r="BW32" s="67"/>
+      <c r="BX32" s="67"/>
+      <c r="BY32" s="67"/>
+      <c r="BZ32" s="67"/>
+      <c r="CA32" s="67"/>
+      <c r="CB32" s="67"/>
+      <c r="CC32" s="67"/>
+      <c r="CD32" s="67"/>
+      <c r="CE32" s="67"/>
+      <c r="CF32" s="67"/>
+      <c r="CG32" s="67"/>
+      <c r="CH32"/>
+      <c r="CI32"/>
+      <c r="CJ32"/>
+      <c r="CK32"/>
+      <c r="CL32"/>
+      <c r="CM32"/>
+      <c r="CN32"/>
+      <c r="CO32"/>
+      <c r="CP32"/>
+      <c r="CQ32"/>
+      <c r="CR32"/>
+      <c r="CS32"/>
+      <c r="CT32"/>
+      <c r="CU32"/>
+      <c r="CV32"/>
+      <c r="CW32"/>
+      <c r="CX32"/>
+      <c r="CY32"/>
+      <c r="CZ32"/>
+      <c r="DA32"/>
+      <c r="DB32"/>
+      <c r="DC32"/>
+      <c r="DD32"/>
+      <c r="DE32"/>
+      <c r="DF32"/>
+      <c r="DG32"/>
+      <c r="DH32"/>
+      <c r="DI32"/>
+      <c r="DJ32"/>
+      <c r="DK32"/>
+      <c r="DL32"/>
+      <c r="DM32"/>
+      <c r="DN32"/>
+      <c r="DO32"/>
+      <c r="DP32"/>
+      <c r="DQ32"/>
+    </row>
+    <row r="33" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="40"/>
+      <c r="B33" s="133" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="72"/>
+      <c r="D33" s="15">
+        <v>0</v>
+      </c>
+      <c r="E33" s="64">
+        <v>45926</v>
+      </c>
+      <c r="F33" s="64">
+        <v>45926</v>
+      </c>
+      <c r="G33" s="90"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="26"/>
+      <c r="X33" s="26"/>
+      <c r="Y33" s="26"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="26"/>
+      <c r="AB33" s="26"/>
+      <c r="AC33" s="97"/>
+      <c r="AD33" s="97"/>
+      <c r="AE33" s="26"/>
+      <c r="AF33" s="26"/>
+      <c r="AG33" s="26"/>
+      <c r="AH33" s="26"/>
+      <c r="AI33" s="26"/>
+      <c r="AJ33" s="26"/>
+      <c r="AK33" s="26"/>
+      <c r="AL33" s="26"/>
+      <c r="AM33" s="26"/>
+      <c r="AN33" s="26"/>
+      <c r="AO33" s="26"/>
+      <c r="AP33" s="26"/>
+      <c r="AQ33" s="26"/>
+      <c r="AR33" s="26"/>
+      <c r="AS33" s="26"/>
+      <c r="AT33" s="26"/>
+      <c r="AU33" s="26"/>
+      <c r="AV33" s="26"/>
+      <c r="AW33" s="26"/>
+      <c r="AX33" s="26"/>
+      <c r="AY33" s="26"/>
+      <c r="AZ33" s="26"/>
+      <c r="BA33" s="26"/>
+      <c r="BB33" s="26"/>
+      <c r="BC33" s="26"/>
+      <c r="BD33" s="26"/>
+      <c r="BE33" s="26"/>
+      <c r="BF33" s="26"/>
+      <c r="BG33" s="26"/>
+      <c r="BH33" s="26"/>
+      <c r="BI33" s="26"/>
+      <c r="BJ33" s="26"/>
+      <c r="BK33" s="26"/>
+      <c r="BL33" s="26"/>
+      <c r="BM33" s="26"/>
+      <c r="BN33" s="26"/>
+      <c r="BO33" s="26"/>
+      <c r="BP33" s="26"/>
+      <c r="BQ33" s="67"/>
+      <c r="BR33" s="67"/>
+      <c r="BS33" s="67"/>
+      <c r="BT33" s="67"/>
+      <c r="BU33" s="67"/>
+      <c r="BV33" s="67"/>
+      <c r="BW33" s="67"/>
+      <c r="BX33" s="67"/>
+      <c r="BY33" s="67"/>
+      <c r="BZ33" s="67"/>
+      <c r="CA33" s="67"/>
+      <c r="CB33" s="67"/>
+      <c r="CC33" s="67"/>
+      <c r="CD33" s="67"/>
+      <c r="CE33" s="67"/>
+      <c r="CF33" s="67"/>
+      <c r="CG33" s="67"/>
+      <c r="CH33"/>
+      <c r="CI33"/>
+      <c r="CJ33"/>
+      <c r="CK33"/>
+      <c r="CL33"/>
+      <c r="CM33"/>
+      <c r="CN33"/>
+      <c r="CO33"/>
+      <c r="CP33"/>
+      <c r="CQ33"/>
+      <c r="CR33"/>
+      <c r="CS33"/>
+      <c r="CT33"/>
+      <c r="CU33"/>
+      <c r="CV33"/>
+      <c r="CW33"/>
+      <c r="CX33"/>
+      <c r="CY33"/>
+      <c r="CZ33"/>
+      <c r="DA33"/>
+      <c r="DB33"/>
+      <c r="DC33"/>
+      <c r="DD33"/>
+      <c r="DE33"/>
+      <c r="DF33"/>
+      <c r="DG33"/>
+      <c r="DH33"/>
+      <c r="DI33"/>
+      <c r="DJ33"/>
+      <c r="DK33"/>
+      <c r="DL33"/>
+      <c r="DM33"/>
+      <c r="DN33"/>
+      <c r="DO33"/>
+      <c r="DP33"/>
+      <c r="DQ33"/>
     </row>
     <row r="34" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="41"/>
-      <c r="B34" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="18">
+      <c r="A34" s="40"/>
+      <c r="B34" s="137" t="s">
+        <v>101</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="15">
         <v>0</v>
       </c>
-      <c r="E34" s="65">
-        <v>45931</v>
-      </c>
-      <c r="F34" s="65">
-        <v>45937</v>
-      </c>
-      <c r="G34" s="92"/>
+      <c r="E34" s="64">
+        <v>45926</v>
+      </c>
+      <c r="F34" s="64">
+        <v>45929</v>
+      </c>
+      <c r="G34" s="90"/>
       <c r="H34" s="14"/>
       <c r="I34" s="26"/>
       <c r="J34" s="26"/>
@@ -6966,21 +7052,21 @@
       <c r="DQ34"/>
     </row>
     <row r="35" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="41"/>
-      <c r="B35" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C35" s="48"/>
-      <c r="D35" s="18">
+      <c r="A35" s="40"/>
+      <c r="B35" s="135" t="s">
+        <v>102</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="15">
         <v>0</v>
       </c>
-      <c r="E35" s="65">
-        <v>45933</v>
-      </c>
-      <c r="F35" s="65">
-        <v>45937</v>
-      </c>
-      <c r="G35" s="92"/>
+      <c r="E35" s="64">
+        <v>45929</v>
+      </c>
+      <c r="F35" s="64">
+        <v>45930</v>
+      </c>
+      <c r="G35" s="90"/>
       <c r="H35" s="14"/>
       <c r="I35" s="26"/>
       <c r="J35" s="26"/>
@@ -7097,99 +7183,98 @@
       <c r="DQ35"/>
     </row>
     <row r="36" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="41"/>
-      <c r="B36" s="52" t="s">
-        <v>70</v>
-      </c>
-      <c r="C36" s="48"/>
-      <c r="D36" s="18">
-        <v>0</v>
-      </c>
-      <c r="E36" s="65">
-        <v>45937</v>
-      </c>
-      <c r="F36" s="65">
-        <v>45937</v>
-      </c>
-      <c r="G36" s="92"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
-      <c r="M36" s="26"/>
-      <c r="N36" s="26"/>
-      <c r="O36" s="26"/>
-      <c r="P36" s="26"/>
-      <c r="Q36" s="26"/>
-      <c r="R36" s="26"/>
-      <c r="S36" s="26"/>
-      <c r="T36" s="26"/>
-      <c r="U36" s="26"/>
-      <c r="V36" s="26"/>
-      <c r="W36" s="26"/>
-      <c r="X36" s="26"/>
-      <c r="Y36" s="26"/>
-      <c r="Z36" s="26"/>
-      <c r="AA36" s="26"/>
-      <c r="AB36" s="26"/>
-      <c r="AC36" s="97"/>
-      <c r="AD36" s="97"/>
-      <c r="AE36" s="26"/>
-      <c r="AF36" s="26"/>
-      <c r="AG36" s="26"/>
-      <c r="AH36" s="26"/>
-      <c r="AI36" s="26"/>
-      <c r="AJ36" s="26"/>
-      <c r="AK36" s="26"/>
-      <c r="AL36" s="26"/>
-      <c r="AM36" s="26"/>
-      <c r="AN36" s="26"/>
-      <c r="AO36" s="26"/>
-      <c r="AP36" s="26"/>
-      <c r="AQ36" s="26"/>
-      <c r="AR36" s="26"/>
-      <c r="AS36" s="26"/>
-      <c r="AT36" s="26"/>
-      <c r="AU36" s="26"/>
-      <c r="AV36" s="26"/>
-      <c r="AW36" s="26"/>
-      <c r="AX36" s="26"/>
-      <c r="AY36" s="26"/>
-      <c r="AZ36" s="26"/>
-      <c r="BA36" s="26"/>
-      <c r="BB36" s="26"/>
-      <c r="BC36" s="26"/>
-      <c r="BD36" s="26"/>
-      <c r="BE36" s="26"/>
-      <c r="BF36" s="26"/>
-      <c r="BG36" s="26"/>
-      <c r="BH36" s="26"/>
-      <c r="BI36" s="26"/>
-      <c r="BJ36" s="26"/>
-      <c r="BK36" s="26"/>
-      <c r="BL36" s="26"/>
-      <c r="BM36" s="26"/>
-      <c r="BN36" s="26"/>
-      <c r="BO36" s="26"/>
-      <c r="BP36" s="26"/>
-      <c r="BQ36" s="67"/>
-      <c r="BR36" s="67"/>
-      <c r="BS36" s="67"/>
-      <c r="BT36" s="67"/>
-      <c r="BU36" s="67"/>
-      <c r="BV36" s="67"/>
-      <c r="BW36" s="67"/>
-      <c r="BX36" s="67"/>
-      <c r="BY36" s="67"/>
-      <c r="BZ36" s="67"/>
-      <c r="CA36" s="67"/>
-      <c r="CB36" s="67"/>
-      <c r="CC36" s="67"/>
-      <c r="CD36" s="67"/>
-      <c r="CE36" s="67"/>
-      <c r="CF36" s="67"/>
-      <c r="CG36" s="67"/>
+      <c r="A36" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" s="47"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I36" s="141"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
+      <c r="M36" s="142"/>
+      <c r="N36" s="142"/>
+      <c r="O36" s="142"/>
+      <c r="P36" s="142"/>
+      <c r="Q36" s="142"/>
+      <c r="R36" s="142"/>
+      <c r="S36" s="142"/>
+      <c r="T36" s="142"/>
+      <c r="U36" s="142"/>
+      <c r="V36" s="142"/>
+      <c r="W36" s="142"/>
+      <c r="X36" s="142"/>
+      <c r="Y36" s="142"/>
+      <c r="Z36" s="142"/>
+      <c r="AA36" s="142"/>
+      <c r="AB36" s="142"/>
+      <c r="AC36" s="142"/>
+      <c r="AD36" s="142"/>
+      <c r="AE36" s="142"/>
+      <c r="AF36" s="142"/>
+      <c r="AG36" s="142"/>
+      <c r="AH36" s="142"/>
+      <c r="AI36" s="142"/>
+      <c r="AJ36" s="142"/>
+      <c r="AK36" s="142"/>
+      <c r="AL36" s="142"/>
+      <c r="AM36" s="142"/>
+      <c r="AN36" s="142"/>
+      <c r="AO36" s="142"/>
+      <c r="AP36" s="142"/>
+      <c r="AQ36" s="142"/>
+      <c r="AR36" s="142"/>
+      <c r="AS36" s="142"/>
+      <c r="AT36" s="142"/>
+      <c r="AU36" s="142"/>
+      <c r="AV36" s="142"/>
+      <c r="AW36" s="142"/>
+      <c r="AX36" s="142"/>
+      <c r="AY36" s="142"/>
+      <c r="AZ36" s="142"/>
+      <c r="BA36" s="142"/>
+      <c r="BB36" s="142"/>
+      <c r="BC36" s="142"/>
+      <c r="BD36" s="142"/>
+      <c r="BE36" s="142"/>
+      <c r="BF36" s="142"/>
+      <c r="BG36" s="142"/>
+      <c r="BH36" s="142"/>
+      <c r="BI36" s="142"/>
+      <c r="BJ36" s="142"/>
+      <c r="BK36" s="142"/>
+      <c r="BL36" s="142"/>
+      <c r="BM36" s="142"/>
+      <c r="BN36" s="142"/>
+      <c r="BO36" s="142"/>
+      <c r="BP36" s="142"/>
+      <c r="BQ36" s="142"/>
+      <c r="BR36" s="142"/>
+      <c r="BS36" s="142"/>
+      <c r="BT36" s="142"/>
+      <c r="BU36" s="142"/>
+      <c r="BV36" s="142"/>
+      <c r="BW36" s="142"/>
+      <c r="BX36" s="142"/>
+      <c r="BY36" s="142"/>
+      <c r="BZ36" s="142"/>
+      <c r="CA36" s="142"/>
+      <c r="CB36" s="142"/>
+      <c r="CC36" s="142"/>
+      <c r="CD36" s="142"/>
+      <c r="CE36" s="142"/>
+      <c r="CF36" s="142"/>
+      <c r="CG36" s="143"/>
       <c r="CH36"/>
       <c r="CI36"/>
       <c r="CJ36"/>
@@ -7227,397 +7312,396 @@
       <c r="DP36"/>
       <c r="DQ36"/>
     </row>
-    <row r="37" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="41"/>
-      <c r="B37" s="52" t="s">
-        <v>73</v>
+    <row r="37" spans="1:121" s="99" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="100"/>
+      <c r="B37" s="122" t="s">
+        <v>82</v>
       </c>
       <c r="C37" s="48"/>
-      <c r="D37" s="18">
-        <v>0</v>
-      </c>
-      <c r="E37" s="65">
-        <v>45938</v>
-      </c>
-      <c r="F37" s="65">
-        <v>45940</v>
-      </c>
+      <c r="D37" s="18"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="124"/>
       <c r="G37" s="92"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="26"/>
-      <c r="J37" s="26"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="26"/>
-      <c r="M37" s="26"/>
-      <c r="N37" s="26"/>
-      <c r="O37" s="26"/>
-      <c r="P37" s="26"/>
-      <c r="Q37" s="26"/>
-      <c r="R37" s="26"/>
-      <c r="S37" s="26"/>
-      <c r="T37" s="26"/>
-      <c r="U37" s="26"/>
-      <c r="V37" s="26"/>
-      <c r="W37" s="26"/>
-      <c r="X37" s="26"/>
-      <c r="Y37" s="26"/>
-      <c r="Z37" s="26"/>
-      <c r="AA37" s="26"/>
-      <c r="AB37" s="26"/>
-      <c r="AC37" s="97"/>
-      <c r="AD37" s="97"/>
-      <c r="AE37" s="26"/>
-      <c r="AF37" s="26"/>
-      <c r="AG37" s="26"/>
-      <c r="AH37" s="26"/>
-      <c r="AI37" s="26"/>
-      <c r="AJ37" s="26"/>
-      <c r="AK37" s="26"/>
-      <c r="AL37" s="26"/>
-      <c r="AM37" s="26"/>
-      <c r="AN37" s="26"/>
-      <c r="AO37" s="26"/>
-      <c r="AP37" s="26"/>
-      <c r="AQ37" s="26"/>
-      <c r="AR37" s="26"/>
-      <c r="AS37" s="26"/>
-      <c r="AT37" s="26"/>
-      <c r="AU37" s="26"/>
-      <c r="AV37" s="26"/>
-      <c r="AW37" s="26"/>
-      <c r="AX37" s="26"/>
-      <c r="AY37" s="26"/>
-      <c r="AZ37" s="26"/>
-      <c r="BA37" s="26"/>
-      <c r="BB37" s="26"/>
-      <c r="BC37" s="26"/>
-      <c r="BD37" s="26"/>
-      <c r="BE37" s="26"/>
-      <c r="BF37" s="26"/>
-      <c r="BG37" s="26"/>
-      <c r="BH37" s="26"/>
-      <c r="BI37" s="26"/>
-      <c r="BJ37" s="26"/>
-      <c r="BK37" s="26"/>
-      <c r="BL37" s="26"/>
-      <c r="BM37" s="26"/>
-      <c r="BN37" s="26"/>
-      <c r="BO37" s="26"/>
-      <c r="BP37" s="26"/>
-      <c r="BQ37" s="67"/>
-      <c r="BR37" s="67"/>
-      <c r="BS37" s="67"/>
-      <c r="BT37" s="67"/>
-      <c r="BU37" s="67"/>
-      <c r="BV37" s="67"/>
-      <c r="BW37" s="67"/>
-      <c r="BX37" s="67"/>
-      <c r="BY37" s="67"/>
-      <c r="BZ37" s="67"/>
-      <c r="CA37" s="67"/>
-      <c r="CB37" s="67"/>
-      <c r="CC37" s="67"/>
-      <c r="CD37" s="67"/>
-      <c r="CE37" s="67"/>
-      <c r="CF37" s="67"/>
-      <c r="CG37" s="67"/>
-      <c r="CH37"/>
-      <c r="CI37"/>
-      <c r="CJ37"/>
-      <c r="CK37"/>
-      <c r="CL37"/>
-      <c r="CM37"/>
-      <c r="CN37"/>
-      <c r="CO37"/>
-      <c r="CP37"/>
-      <c r="CQ37"/>
-      <c r="CR37"/>
-      <c r="CS37"/>
-      <c r="CT37"/>
-      <c r="CU37"/>
-      <c r="CV37"/>
-      <c r="CW37"/>
-      <c r="CX37"/>
-      <c r="CY37"/>
-      <c r="CZ37"/>
-      <c r="DA37"/>
-      <c r="DB37"/>
-      <c r="DC37"/>
-      <c r="DD37"/>
-      <c r="DE37"/>
-      <c r="DF37"/>
-      <c r="DG37"/>
-      <c r="DH37"/>
-      <c r="DI37"/>
-      <c r="DJ37"/>
-      <c r="DK37"/>
-      <c r="DL37"/>
-      <c r="DM37"/>
-      <c r="DN37"/>
-      <c r="DO37"/>
-      <c r="DP37"/>
-      <c r="DQ37"/>
-    </row>
-    <row r="38" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="41"/>
-      <c r="B38" s="52" t="s">
-        <v>76</v>
+      <c r="H37" s="125"/>
+      <c r="I37" s="126"/>
+      <c r="J37" s="127"/>
+      <c r="K37" s="127"/>
+      <c r="L37" s="127"/>
+      <c r="M37" s="127"/>
+      <c r="N37" s="127"/>
+      <c r="O37" s="127"/>
+      <c r="P37" s="127"/>
+      <c r="Q37" s="127"/>
+      <c r="R37" s="127"/>
+      <c r="S37" s="127"/>
+      <c r="T37" s="127"/>
+      <c r="U37" s="127"/>
+      <c r="V37" s="127"/>
+      <c r="W37" s="127"/>
+      <c r="X37" s="127"/>
+      <c r="Y37" s="127"/>
+      <c r="Z37" s="127"/>
+      <c r="AA37" s="127"/>
+      <c r="AB37" s="127"/>
+      <c r="AC37" s="127"/>
+      <c r="AD37" s="127"/>
+      <c r="AE37" s="127"/>
+      <c r="AF37" s="127"/>
+      <c r="AG37" s="127"/>
+      <c r="AH37" s="127"/>
+      <c r="AI37" s="127"/>
+      <c r="AJ37" s="127"/>
+      <c r="AK37" s="127"/>
+      <c r="AL37" s="127"/>
+      <c r="AM37" s="127"/>
+      <c r="AN37" s="127"/>
+      <c r="AO37" s="127"/>
+      <c r="AP37" s="127"/>
+      <c r="AQ37" s="127"/>
+      <c r="AR37" s="127"/>
+      <c r="AS37" s="127"/>
+      <c r="AT37" s="127"/>
+      <c r="AU37" s="127"/>
+      <c r="AV37" s="127"/>
+      <c r="AW37" s="127"/>
+      <c r="AX37" s="127"/>
+      <c r="AY37" s="127"/>
+      <c r="AZ37" s="127"/>
+      <c r="BA37" s="127"/>
+      <c r="BB37" s="127"/>
+      <c r="BC37" s="127"/>
+      <c r="BD37" s="127"/>
+      <c r="BE37" s="127"/>
+      <c r="BF37" s="127"/>
+      <c r="BG37" s="127"/>
+      <c r="BH37" s="127"/>
+      <c r="BI37" s="127"/>
+      <c r="BJ37" s="127"/>
+      <c r="BK37" s="127"/>
+      <c r="BL37" s="127"/>
+      <c r="BM37" s="127"/>
+      <c r="BN37" s="127"/>
+      <c r="BO37" s="127"/>
+      <c r="BP37" s="127"/>
+      <c r="BQ37" s="127"/>
+      <c r="BR37" s="127"/>
+      <c r="BS37" s="127"/>
+      <c r="BT37" s="127"/>
+      <c r="BU37" s="127"/>
+      <c r="BV37" s="127"/>
+      <c r="BW37" s="127"/>
+      <c r="BX37" s="127"/>
+      <c r="BY37" s="127"/>
+      <c r="BZ37" s="127"/>
+      <c r="CA37" s="127"/>
+      <c r="CB37" s="127"/>
+      <c r="CC37" s="127"/>
+      <c r="CD37" s="127"/>
+      <c r="CE37" s="127"/>
+      <c r="CF37" s="127"/>
+      <c r="CG37" s="128"/>
+      <c r="CH37" s="98"/>
+      <c r="CI37" s="98"/>
+      <c r="CJ37" s="98"/>
+      <c r="CK37" s="98"/>
+      <c r="CL37" s="98"/>
+      <c r="CM37" s="98"/>
+      <c r="CN37" s="98"/>
+      <c r="CO37" s="98"/>
+      <c r="CP37" s="98"/>
+      <c r="CQ37" s="98"/>
+      <c r="CR37" s="98"/>
+      <c r="CS37" s="98"/>
+      <c r="CT37" s="98"/>
+      <c r="CU37" s="98"/>
+      <c r="CV37" s="98"/>
+      <c r="CW37" s="98"/>
+      <c r="CX37" s="98"/>
+      <c r="CY37" s="98"/>
+      <c r="CZ37" s="98"/>
+      <c r="DA37" s="98"/>
+      <c r="DB37" s="98"/>
+      <c r="DC37" s="98"/>
+      <c r="DD37" s="98"/>
+      <c r="DE37" s="98"/>
+      <c r="DF37" s="98"/>
+      <c r="DG37" s="98"/>
+      <c r="DH37" s="98"/>
+      <c r="DI37" s="98"/>
+      <c r="DJ37" s="98"/>
+      <c r="DK37" s="98"/>
+      <c r="DL37" s="98"/>
+      <c r="DM37" s="98"/>
+      <c r="DN37" s="98"/>
+      <c r="DO37" s="98"/>
+      <c r="DP37" s="98"/>
+      <c r="DQ37" s="98"/>
+    </row>
+    <row r="38" spans="1:121" s="103" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="100"/>
+      <c r="B38" s="73" t="s">
+        <v>65</v>
       </c>
       <c r="C38" s="48"/>
       <c r="D38" s="18">
         <v>0</v>
       </c>
-      <c r="E38" s="65">
-        <v>45940</v>
-      </c>
-      <c r="F38" s="65">
-        <v>45945</v>
-      </c>
+      <c r="E38" s="65"/>
+      <c r="F38" s="65"/>
       <c r="G38" s="92"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="26"/>
-      <c r="J38" s="26"/>
-      <c r="K38" s="26"/>
-      <c r="L38" s="26"/>
-      <c r="M38" s="26"/>
-      <c r="N38" s="26"/>
-      <c r="O38" s="26"/>
-      <c r="P38" s="26"/>
-      <c r="Q38" s="26"/>
-      <c r="R38" s="26"/>
-      <c r="S38" s="26"/>
-      <c r="T38" s="26"/>
-      <c r="U38" s="26"/>
-      <c r="V38" s="26"/>
-      <c r="W38" s="26"/>
-      <c r="X38" s="26"/>
-      <c r="Y38" s="26"/>
-      <c r="Z38" s="26"/>
-      <c r="AA38" s="26"/>
-      <c r="AB38" s="26"/>
-      <c r="AC38" s="97"/>
-      <c r="AD38" s="97"/>
-      <c r="AE38" s="26"/>
-      <c r="AF38" s="26"/>
-      <c r="AG38" s="26"/>
-      <c r="AH38" s="26"/>
-      <c r="AI38" s="26"/>
-      <c r="AJ38" s="26"/>
-      <c r="AK38" s="26"/>
-      <c r="AL38" s="26"/>
-      <c r="AM38" s="26"/>
-      <c r="AN38" s="26"/>
-      <c r="AO38" s="26"/>
-      <c r="AP38" s="26"/>
-      <c r="AQ38" s="26"/>
-      <c r="AR38" s="26"/>
-      <c r="AS38" s="26"/>
-      <c r="AT38" s="26"/>
-      <c r="AU38" s="26"/>
-      <c r="AV38" s="26"/>
-      <c r="AW38" s="26"/>
-      <c r="AX38" s="26"/>
-      <c r="AY38" s="26"/>
-      <c r="AZ38" s="26"/>
-      <c r="BA38" s="26"/>
-      <c r="BB38" s="26"/>
-      <c r="BC38" s="26"/>
-      <c r="BD38" s="26"/>
-      <c r="BE38" s="26"/>
-      <c r="BF38" s="26"/>
-      <c r="BG38" s="26"/>
-      <c r="BH38" s="26"/>
-      <c r="BI38" s="26"/>
-      <c r="BJ38" s="26"/>
-      <c r="BK38" s="26"/>
-      <c r="BL38" s="26"/>
-      <c r="BM38" s="26"/>
-      <c r="BN38" s="26"/>
-      <c r="BO38" s="26"/>
-      <c r="BP38" s="26"/>
-      <c r="BQ38" s="67"/>
-      <c r="BR38" s="67"/>
-      <c r="BS38" s="67"/>
-      <c r="BT38" s="67"/>
-      <c r="BU38" s="67"/>
-      <c r="BV38" s="67"/>
-      <c r="BW38" s="67"/>
-      <c r="BX38" s="67"/>
-      <c r="BY38" s="67"/>
-      <c r="BZ38" s="67"/>
-      <c r="CA38" s="67"/>
-      <c r="CB38" s="67"/>
-      <c r="CC38" s="67"/>
-      <c r="CD38" s="67"/>
-      <c r="CE38" s="67"/>
-      <c r="CF38" s="67"/>
-      <c r="CG38" s="67"/>
-      <c r="CH38"/>
-      <c r="CI38"/>
-      <c r="CJ38"/>
-      <c r="CK38"/>
-      <c r="CL38"/>
-      <c r="CM38"/>
-      <c r="CN38"/>
-      <c r="CO38"/>
-      <c r="CP38"/>
-      <c r="CQ38"/>
-      <c r="CR38"/>
-      <c r="CS38"/>
-      <c r="CT38"/>
-      <c r="CU38"/>
-      <c r="CV38"/>
-      <c r="CW38"/>
-      <c r="CX38"/>
-      <c r="CY38"/>
-      <c r="CZ38"/>
-      <c r="DA38"/>
-      <c r="DB38"/>
-      <c r="DC38"/>
-      <c r="DD38"/>
-      <c r="DE38"/>
-      <c r="DF38"/>
-      <c r="DG38"/>
-      <c r="DH38"/>
-      <c r="DI38"/>
-      <c r="DJ38"/>
-      <c r="DK38"/>
-      <c r="DL38"/>
-      <c r="DM38"/>
-      <c r="DN38"/>
-      <c r="DO38"/>
-      <c r="DP38"/>
-      <c r="DQ38"/>
-    </row>
-    <row r="39" spans="1:121" s="118" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="100"/>
-      <c r="B39" s="73" t="s">
-        <v>68</v>
+      <c r="H38" s="92" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I38" s="101"/>
+      <c r="J38" s="101"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="101"/>
+      <c r="N38" s="101"/>
+      <c r="O38" s="101"/>
+      <c r="P38" s="101"/>
+      <c r="Q38" s="101"/>
+      <c r="R38" s="101"/>
+      <c r="S38" s="101"/>
+      <c r="T38" s="101"/>
+      <c r="U38" s="101"/>
+      <c r="V38" s="101"/>
+      <c r="W38" s="101"/>
+      <c r="X38" s="101"/>
+      <c r="Y38" s="101"/>
+      <c r="Z38" s="101"/>
+      <c r="AA38" s="101"/>
+      <c r="AB38" s="101"/>
+      <c r="AC38" s="101"/>
+      <c r="AD38" s="101"/>
+      <c r="AE38" s="101"/>
+      <c r="AF38" s="101"/>
+      <c r="AG38" s="101"/>
+      <c r="AH38" s="101"/>
+      <c r="AI38" s="101"/>
+      <c r="AJ38" s="101"/>
+      <c r="AK38" s="101"/>
+      <c r="AL38" s="101"/>
+      <c r="AM38" s="101"/>
+      <c r="AN38" s="101"/>
+      <c r="AO38" s="101"/>
+      <c r="AP38" s="101"/>
+      <c r="AQ38" s="101"/>
+      <c r="AR38" s="101"/>
+      <c r="AS38" s="101"/>
+      <c r="AT38" s="101"/>
+      <c r="AU38" s="101"/>
+      <c r="AV38" s="101"/>
+      <c r="AW38" s="101"/>
+      <c r="AX38" s="101"/>
+      <c r="AY38" s="101"/>
+      <c r="AZ38" s="101"/>
+      <c r="BA38" s="101"/>
+      <c r="BB38" s="101"/>
+      <c r="BC38" s="101"/>
+      <c r="BD38" s="101"/>
+      <c r="BE38" s="101"/>
+      <c r="BF38" s="101"/>
+      <c r="BG38" s="101"/>
+      <c r="BH38" s="101"/>
+      <c r="BI38" s="101"/>
+      <c r="BJ38" s="101"/>
+      <c r="BK38" s="101"/>
+      <c r="BL38" s="101"/>
+      <c r="BM38" s="101"/>
+      <c r="BN38" s="101"/>
+      <c r="BO38" s="101"/>
+      <c r="BP38" s="101"/>
+      <c r="BQ38" s="101"/>
+      <c r="BR38" s="101"/>
+      <c r="BS38" s="101"/>
+      <c r="BT38" s="101"/>
+      <c r="BU38" s="101"/>
+      <c r="BV38" s="101"/>
+      <c r="BW38" s="101"/>
+      <c r="BX38" s="101"/>
+      <c r="BY38" s="101"/>
+      <c r="BZ38" s="101"/>
+      <c r="CA38" s="101"/>
+      <c r="CB38" s="101"/>
+      <c r="CC38" s="101"/>
+      <c r="CD38" s="101"/>
+      <c r="CE38" s="101"/>
+      <c r="CF38" s="101"/>
+      <c r="CG38" s="101"/>
+      <c r="CH38" s="102"/>
+      <c r="CI38" s="102"/>
+      <c r="CJ38" s="102"/>
+      <c r="CK38" s="102"/>
+      <c r="CL38" s="102"/>
+      <c r="CM38" s="102"/>
+      <c r="CN38" s="102"/>
+      <c r="CO38" s="102"/>
+      <c r="CP38" s="102"/>
+      <c r="CQ38" s="102"/>
+      <c r="CR38" s="102"/>
+      <c r="CS38" s="102"/>
+      <c r="CT38" s="102"/>
+      <c r="CU38" s="102"/>
+      <c r="CV38" s="102"/>
+      <c r="CW38" s="102"/>
+      <c r="CX38" s="102"/>
+      <c r="CY38" s="102"/>
+      <c r="CZ38" s="102"/>
+      <c r="DA38" s="102"/>
+      <c r="DB38" s="102"/>
+      <c r="DC38" s="102"/>
+      <c r="DD38" s="102"/>
+      <c r="DE38" s="102"/>
+      <c r="DF38" s="102"/>
+      <c r="DG38" s="102"/>
+      <c r="DH38" s="102"/>
+      <c r="DI38" s="102"/>
+      <c r="DJ38" s="102"/>
+      <c r="DK38" s="102"/>
+      <c r="DL38" s="102"/>
+      <c r="DM38" s="102"/>
+      <c r="DN38" s="102"/>
+      <c r="DO38" s="102"/>
+      <c r="DP38" s="102"/>
+      <c r="DQ38" s="102"/>
+    </row>
+    <row r="39" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="41"/>
+      <c r="B39" s="52" t="s">
+        <v>67</v>
       </c>
       <c r="C39" s="48"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="65"/>
-      <c r="F39" s="65"/>
+      <c r="D39" s="18">
+        <v>0</v>
+      </c>
+      <c r="E39" s="65">
+        <v>45931</v>
+      </c>
+      <c r="F39" s="65">
+        <v>45937</v>
+      </c>
       <c r="G39" s="92"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="116"/>
-      <c r="J39" s="116"/>
-      <c r="K39" s="116"/>
-      <c r="L39" s="116"/>
-      <c r="M39" s="116"/>
-      <c r="N39" s="116"/>
-      <c r="O39" s="116"/>
-      <c r="P39" s="116"/>
-      <c r="Q39" s="116"/>
-      <c r="R39" s="116"/>
-      <c r="S39" s="116"/>
-      <c r="T39" s="116"/>
-      <c r="U39" s="116"/>
-      <c r="V39" s="116"/>
-      <c r="W39" s="116"/>
-      <c r="X39" s="116"/>
-      <c r="Y39" s="116"/>
-      <c r="Z39" s="116"/>
-      <c r="AA39" s="116"/>
-      <c r="AB39" s="116"/>
-      <c r="AC39" s="116"/>
-      <c r="AD39" s="116"/>
-      <c r="AE39" s="116"/>
-      <c r="AF39" s="116"/>
-      <c r="AG39" s="116"/>
-      <c r="AH39" s="116"/>
-      <c r="AI39" s="116"/>
-      <c r="AJ39" s="116"/>
-      <c r="AK39" s="116"/>
-      <c r="AL39" s="116"/>
-      <c r="AM39" s="116"/>
-      <c r="AN39" s="116"/>
-      <c r="AO39" s="116"/>
-      <c r="AP39" s="116"/>
-      <c r="AQ39" s="116"/>
-      <c r="AR39" s="116"/>
-      <c r="AS39" s="116"/>
-      <c r="AT39" s="116"/>
-      <c r="AU39" s="116"/>
-      <c r="AV39" s="116"/>
-      <c r="AW39" s="116"/>
-      <c r="AX39" s="116"/>
-      <c r="AY39" s="116"/>
-      <c r="AZ39" s="116"/>
-      <c r="BA39" s="116"/>
-      <c r="BB39" s="116"/>
-      <c r="BC39" s="116"/>
-      <c r="BD39" s="116"/>
-      <c r="BE39" s="116"/>
-      <c r="BF39" s="116"/>
-      <c r="BG39" s="116"/>
-      <c r="BH39" s="116"/>
-      <c r="BI39" s="116"/>
-      <c r="BJ39" s="116"/>
-      <c r="BK39" s="116"/>
-      <c r="BL39" s="116"/>
-      <c r="BM39" s="116"/>
-      <c r="BN39" s="116"/>
-      <c r="BO39" s="116"/>
-      <c r="BP39" s="116"/>
-      <c r="BQ39" s="116"/>
-      <c r="BR39" s="116"/>
-      <c r="BS39" s="116"/>
-      <c r="BT39" s="116"/>
-      <c r="BU39" s="116"/>
-      <c r="BV39" s="116"/>
-      <c r="BW39" s="116"/>
-      <c r="BX39" s="116"/>
-      <c r="BY39" s="116"/>
-      <c r="BZ39" s="116"/>
-      <c r="CA39" s="116"/>
-      <c r="CB39" s="116"/>
-      <c r="CC39" s="116"/>
-      <c r="CD39" s="116"/>
-      <c r="CE39" s="116"/>
-      <c r="CF39" s="116"/>
-      <c r="CG39" s="116"/>
-      <c r="CH39" s="117"/>
-      <c r="CI39" s="117"/>
-      <c r="CJ39" s="117"/>
-      <c r="CK39" s="117"/>
-      <c r="CL39" s="117"/>
-      <c r="CM39" s="117"/>
-      <c r="CN39" s="117"/>
-      <c r="CO39" s="117"/>
-      <c r="CP39" s="117"/>
-      <c r="CQ39" s="117"/>
-      <c r="CR39" s="117"/>
-      <c r="CS39" s="117"/>
-      <c r="CT39" s="117"/>
-      <c r="CU39" s="117"/>
-      <c r="CV39" s="117"/>
-      <c r="CW39" s="117"/>
-      <c r="CX39" s="117"/>
-      <c r="CY39" s="117"/>
-      <c r="CZ39" s="117"/>
-      <c r="DA39" s="117"/>
-      <c r="DB39" s="117"/>
-      <c r="DC39" s="117"/>
-      <c r="DD39" s="117"/>
-      <c r="DE39" s="117"/>
-      <c r="DF39" s="117"/>
-      <c r="DG39" s="117"/>
-      <c r="DH39" s="117"/>
-      <c r="DI39" s="117"/>
-      <c r="DJ39" s="117"/>
-      <c r="DK39" s="117"/>
-      <c r="DL39" s="117"/>
-      <c r="DM39" s="117"/>
-      <c r="DN39" s="117"/>
-      <c r="DO39" s="117"/>
-      <c r="DP39" s="117"/>
-      <c r="DQ39" s="117"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="26"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="26"/>
+      <c r="X39" s="26"/>
+      <c r="Y39" s="26"/>
+      <c r="Z39" s="26"/>
+      <c r="AA39" s="26"/>
+      <c r="AB39" s="26"/>
+      <c r="AC39" s="97"/>
+      <c r="AD39" s="97"/>
+      <c r="AE39" s="26"/>
+      <c r="AF39" s="26"/>
+      <c r="AG39" s="26"/>
+      <c r="AH39" s="26"/>
+      <c r="AI39" s="26"/>
+      <c r="AJ39" s="26"/>
+      <c r="AK39" s="26"/>
+      <c r="AL39" s="26"/>
+      <c r="AM39" s="26"/>
+      <c r="AN39" s="26"/>
+      <c r="AO39" s="26"/>
+      <c r="AP39" s="26"/>
+      <c r="AQ39" s="26"/>
+      <c r="AR39" s="26"/>
+      <c r="AS39" s="26"/>
+      <c r="AT39" s="26"/>
+      <c r="AU39" s="26"/>
+      <c r="AV39" s="26"/>
+      <c r="AW39" s="26"/>
+      <c r="AX39" s="26"/>
+      <c r="AY39" s="26"/>
+      <c r="AZ39" s="26"/>
+      <c r="BA39" s="26"/>
+      <c r="BB39" s="26"/>
+      <c r="BC39" s="26"/>
+      <c r="BD39" s="26"/>
+      <c r="BE39" s="26"/>
+      <c r="BF39" s="26"/>
+      <c r="BG39" s="26"/>
+      <c r="BH39" s="26"/>
+      <c r="BI39" s="26"/>
+      <c r="BJ39" s="26"/>
+      <c r="BK39" s="26"/>
+      <c r="BL39" s="26"/>
+      <c r="BM39" s="26"/>
+      <c r="BN39" s="26"/>
+      <c r="BO39" s="26"/>
+      <c r="BP39" s="26"/>
+      <c r="BQ39" s="67"/>
+      <c r="BR39" s="67"/>
+      <c r="BS39" s="67"/>
+      <c r="BT39" s="67"/>
+      <c r="BU39" s="67"/>
+      <c r="BV39" s="67"/>
+      <c r="BW39" s="67"/>
+      <c r="BX39" s="67"/>
+      <c r="BY39" s="67"/>
+      <c r="BZ39" s="67"/>
+      <c r="CA39" s="67"/>
+      <c r="CB39" s="67"/>
+      <c r="CC39" s="67"/>
+      <c r="CD39" s="67"/>
+      <c r="CE39" s="67"/>
+      <c r="CF39" s="67"/>
+      <c r="CG39" s="67"/>
+      <c r="CH39"/>
+      <c r="CI39"/>
+      <c r="CJ39"/>
+      <c r="CK39"/>
+      <c r="CL39"/>
+      <c r="CM39"/>
+      <c r="CN39"/>
+      <c r="CO39"/>
+      <c r="CP39"/>
+      <c r="CQ39"/>
+      <c r="CR39"/>
+      <c r="CS39"/>
+      <c r="CT39"/>
+      <c r="CU39"/>
+      <c r="CV39"/>
+      <c r="CW39"/>
+      <c r="CX39"/>
+      <c r="CY39"/>
+      <c r="CZ39"/>
+      <c r="DA39"/>
+      <c r="DB39"/>
+      <c r="DC39"/>
+      <c r="DD39"/>
+      <c r="DE39"/>
+      <c r="DF39"/>
+      <c r="DG39"/>
+      <c r="DH39"/>
+      <c r="DI39"/>
+      <c r="DJ39"/>
+      <c r="DK39"/>
+      <c r="DL39"/>
+      <c r="DM39"/>
+      <c r="DN39"/>
+      <c r="DO39"/>
+      <c r="DP39"/>
+      <c r="DQ39"/>
     </row>
     <row r="40" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="41"/>
       <c r="B40" s="52" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="48"/>
       <c r="D40" s="18">
@@ -7627,7 +7711,7 @@
         <v>45933</v>
       </c>
       <c r="F40" s="65">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="G40" s="92"/>
       <c r="H40" s="14"/>
@@ -7748,17 +7832,17 @@
     <row r="41" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="41"/>
       <c r="B41" s="52" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C41" s="48"/>
       <c r="D41" s="18">
         <v>0</v>
       </c>
       <c r="E41" s="65">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="F41" s="65">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="G41" s="92"/>
       <c r="H41" s="14"/>
@@ -7879,7 +7963,7 @@
     <row r="42" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="41"/>
       <c r="B42" s="52" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="C42" s="48"/>
       <c r="D42" s="18">
@@ -7889,7 +7973,7 @@
         <v>45937</v>
       </c>
       <c r="F42" s="65">
-        <v>45954</v>
+        <v>45937</v>
       </c>
       <c r="G42" s="92"/>
       <c r="H42" s="14"/>
@@ -7926,7 +8010,7 @@
       <c r="AM42" s="26"/>
       <c r="AN42" s="26"/>
       <c r="AO42" s="26"/>
-      <c r="AP42" s="26"/>
+      <c r="AP42" s="160"/>
       <c r="AQ42" s="26"/>
       <c r="AR42" s="26"/>
       <c r="AS42" s="26"/>
@@ -8008,25 +8092,22 @@
       <c r="DQ42"/>
     </row>
     <row r="43" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="40"/>
+      <c r="A43" s="41"/>
       <c r="B43" s="52" t="s">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="C43" s="48"/>
       <c r="D43" s="18">
         <v>0</v>
       </c>
       <c r="E43" s="65">
-        <v>45954</v>
+        <v>45938</v>
       </c>
       <c r="F43" s="65">
-        <v>45958</v>
+        <v>45940</v>
       </c>
       <c r="G43" s="92"/>
-      <c r="H43" s="14">
-        <f t="shared" si="19"/>
-        <v>5</v>
-      </c>
+      <c r="H43" s="14"/>
       <c r="I43" s="26"/>
       <c r="J43" s="26"/>
       <c r="K43" s="26"/>
@@ -8039,8 +8120,8 @@
       <c r="R43" s="26"/>
       <c r="S43" s="26"/>
       <c r="T43" s="26"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="26"/>
       <c r="W43" s="26"/>
       <c r="X43" s="26"/>
       <c r="Y43" s="26"/>
@@ -8095,8 +8176,8 @@
       <c r="BV43" s="67"/>
       <c r="BW43" s="67"/>
       <c r="BX43" s="67"/>
-      <c r="BY43" s="68"/>
-      <c r="BZ43" s="68"/>
+      <c r="BY43" s="67"/>
+      <c r="BZ43" s="67"/>
       <c r="CA43" s="67"/>
       <c r="CB43" s="67"/>
       <c r="CC43" s="67"/>
@@ -8142,19 +8223,19 @@
       <c r="DQ43"/>
     </row>
     <row r="44" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="40"/>
+      <c r="A44" s="41"/>
       <c r="B44" s="52" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C44" s="48"/>
       <c r="D44" s="18">
         <v>0</v>
       </c>
       <c r="E44" s="65">
-        <v>45957</v>
+        <v>45940</v>
       </c>
       <c r="F44" s="65">
-        <v>45960</v>
+        <v>45945</v>
       </c>
       <c r="G44" s="92"/>
       <c r="H44" s="14"/>
@@ -8170,8 +8251,8 @@
       <c r="R44" s="26"/>
       <c r="S44" s="26"/>
       <c r="T44" s="26"/>
-      <c r="U44" s="27"/>
-      <c r="V44" s="27"/>
+      <c r="U44" s="26"/>
+      <c r="V44" s="26"/>
       <c r="W44" s="26"/>
       <c r="X44" s="26"/>
       <c r="Y44" s="26"/>
@@ -8226,8 +8307,8 @@
       <c r="BV44" s="67"/>
       <c r="BW44" s="67"/>
       <c r="BX44" s="67"/>
-      <c r="BY44" s="68"/>
-      <c r="BZ44" s="68"/>
+      <c r="BY44" s="67"/>
+      <c r="BZ44" s="67"/>
       <c r="CA44" s="67"/>
       <c r="CB44" s="67"/>
       <c r="CC44" s="67"/>
@@ -8272,154 +8353,148 @@
       <c r="DP44"/>
       <c r="DQ44"/>
     </row>
-    <row r="45" spans="1:121" s="118" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="138"/>
+    <row r="45" spans="1:121" s="103" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="100"/>
       <c r="B45" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="52"/>
+        <v>66</v>
+      </c>
+      <c r="C45" s="48"/>
       <c r="D45" s="18"/>
       <c r="E45" s="65"/>
       <c r="F45" s="65"/>
       <c r="G45" s="92"/>
-      <c r="H45" s="92" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I45" s="116"/>
-      <c r="J45" s="116"/>
-      <c r="K45" s="116"/>
-      <c r="L45" s="116"/>
-      <c r="M45" s="116"/>
-      <c r="N45" s="116"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="116"/>
-      <c r="Q45" s="116"/>
-      <c r="R45" s="116"/>
-      <c r="S45" s="116"/>
-      <c r="T45" s="116"/>
-      <c r="U45" s="116"/>
-      <c r="V45" s="116"/>
-      <c r="W45" s="116"/>
-      <c r="X45" s="116"/>
-      <c r="Y45" s="116"/>
-      <c r="Z45" s="116"/>
-      <c r="AA45" s="116"/>
-      <c r="AB45" s="116"/>
-      <c r="AC45" s="116"/>
-      <c r="AD45" s="116"/>
-      <c r="AE45" s="116"/>
-      <c r="AF45" s="116"/>
-      <c r="AG45" s="116"/>
-      <c r="AH45" s="116"/>
-      <c r="AI45" s="116"/>
-      <c r="AJ45" s="116"/>
-      <c r="AK45" s="116"/>
-      <c r="AL45" s="116"/>
-      <c r="AM45" s="116"/>
-      <c r="AN45" s="116"/>
-      <c r="AO45" s="116"/>
-      <c r="AP45" s="116"/>
-      <c r="AQ45" s="116"/>
-      <c r="AR45" s="116"/>
-      <c r="AS45" s="116"/>
-      <c r="AT45" s="116"/>
-      <c r="AU45" s="116"/>
-      <c r="AV45" s="116"/>
-      <c r="AW45" s="116"/>
-      <c r="AX45" s="116"/>
-      <c r="AY45" s="116"/>
-      <c r="AZ45" s="116"/>
-      <c r="BA45" s="116"/>
-      <c r="BB45" s="116"/>
-      <c r="BC45" s="116"/>
-      <c r="BD45" s="116"/>
-      <c r="BE45" s="116"/>
-      <c r="BF45" s="116"/>
-      <c r="BG45" s="116"/>
-      <c r="BH45" s="116"/>
-      <c r="BI45" s="116"/>
-      <c r="BJ45" s="116"/>
-      <c r="BK45" s="116"/>
-      <c r="BL45" s="116"/>
-      <c r="BM45" s="116"/>
-      <c r="BN45" s="116"/>
-      <c r="BO45" s="116"/>
-      <c r="BP45" s="116"/>
-      <c r="BQ45" s="116"/>
-      <c r="BR45" s="116"/>
-      <c r="BS45" s="116"/>
-      <c r="BT45" s="116"/>
-      <c r="BU45" s="116"/>
-      <c r="BV45" s="116"/>
-      <c r="BW45" s="116"/>
-      <c r="BX45" s="116"/>
-      <c r="BY45" s="116"/>
-      <c r="BZ45" s="116"/>
-      <c r="CA45" s="116"/>
-      <c r="CB45" s="116"/>
-      <c r="CC45" s="116"/>
-      <c r="CD45" s="116"/>
-      <c r="CE45" s="116"/>
-      <c r="CF45" s="116"/>
-      <c r="CG45" s="116"/>
-      <c r="CH45" s="117"/>
-      <c r="CI45" s="117"/>
-      <c r="CJ45" s="117"/>
-      <c r="CK45" s="117"/>
-      <c r="CL45" s="117"/>
-      <c r="CM45" s="117"/>
-      <c r="CN45" s="117"/>
-      <c r="CO45" s="117"/>
-      <c r="CP45" s="117"/>
-      <c r="CQ45" s="117"/>
-      <c r="CR45" s="117"/>
-      <c r="CS45" s="117"/>
-      <c r="CT45" s="117"/>
-      <c r="CU45" s="117"/>
-      <c r="CV45" s="117"/>
-      <c r="CW45" s="117"/>
-      <c r="CX45" s="117"/>
-      <c r="CY45" s="117"/>
-      <c r="CZ45" s="117"/>
-      <c r="DA45" s="117"/>
-      <c r="DB45" s="117"/>
-      <c r="DC45" s="117"/>
-      <c r="DD45" s="117"/>
-      <c r="DE45" s="117"/>
-      <c r="DF45" s="117"/>
-      <c r="DG45" s="117"/>
-      <c r="DH45" s="117"/>
-      <c r="DI45" s="117"/>
-      <c r="DJ45" s="117"/>
-      <c r="DK45" s="117"/>
-      <c r="DL45" s="117"/>
-      <c r="DM45" s="117"/>
-      <c r="DN45" s="117"/>
-      <c r="DO45" s="117"/>
-      <c r="DP45" s="117"/>
-      <c r="DQ45" s="117"/>
+      <c r="H45" s="92"/>
+      <c r="I45" s="101"/>
+      <c r="J45" s="101"/>
+      <c r="K45" s="101"/>
+      <c r="L45" s="101"/>
+      <c r="M45" s="101"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="101"/>
+      <c r="P45" s="101"/>
+      <c r="Q45" s="101"/>
+      <c r="R45" s="101"/>
+      <c r="S45" s="101"/>
+      <c r="T45" s="101"/>
+      <c r="U45" s="101"/>
+      <c r="V45" s="101"/>
+      <c r="W45" s="101"/>
+      <c r="X45" s="101"/>
+      <c r="Y45" s="101"/>
+      <c r="Z45" s="101"/>
+      <c r="AA45" s="101"/>
+      <c r="AB45" s="101"/>
+      <c r="AC45" s="101"/>
+      <c r="AD45" s="101"/>
+      <c r="AE45" s="101"/>
+      <c r="AF45" s="101"/>
+      <c r="AG45" s="101"/>
+      <c r="AH45" s="101"/>
+      <c r="AI45" s="101"/>
+      <c r="AJ45" s="101"/>
+      <c r="AK45" s="101"/>
+      <c r="AL45" s="101"/>
+      <c r="AM45" s="101"/>
+      <c r="AN45" s="101"/>
+      <c r="AO45" s="101"/>
+      <c r="AP45" s="101"/>
+      <c r="AQ45" s="101"/>
+      <c r="AR45" s="101"/>
+      <c r="AS45" s="101"/>
+      <c r="AT45" s="101"/>
+      <c r="AU45" s="101"/>
+      <c r="AV45" s="101"/>
+      <c r="AW45" s="101"/>
+      <c r="AX45" s="101"/>
+      <c r="AY45" s="101"/>
+      <c r="AZ45" s="101"/>
+      <c r="BA45" s="101"/>
+      <c r="BB45" s="101"/>
+      <c r="BC45" s="101"/>
+      <c r="BD45" s="101"/>
+      <c r="BE45" s="101"/>
+      <c r="BF45" s="101"/>
+      <c r="BG45" s="101"/>
+      <c r="BH45" s="101"/>
+      <c r="BI45" s="101"/>
+      <c r="BJ45" s="101"/>
+      <c r="BK45" s="101"/>
+      <c r="BL45" s="101"/>
+      <c r="BM45" s="101"/>
+      <c r="BN45" s="101"/>
+      <c r="BO45" s="101"/>
+      <c r="BP45" s="101"/>
+      <c r="BQ45" s="101"/>
+      <c r="BR45" s="101"/>
+      <c r="BS45" s="101"/>
+      <c r="BT45" s="101"/>
+      <c r="BU45" s="101"/>
+      <c r="BV45" s="101"/>
+      <c r="BW45" s="101"/>
+      <c r="BX45" s="101"/>
+      <c r="BY45" s="101"/>
+      <c r="BZ45" s="101"/>
+      <c r="CA45" s="101"/>
+      <c r="CB45" s="101"/>
+      <c r="CC45" s="101"/>
+      <c r="CD45" s="101"/>
+      <c r="CE45" s="101"/>
+      <c r="CF45" s="101"/>
+      <c r="CG45" s="101"/>
+      <c r="CH45" s="102"/>
+      <c r="CI45" s="102"/>
+      <c r="CJ45" s="102"/>
+      <c r="CK45" s="102"/>
+      <c r="CL45" s="102"/>
+      <c r="CM45" s="102"/>
+      <c r="CN45" s="102"/>
+      <c r="CO45" s="102"/>
+      <c r="CP45" s="102"/>
+      <c r="CQ45" s="102"/>
+      <c r="CR45" s="102"/>
+      <c r="CS45" s="102"/>
+      <c r="CT45" s="102"/>
+      <c r="CU45" s="102"/>
+      <c r="CV45" s="102"/>
+      <c r="CW45" s="102"/>
+      <c r="CX45" s="102"/>
+      <c r="CY45" s="102"/>
+      <c r="CZ45" s="102"/>
+      <c r="DA45" s="102"/>
+      <c r="DB45" s="102"/>
+      <c r="DC45" s="102"/>
+      <c r="DD45" s="102"/>
+      <c r="DE45" s="102"/>
+      <c r="DF45" s="102"/>
+      <c r="DG45" s="102"/>
+      <c r="DH45" s="102"/>
+      <c r="DI45" s="102"/>
+      <c r="DJ45" s="102"/>
+      <c r="DK45" s="102"/>
+      <c r="DL45" s="102"/>
+      <c r="DM45" s="102"/>
+      <c r="DN45" s="102"/>
+      <c r="DO45" s="102"/>
+      <c r="DP45" s="102"/>
+      <c r="DQ45" s="102"/>
     </row>
     <row r="46" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="40"/>
-      <c r="B46" s="95" t="s">
-        <v>74</v>
+      <c r="A46" s="41"/>
+      <c r="B46" s="52" t="s">
+        <v>69</v>
       </c>
       <c r="C46" s="48"/>
       <c r="D46" s="18">
         <v>0</v>
       </c>
       <c r="E46" s="65">
-        <v>45959</v>
+        <v>45933</v>
       </c>
       <c r="F46" s="65">
-        <v>45959</v>
+        <v>45933</v>
       </c>
       <c r="G46" s="92"/>
-      <c r="H46" s="14">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
+      <c r="H46" s="14"/>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
       <c r="K46" s="26"/>
@@ -8436,7 +8511,7 @@
       <c r="V46" s="26"/>
       <c r="W46" s="26"/>
       <c r="X46" s="26"/>
-      <c r="Y46" s="27"/>
+      <c r="Y46" s="26"/>
       <c r="Z46" s="26"/>
       <c r="AA46" s="26"/>
       <c r="AB46" s="26"/>
@@ -8492,7 +8567,7 @@
       <c r="BZ46" s="67"/>
       <c r="CA46" s="67"/>
       <c r="CB46" s="67"/>
-      <c r="CC46" s="68"/>
+      <c r="CC46" s="67"/>
       <c r="CD46" s="67"/>
       <c r="CE46" s="67"/>
       <c r="CF46" s="67"/>
@@ -8535,7 +8610,7 @@
       <c r="DQ46"/>
     </row>
     <row r="47" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="40"/>
+      <c r="A47" s="41"/>
       <c r="B47" s="52" t="s">
         <v>75</v>
       </c>
@@ -8544,16 +8619,13 @@
         <v>0</v>
       </c>
       <c r="E47" s="65">
-        <v>45959</v>
+        <v>45936</v>
       </c>
       <c r="F47" s="65">
-        <v>45959</v>
+        <v>45936</v>
       </c>
       <c r="G47" s="92"/>
-      <c r="H47" s="14">
-        <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
+      <c r="H47" s="14"/>
       <c r="I47" s="26"/>
       <c r="J47" s="26"/>
       <c r="K47" s="26"/>
@@ -8668,148 +8740,157 @@
       <c r="DP47"/>
       <c r="DQ47"/>
     </row>
-    <row r="48" spans="1:121" s="118" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="138"/>
-      <c r="B48" s="73" t="s">
-        <v>66</v>
+    <row r="48" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="41"/>
+      <c r="B48" s="52" t="s">
+        <v>76</v>
       </c>
       <c r="C48" s="48"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="65"/>
-      <c r="F48" s="65"/>
+      <c r="D48" s="18">
+        <v>0</v>
+      </c>
+      <c r="E48" s="65">
+        <v>45937</v>
+      </c>
+      <c r="F48" s="65">
+        <v>45954</v>
+      </c>
       <c r="G48" s="92"/>
-      <c r="H48" s="92"/>
-      <c r="I48" s="116"/>
-      <c r="J48" s="116"/>
-      <c r="K48" s="116"/>
-      <c r="L48" s="116"/>
-      <c r="M48" s="116"/>
-      <c r="N48" s="116"/>
-      <c r="O48" s="116"/>
-      <c r="P48" s="116"/>
-      <c r="Q48" s="116"/>
-      <c r="R48" s="116"/>
-      <c r="S48" s="116"/>
-      <c r="T48" s="116"/>
-      <c r="U48" s="116"/>
-      <c r="V48" s="116"/>
-      <c r="W48" s="116"/>
-      <c r="X48" s="116"/>
-      <c r="Y48" s="116"/>
-      <c r="Z48" s="116"/>
-      <c r="AA48" s="116"/>
-      <c r="AB48" s="116"/>
-      <c r="AC48" s="116"/>
-      <c r="AD48" s="116"/>
-      <c r="AE48" s="116"/>
-      <c r="AF48" s="116"/>
-      <c r="AG48" s="116"/>
-      <c r="AH48" s="116"/>
-      <c r="AI48" s="116"/>
-      <c r="AJ48" s="116"/>
-      <c r="AK48" s="116"/>
-      <c r="AL48" s="116"/>
-      <c r="AM48" s="116"/>
-      <c r="AN48" s="116"/>
-      <c r="AO48" s="116"/>
-      <c r="AP48" s="116"/>
-      <c r="AQ48" s="116"/>
-      <c r="AR48" s="116"/>
-      <c r="AS48" s="116"/>
-      <c r="AT48" s="116"/>
-      <c r="AU48" s="116"/>
-      <c r="AV48" s="116"/>
-      <c r="AW48" s="116"/>
-      <c r="AX48" s="116"/>
-      <c r="AY48" s="116"/>
-      <c r="AZ48" s="116"/>
-      <c r="BA48" s="116"/>
-      <c r="BB48" s="116"/>
-      <c r="BC48" s="116"/>
-      <c r="BD48" s="116"/>
-      <c r="BE48" s="116"/>
-      <c r="BF48" s="116"/>
-      <c r="BG48" s="116"/>
-      <c r="BH48" s="116"/>
-      <c r="BI48" s="116"/>
-      <c r="BJ48" s="116"/>
-      <c r="BK48" s="116"/>
-      <c r="BL48" s="116"/>
-      <c r="BM48" s="116"/>
-      <c r="BN48" s="116"/>
-      <c r="BO48" s="116"/>
-      <c r="BP48" s="116"/>
-      <c r="BQ48" s="116"/>
-      <c r="BR48" s="116"/>
-      <c r="BS48" s="116"/>
-      <c r="BT48" s="116"/>
-      <c r="BU48" s="116"/>
-      <c r="BV48" s="116"/>
-      <c r="BW48" s="116"/>
-      <c r="BX48" s="116"/>
-      <c r="BY48" s="116"/>
-      <c r="BZ48" s="116"/>
-      <c r="CA48" s="116"/>
-      <c r="CB48" s="116"/>
-      <c r="CC48" s="116"/>
-      <c r="CD48" s="116"/>
-      <c r="CE48" s="116"/>
-      <c r="CF48" s="116"/>
-      <c r="CG48" s="116"/>
-      <c r="CH48" s="117"/>
-      <c r="CI48" s="117"/>
-      <c r="CJ48" s="117"/>
-      <c r="CK48" s="117"/>
-      <c r="CL48" s="117"/>
-      <c r="CM48" s="117"/>
-      <c r="CN48" s="117"/>
-      <c r="CO48" s="117"/>
-      <c r="CP48" s="117"/>
-      <c r="CQ48" s="117"/>
-      <c r="CR48" s="117"/>
-      <c r="CS48" s="117"/>
-      <c r="CT48" s="117"/>
-      <c r="CU48" s="117"/>
-      <c r="CV48" s="117"/>
-      <c r="CW48" s="117"/>
-      <c r="CX48" s="117"/>
-      <c r="CY48" s="117"/>
-      <c r="CZ48" s="117"/>
-      <c r="DA48" s="117"/>
-      <c r="DB48" s="117"/>
-      <c r="DC48" s="117"/>
-      <c r="DD48" s="117"/>
-      <c r="DE48" s="117"/>
-      <c r="DF48" s="117"/>
-      <c r="DG48" s="117"/>
-      <c r="DH48" s="117"/>
-      <c r="DI48" s="117"/>
-      <c r="DJ48" s="117"/>
-      <c r="DK48" s="117"/>
-      <c r="DL48" s="117"/>
-      <c r="DM48" s="117"/>
-      <c r="DN48" s="117"/>
-      <c r="DO48" s="117"/>
-      <c r="DP48" s="117"/>
-      <c r="DQ48" s="117"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="26"/>
+      <c r="J48" s="26"/>
+      <c r="K48" s="26"/>
+      <c r="L48" s="26"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="26"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="26"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="26"/>
+      <c r="S48" s="26"/>
+      <c r="T48" s="26"/>
+      <c r="U48" s="26"/>
+      <c r="V48" s="26"/>
+      <c r="W48" s="26"/>
+      <c r="X48" s="26"/>
+      <c r="Y48" s="26"/>
+      <c r="Z48" s="26"/>
+      <c r="AA48" s="26"/>
+      <c r="AB48" s="26"/>
+      <c r="AC48" s="97"/>
+      <c r="AD48" s="97"/>
+      <c r="AE48" s="26"/>
+      <c r="AF48" s="26"/>
+      <c r="AG48" s="26"/>
+      <c r="AH48" s="26"/>
+      <c r="AI48" s="26"/>
+      <c r="AJ48" s="26"/>
+      <c r="AK48" s="26"/>
+      <c r="AL48" s="26"/>
+      <c r="AM48" s="26"/>
+      <c r="AN48" s="26"/>
+      <c r="AO48" s="26"/>
+      <c r="AP48" s="26"/>
+      <c r="AQ48" s="26"/>
+      <c r="AR48" s="26"/>
+      <c r="AS48" s="26"/>
+      <c r="AT48" s="26"/>
+      <c r="AU48" s="26"/>
+      <c r="AV48" s="26"/>
+      <c r="AW48" s="26"/>
+      <c r="AX48" s="26"/>
+      <c r="AY48" s="26"/>
+      <c r="AZ48" s="26"/>
+      <c r="BA48" s="26"/>
+      <c r="BB48" s="26"/>
+      <c r="BC48" s="26"/>
+      <c r="BD48" s="26"/>
+      <c r="BE48" s="26"/>
+      <c r="BF48" s="26"/>
+      <c r="BG48" s="26"/>
+      <c r="BH48" s="26"/>
+      <c r="BI48" s="26"/>
+      <c r="BJ48" s="26"/>
+      <c r="BK48" s="26"/>
+      <c r="BL48" s="26"/>
+      <c r="BM48" s="26"/>
+      <c r="BN48" s="26"/>
+      <c r="BO48" s="26"/>
+      <c r="BP48" s="26"/>
+      <c r="BQ48" s="67"/>
+      <c r="BR48" s="67"/>
+      <c r="BS48" s="67"/>
+      <c r="BT48" s="67"/>
+      <c r="BU48" s="67"/>
+      <c r="BV48" s="67"/>
+      <c r="BW48" s="67"/>
+      <c r="BX48" s="67"/>
+      <c r="BY48" s="67"/>
+      <c r="BZ48" s="67"/>
+      <c r="CA48" s="67"/>
+      <c r="CB48" s="67"/>
+      <c r="CC48" s="67"/>
+      <c r="CD48" s="67"/>
+      <c r="CE48" s="67"/>
+      <c r="CF48" s="67"/>
+      <c r="CG48" s="67"/>
+      <c r="CH48"/>
+      <c r="CI48"/>
+      <c r="CJ48"/>
+      <c r="CK48"/>
+      <c r="CL48"/>
+      <c r="CM48"/>
+      <c r="CN48"/>
+      <c r="CO48"/>
+      <c r="CP48"/>
+      <c r="CQ48"/>
+      <c r="CR48"/>
+      <c r="CS48"/>
+      <c r="CT48"/>
+      <c r="CU48"/>
+      <c r="CV48"/>
+      <c r="CW48"/>
+      <c r="CX48"/>
+      <c r="CY48"/>
+      <c r="CZ48"/>
+      <c r="DA48"/>
+      <c r="DB48"/>
+      <c r="DC48"/>
+      <c r="DD48"/>
+      <c r="DE48"/>
+      <c r="DF48"/>
+      <c r="DG48"/>
+      <c r="DH48"/>
+      <c r="DI48"/>
+      <c r="DJ48"/>
+      <c r="DK48"/>
+      <c r="DL48"/>
+      <c r="DM48"/>
+      <c r="DN48"/>
+      <c r="DO48"/>
+      <c r="DP48"/>
+      <c r="DQ48"/>
     </row>
     <row r="49" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="40"/>
       <c r="B49" s="52" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C49" s="48"/>
       <c r="D49" s="18">
         <v>0</v>
       </c>
       <c r="E49" s="65">
-        <v>45960</v>
+        <v>45954</v>
       </c>
       <c r="F49" s="65">
-        <v>45964</v>
+        <v>45958</v>
       </c>
       <c r="G49" s="92"/>
-      <c r="H49" s="14"/>
+      <c r="H49" s="14">
+        <f t="shared" si="17"/>
+        <v>5</v>
+      </c>
       <c r="I49" s="26"/>
       <c r="J49" s="26"/>
       <c r="K49" s="26"/>
@@ -8822,8 +8903,8 @@
       <c r="R49" s="26"/>
       <c r="S49" s="26"/>
       <c r="T49" s="26"/>
-      <c r="U49" s="26"/>
-      <c r="V49" s="26"/>
+      <c r="U49" s="27"/>
+      <c r="V49" s="27"/>
       <c r="W49" s="26"/>
       <c r="X49" s="26"/>
       <c r="Y49" s="26"/>
@@ -8878,8 +8959,8 @@
       <c r="BV49" s="67"/>
       <c r="BW49" s="67"/>
       <c r="BX49" s="67"/>
-      <c r="BY49" s="67"/>
-      <c r="BZ49" s="67"/>
+      <c r="BY49" s="68"/>
+      <c r="BZ49" s="68"/>
       <c r="CA49" s="67"/>
       <c r="CB49" s="67"/>
       <c r="CC49" s="67"/>
@@ -8927,17 +9008,17 @@
     <row r="50" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="40"/>
       <c r="B50" s="52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C50" s="48"/>
       <c r="D50" s="18">
         <v>0</v>
       </c>
       <c r="E50" s="65">
-        <v>45965</v>
+        <v>45957</v>
       </c>
       <c r="F50" s="65">
-        <v>45967</v>
+        <v>45960</v>
       </c>
       <c r="G50" s="92"/>
       <c r="H50" s="14"/>
@@ -8953,8 +9034,8 @@
       <c r="R50" s="26"/>
       <c r="S50" s="26"/>
       <c r="T50" s="26"/>
-      <c r="U50" s="26"/>
-      <c r="V50" s="26"/>
+      <c r="U50" s="27"/>
+      <c r="V50" s="27"/>
       <c r="W50" s="26"/>
       <c r="X50" s="26"/>
       <c r="Y50" s="26"/>
@@ -9009,8 +9090,8 @@
       <c r="BV50" s="67"/>
       <c r="BW50" s="67"/>
       <c r="BX50" s="67"/>
-      <c r="BY50" s="67"/>
-      <c r="BZ50" s="67"/>
+      <c r="BY50" s="68"/>
+      <c r="BZ50" s="68"/>
       <c r="CA50" s="67"/>
       <c r="CB50" s="67"/>
       <c r="CC50" s="67"/>
@@ -9055,230 +9136,231 @@
       <c r="DP50"/>
       <c r="DQ50"/>
     </row>
-    <row r="51" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="40"/>
-      <c r="B51" s="52" t="s">
-        <v>83</v>
-      </c>
-      <c r="C51" s="48"/>
-      <c r="D51" s="18">
+    <row r="51" spans="1:121" s="103" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="120"/>
+      <c r="B51" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="52"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="65"/>
+      <c r="F51" s="65"/>
+      <c r="G51" s="92"/>
+      <c r="H51" s="92" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I51" s="101"/>
+      <c r="J51" s="101"/>
+      <c r="K51" s="101"/>
+      <c r="L51" s="101"/>
+      <c r="M51" s="101"/>
+      <c r="N51" s="101"/>
+      <c r="O51" s="101"/>
+      <c r="P51" s="101"/>
+      <c r="Q51" s="101"/>
+      <c r="R51" s="101"/>
+      <c r="S51" s="101"/>
+      <c r="T51" s="101"/>
+      <c r="U51" s="101"/>
+      <c r="V51" s="101"/>
+      <c r="W51" s="101"/>
+      <c r="X51" s="101"/>
+      <c r="Y51" s="101"/>
+      <c r="Z51" s="101"/>
+      <c r="AA51" s="101"/>
+      <c r="AB51" s="101"/>
+      <c r="AC51" s="101"/>
+      <c r="AD51" s="101"/>
+      <c r="AE51" s="101"/>
+      <c r="AF51" s="101"/>
+      <c r="AG51" s="101"/>
+      <c r="AH51" s="101"/>
+      <c r="AI51" s="101"/>
+      <c r="AJ51" s="101"/>
+      <c r="AK51" s="101"/>
+      <c r="AL51" s="101"/>
+      <c r="AM51" s="101"/>
+      <c r="AN51" s="101"/>
+      <c r="AO51" s="101"/>
+      <c r="AP51" s="101"/>
+      <c r="AQ51" s="101"/>
+      <c r="AR51" s="101"/>
+      <c r="AS51" s="101"/>
+      <c r="AT51" s="101"/>
+      <c r="AU51" s="101"/>
+      <c r="AV51" s="101"/>
+      <c r="AW51" s="101"/>
+      <c r="AX51" s="101"/>
+      <c r="AY51" s="101"/>
+      <c r="AZ51" s="101"/>
+      <c r="BA51" s="101"/>
+      <c r="BB51" s="101"/>
+      <c r="BC51" s="101"/>
+      <c r="BD51" s="101"/>
+      <c r="BE51" s="101"/>
+      <c r="BF51" s="101"/>
+      <c r="BG51" s="101"/>
+      <c r="BH51" s="101"/>
+      <c r="BI51" s="101"/>
+      <c r="BJ51" s="101"/>
+      <c r="BK51" s="101"/>
+      <c r="BL51" s="101"/>
+      <c r="BM51" s="101"/>
+      <c r="BN51" s="101"/>
+      <c r="BO51" s="101"/>
+      <c r="BP51" s="101"/>
+      <c r="BQ51" s="101"/>
+      <c r="BR51" s="101"/>
+      <c r="BS51" s="101"/>
+      <c r="BT51" s="101"/>
+      <c r="BU51" s="101"/>
+      <c r="BV51" s="101"/>
+      <c r="BW51" s="101"/>
+      <c r="BX51" s="101"/>
+      <c r="BY51" s="101"/>
+      <c r="BZ51" s="101"/>
+      <c r="CA51" s="101"/>
+      <c r="CB51" s="101"/>
+      <c r="CC51" s="101"/>
+      <c r="CD51" s="101"/>
+      <c r="CE51" s="101"/>
+      <c r="CF51" s="101"/>
+      <c r="CG51" s="101"/>
+      <c r="CH51" s="102"/>
+      <c r="CI51" s="102"/>
+      <c r="CJ51" s="102"/>
+      <c r="CK51" s="102"/>
+      <c r="CL51" s="102"/>
+      <c r="CM51" s="102"/>
+      <c r="CN51" s="102"/>
+      <c r="CO51" s="102"/>
+      <c r="CP51" s="102"/>
+      <c r="CQ51" s="102"/>
+      <c r="CR51" s="102"/>
+      <c r="CS51" s="102"/>
+      <c r="CT51" s="102"/>
+      <c r="CU51" s="102"/>
+      <c r="CV51" s="102"/>
+      <c r="CW51" s="102"/>
+      <c r="CX51" s="102"/>
+      <c r="CY51" s="102"/>
+      <c r="CZ51" s="102"/>
+      <c r="DA51" s="102"/>
+      <c r="DB51" s="102"/>
+      <c r="DC51" s="102"/>
+      <c r="DD51" s="102"/>
+      <c r="DE51" s="102"/>
+      <c r="DF51" s="102"/>
+      <c r="DG51" s="102"/>
+      <c r="DH51" s="102"/>
+      <c r="DI51" s="102"/>
+      <c r="DJ51" s="102"/>
+      <c r="DK51" s="102"/>
+      <c r="DL51" s="102"/>
+      <c r="DM51" s="102"/>
+      <c r="DN51" s="102"/>
+      <c r="DO51" s="102"/>
+      <c r="DP51" s="102"/>
+      <c r="DQ51" s="102"/>
+    </row>
+    <row r="52" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="40"/>
+      <c r="B52" s="95" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="48"/>
+      <c r="D52" s="18">
         <v>0</v>
       </c>
-      <c r="E51" s="65">
-        <v>45968</v>
-      </c>
-      <c r="F51" s="65">
-        <v>45968</v>
-      </c>
-      <c r="G51" s="92"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="26"/>
-      <c r="J51" s="26"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="26"/>
-      <c r="O51" s="26"/>
-      <c r="P51" s="26"/>
-      <c r="Q51" s="26"/>
-      <c r="R51" s="26"/>
-      <c r="S51" s="26"/>
-      <c r="T51" s="26"/>
-      <c r="U51" s="26"/>
-      <c r="V51" s="26"/>
-      <c r="W51" s="26"/>
-      <c r="X51" s="26"/>
-      <c r="Y51" s="26"/>
-      <c r="Z51" s="26"/>
-      <c r="AA51" s="26"/>
-      <c r="AB51" s="26"/>
-      <c r="AC51" s="97"/>
-      <c r="AD51" s="97"/>
-      <c r="AE51" s="26"/>
-      <c r="AF51" s="26"/>
-      <c r="AG51" s="26"/>
-      <c r="AH51" s="26"/>
-      <c r="AI51" s="26"/>
-      <c r="AJ51" s="26"/>
-      <c r="AK51" s="26"/>
-      <c r="AL51" s="26"/>
-      <c r="AM51" s="26"/>
-      <c r="AN51" s="26"/>
-      <c r="AO51" s="26"/>
-      <c r="AP51" s="26"/>
-      <c r="AQ51" s="26"/>
-      <c r="AR51" s="26"/>
-      <c r="AS51" s="26"/>
-      <c r="AT51" s="26"/>
-      <c r="AU51" s="26"/>
-      <c r="AV51" s="26"/>
-      <c r="AW51" s="26"/>
-      <c r="AX51" s="26"/>
-      <c r="AY51" s="26"/>
-      <c r="AZ51" s="26"/>
-      <c r="BA51" s="26"/>
-      <c r="BB51" s="26"/>
-      <c r="BC51" s="26"/>
-      <c r="BD51" s="26"/>
-      <c r="BE51" s="26"/>
-      <c r="BF51" s="26"/>
-      <c r="BG51" s="26"/>
-      <c r="BH51" s="26"/>
-      <c r="BI51" s="26"/>
-      <c r="BJ51" s="26"/>
-      <c r="BK51" s="26"/>
-      <c r="BL51" s="26"/>
-      <c r="BM51" s="26"/>
-      <c r="BN51" s="26"/>
-      <c r="BO51" s="26"/>
-      <c r="BP51" s="26"/>
-      <c r="BQ51" s="67"/>
-      <c r="BR51" s="67"/>
-      <c r="BS51" s="67"/>
-      <c r="BT51" s="67"/>
-      <c r="BU51" s="67"/>
-      <c r="BV51" s="67"/>
-      <c r="BW51" s="67"/>
-      <c r="BX51" s="67"/>
-      <c r="BY51" s="67"/>
-      <c r="BZ51" s="67"/>
-      <c r="CA51" s="67"/>
-      <c r="CB51" s="67"/>
-      <c r="CC51" s="67"/>
-      <c r="CD51" s="67"/>
-      <c r="CE51" s="67"/>
-      <c r="CF51" s="67"/>
-      <c r="CG51" s="67"/>
-      <c r="CH51"/>
-      <c r="CI51"/>
-      <c r="CJ51"/>
-      <c r="CK51"/>
-      <c r="CL51"/>
-      <c r="CM51"/>
-      <c r="CN51"/>
-      <c r="CO51"/>
-      <c r="CP51"/>
-      <c r="CQ51"/>
-      <c r="CR51"/>
-      <c r="CS51"/>
-      <c r="CT51"/>
-      <c r="CU51"/>
-      <c r="CV51"/>
-      <c r="CW51"/>
-      <c r="CX51"/>
-      <c r="CY51"/>
-      <c r="CZ51"/>
-      <c r="DA51"/>
-      <c r="DB51"/>
-      <c r="DC51"/>
-      <c r="DD51"/>
-      <c r="DE51"/>
-      <c r="DF51"/>
-      <c r="DG51"/>
-      <c r="DH51"/>
-      <c r="DI51"/>
-      <c r="DJ51"/>
-      <c r="DK51"/>
-      <c r="DL51"/>
-      <c r="DM51"/>
-      <c r="DN51"/>
-      <c r="DO51"/>
-      <c r="DP51"/>
-      <c r="DQ51"/>
-    </row>
-    <row r="52" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52" s="49"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="59"/>
-      <c r="G52" s="93"/>
-      <c r="H52" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I52" s="113"/>
-      <c r="J52" s="114"/>
-      <c r="K52" s="114"/>
-      <c r="L52" s="114"/>
-      <c r="M52" s="114"/>
-      <c r="N52" s="114"/>
-      <c r="O52" s="114"/>
-      <c r="P52" s="114"/>
-      <c r="Q52" s="114"/>
-      <c r="R52" s="114"/>
-      <c r="S52" s="114"/>
-      <c r="T52" s="114"/>
-      <c r="U52" s="114"/>
-      <c r="V52" s="114"/>
-      <c r="W52" s="114"/>
-      <c r="X52" s="114"/>
-      <c r="Y52" s="114"/>
-      <c r="Z52" s="114"/>
-      <c r="AA52" s="114"/>
-      <c r="AB52" s="114"/>
-      <c r="AC52" s="114"/>
-      <c r="AD52" s="114"/>
-      <c r="AE52" s="114"/>
-      <c r="AF52" s="114"/>
-      <c r="AG52" s="114"/>
-      <c r="AH52" s="114"/>
-      <c r="AI52" s="114"/>
-      <c r="AJ52" s="114"/>
-      <c r="AK52" s="114"/>
-      <c r="AL52" s="114"/>
-      <c r="AM52" s="114"/>
-      <c r="AN52" s="114"/>
-      <c r="AO52" s="114"/>
-      <c r="AP52" s="114"/>
-      <c r="AQ52" s="114"/>
-      <c r="AR52" s="114"/>
-      <c r="AS52" s="114"/>
-      <c r="AT52" s="114"/>
-      <c r="AU52" s="114"/>
-      <c r="AV52" s="114"/>
-      <c r="AW52" s="114"/>
-      <c r="AX52" s="114"/>
-      <c r="AY52" s="114"/>
-      <c r="AZ52" s="114"/>
-      <c r="BA52" s="114"/>
-      <c r="BB52" s="114"/>
-      <c r="BC52" s="114"/>
-      <c r="BD52" s="114"/>
-      <c r="BE52" s="114"/>
-      <c r="BF52" s="114"/>
-      <c r="BG52" s="114"/>
-      <c r="BH52" s="114"/>
-      <c r="BI52" s="114"/>
-      <c r="BJ52" s="114"/>
-      <c r="BK52" s="114"/>
-      <c r="BL52" s="114"/>
-      <c r="BM52" s="114"/>
-      <c r="BN52" s="114"/>
-      <c r="BO52" s="114"/>
-      <c r="BP52" s="114"/>
-      <c r="BQ52" s="114"/>
-      <c r="BR52" s="114"/>
-      <c r="BS52" s="114"/>
-      <c r="BT52" s="114"/>
-      <c r="BU52" s="114"/>
-      <c r="BV52" s="114"/>
-      <c r="BW52" s="114"/>
-      <c r="BX52" s="114"/>
-      <c r="BY52" s="114"/>
-      <c r="BZ52" s="114"/>
-      <c r="CA52" s="114"/>
-      <c r="CB52" s="114"/>
-      <c r="CC52" s="114"/>
-      <c r="CD52" s="114"/>
-      <c r="CE52" s="114"/>
-      <c r="CF52" s="114"/>
-      <c r="CG52" s="115"/>
+      <c r="E52" s="65">
+        <v>45959</v>
+      </c>
+      <c r="F52" s="65">
+        <v>45959</v>
+      </c>
+      <c r="G52" s="92"/>
+      <c r="H52" s="14">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="26"/>
+      <c r="L52" s="26"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="26"/>
+      <c r="Q52" s="26"/>
+      <c r="R52" s="26"/>
+      <c r="S52" s="26"/>
+      <c r="T52" s="26"/>
+      <c r="U52" s="26"/>
+      <c r="V52" s="26"/>
+      <c r="W52" s="26"/>
+      <c r="X52" s="26"/>
+      <c r="Y52" s="27"/>
+      <c r="Z52" s="26"/>
+      <c r="AA52" s="26"/>
+      <c r="AB52" s="26"/>
+      <c r="AC52" s="97"/>
+      <c r="AD52" s="97"/>
+      <c r="AE52" s="26"/>
+      <c r="AF52" s="26"/>
+      <c r="AG52" s="26"/>
+      <c r="AH52" s="26"/>
+      <c r="AI52" s="26"/>
+      <c r="AJ52" s="26"/>
+      <c r="AK52" s="26"/>
+      <c r="AL52" s="26"/>
+      <c r="AM52" s="26"/>
+      <c r="AN52" s="26"/>
+      <c r="AO52" s="26"/>
+      <c r="AP52" s="26"/>
+      <c r="AQ52" s="26"/>
+      <c r="AR52" s="26"/>
+      <c r="AS52" s="26"/>
+      <c r="AT52" s="26"/>
+      <c r="AU52" s="26"/>
+      <c r="AV52" s="26"/>
+      <c r="AW52" s="26"/>
+      <c r="AX52" s="26"/>
+      <c r="AY52" s="26"/>
+      <c r="AZ52" s="26"/>
+      <c r="BA52" s="26"/>
+      <c r="BB52" s="26"/>
+      <c r="BC52" s="26"/>
+      <c r="BD52" s="26"/>
+      <c r="BE52" s="26"/>
+      <c r="BF52" s="26"/>
+      <c r="BG52" s="26"/>
+      <c r="BH52" s="26"/>
+      <c r="BI52" s="26"/>
+      <c r="BJ52" s="26"/>
+      <c r="BK52" s="26"/>
+      <c r="BL52" s="26"/>
+      <c r="BM52" s="26"/>
+      <c r="BN52" s="26"/>
+      <c r="BO52" s="26"/>
+      <c r="BP52" s="26"/>
+      <c r="BQ52" s="67"/>
+      <c r="BR52" s="67"/>
+      <c r="BS52" s="67"/>
+      <c r="BT52" s="67"/>
+      <c r="BU52" s="67"/>
+      <c r="BV52" s="67"/>
+      <c r="BW52" s="67"/>
+      <c r="BX52" s="67"/>
+      <c r="BY52" s="67"/>
+      <c r="BZ52" s="67"/>
+      <c r="CA52" s="67"/>
+      <c r="CB52" s="67"/>
+      <c r="CC52" s="68"/>
+      <c r="CD52" s="67"/>
+      <c r="CE52" s="67"/>
+      <c r="CF52" s="67"/>
+      <c r="CG52" s="67"/>
       <c r="CH52"/>
       <c r="CI52"/>
       <c r="CJ52"/>
@@ -9318,17 +9400,23 @@
     </row>
     <row r="53" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="40"/>
-      <c r="B53" s="147" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53" s="50"/>
-      <c r="D53" s="21"/>
-      <c r="E53" s="60"/>
-      <c r="F53" s="60"/>
-      <c r="G53" s="94"/>
-      <c r="H53" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
+      <c r="B53" s="52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="48"/>
+      <c r="D53" s="18">
+        <v>0</v>
+      </c>
+      <c r="E53" s="65">
+        <v>45959</v>
+      </c>
+      <c r="F53" s="65">
+        <v>45959</v>
+      </c>
+      <c r="G53" s="92"/>
+      <c r="H53" s="14">
+        <f t="shared" si="17"/>
+        <v>1</v>
       </c>
       <c r="I53" s="26"/>
       <c r="J53" s="26"/>
@@ -9446,18 +9534,21 @@
     </row>
     <row r="54" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="40"/>
-      <c r="B54" s="148" t="s">
-        <v>92</v>
-      </c>
-      <c r="C54" s="50"/>
-      <c r="D54" s="21"/>
-      <c r="E54" s="60"/>
-      <c r="F54" s="60"/>
-      <c r="G54" s="94"/>
-      <c r="H54" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+      <c r="B54" s="52" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="48"/>
+      <c r="D54" s="18">
+        <v>0</v>
+      </c>
+      <c r="E54" s="65">
+        <v>45959</v>
+      </c>
+      <c r="F54" s="65">
+        <v>45959</v>
+      </c>
+      <c r="G54" s="92"/>
+      <c r="H54" s="14"/>
       <c r="I54" s="26"/>
       <c r="J54" s="26"/>
       <c r="K54" s="26"/>
@@ -9572,148 +9663,148 @@
       <c r="DP54"/>
       <c r="DQ54"/>
     </row>
-    <row r="55" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="40"/>
-      <c r="B55" s="148" t="s">
-        <v>89</v>
-      </c>
-      <c r="C55" s="50"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="60"/>
-      <c r="F55" s="60"/>
-      <c r="G55" s="94"/>
-      <c r="H55" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="I55" s="26"/>
-      <c r="J55" s="26"/>
-      <c r="K55" s="26"/>
-      <c r="L55" s="26"/>
-      <c r="M55" s="26"/>
-      <c r="N55" s="26"/>
-      <c r="O55" s="26"/>
-      <c r="P55" s="26"/>
-      <c r="Q55" s="26"/>
-      <c r="R55" s="26"/>
-      <c r="S55" s="26"/>
-      <c r="T55" s="26"/>
-      <c r="U55" s="26"/>
-      <c r="V55" s="26"/>
-      <c r="W55" s="26"/>
-      <c r="X55" s="26"/>
-      <c r="Y55" s="26"/>
-      <c r="Z55" s="26"/>
-      <c r="AA55" s="26"/>
-      <c r="AB55" s="26"/>
-      <c r="AC55" s="97"/>
-      <c r="AD55" s="97"/>
-      <c r="AE55" s="26"/>
-      <c r="AF55" s="26"/>
-      <c r="AG55" s="26"/>
-      <c r="AH55" s="26"/>
-      <c r="AI55" s="26"/>
-      <c r="AJ55" s="26"/>
-      <c r="AK55" s="26"/>
-      <c r="AL55" s="26"/>
-      <c r="AM55" s="26"/>
-      <c r="AN55" s="26"/>
-      <c r="AO55" s="26"/>
-      <c r="AP55" s="26"/>
-      <c r="AQ55" s="26"/>
-      <c r="AR55" s="26"/>
-      <c r="AS55" s="26"/>
-      <c r="AT55" s="26"/>
-      <c r="AU55" s="26"/>
-      <c r="AV55" s="26"/>
-      <c r="AW55" s="26"/>
-      <c r="AX55" s="26"/>
-      <c r="AY55" s="26"/>
-      <c r="AZ55" s="26"/>
-      <c r="BA55" s="26"/>
-      <c r="BB55" s="26"/>
-      <c r="BC55" s="26"/>
-      <c r="BD55" s="26"/>
-      <c r="BE55" s="26"/>
-      <c r="BF55" s="26"/>
-      <c r="BG55" s="26"/>
-      <c r="BH55" s="26"/>
-      <c r="BI55" s="26"/>
-      <c r="BJ55" s="26"/>
-      <c r="BK55" s="26"/>
-      <c r="BL55" s="26"/>
-      <c r="BM55" s="26"/>
-      <c r="BN55" s="26"/>
-      <c r="BO55" s="26"/>
-      <c r="BP55" s="26"/>
-      <c r="BQ55" s="67"/>
-      <c r="BR55" s="67"/>
-      <c r="BS55" s="67"/>
-      <c r="BT55" s="67"/>
-      <c r="BU55" s="67"/>
-      <c r="BV55" s="67"/>
-      <c r="BW55" s="67"/>
-      <c r="BX55" s="67"/>
-      <c r="BY55" s="67"/>
-      <c r="BZ55" s="67"/>
-      <c r="CA55" s="67"/>
-      <c r="CB55" s="67"/>
-      <c r="CC55" s="67"/>
-      <c r="CD55" s="67"/>
-      <c r="CE55" s="67"/>
-      <c r="CF55" s="67"/>
-      <c r="CG55" s="67"/>
-      <c r="CH55"/>
-      <c r="CI55"/>
-      <c r="CJ55"/>
-      <c r="CK55"/>
-      <c r="CL55"/>
-      <c r="CM55"/>
-      <c r="CN55"/>
-      <c r="CO55"/>
-      <c r="CP55"/>
-      <c r="CQ55"/>
-      <c r="CR55"/>
-      <c r="CS55"/>
-      <c r="CT55"/>
-      <c r="CU55"/>
-      <c r="CV55"/>
-      <c r="CW55"/>
-      <c r="CX55"/>
-      <c r="CY55"/>
-      <c r="CZ55"/>
-      <c r="DA55"/>
-      <c r="DB55"/>
-      <c r="DC55"/>
-      <c r="DD55"/>
-      <c r="DE55"/>
-      <c r="DF55"/>
-      <c r="DG55"/>
-      <c r="DH55"/>
-      <c r="DI55"/>
-      <c r="DJ55"/>
-      <c r="DK55"/>
-      <c r="DL55"/>
-      <c r="DM55"/>
-      <c r="DN55"/>
-      <c r="DO55"/>
-      <c r="DP55"/>
-      <c r="DQ55"/>
+    <row r="55" spans="1:121" s="103" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="120"/>
+      <c r="B55" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="48"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="65"/>
+      <c r="F55" s="65"/>
+      <c r="G55" s="92"/>
+      <c r="H55" s="92"/>
+      <c r="I55" s="101"/>
+      <c r="J55" s="101"/>
+      <c r="K55" s="101"/>
+      <c r="L55" s="101"/>
+      <c r="M55" s="101"/>
+      <c r="N55" s="101"/>
+      <c r="O55" s="101"/>
+      <c r="P55" s="101"/>
+      <c r="Q55" s="101"/>
+      <c r="R55" s="101"/>
+      <c r="S55" s="101"/>
+      <c r="T55" s="101"/>
+      <c r="U55" s="101"/>
+      <c r="V55" s="101"/>
+      <c r="W55" s="101"/>
+      <c r="X55" s="101"/>
+      <c r="Y55" s="101"/>
+      <c r="Z55" s="101"/>
+      <c r="AA55" s="101"/>
+      <c r="AB55" s="101"/>
+      <c r="AC55" s="101"/>
+      <c r="AD55" s="101"/>
+      <c r="AE55" s="101"/>
+      <c r="AF55" s="101"/>
+      <c r="AG55" s="101"/>
+      <c r="AH55" s="101"/>
+      <c r="AI55" s="101"/>
+      <c r="AJ55" s="101"/>
+      <c r="AK55" s="101"/>
+      <c r="AL55" s="101"/>
+      <c r="AM55" s="101"/>
+      <c r="AN55" s="101"/>
+      <c r="AO55" s="101"/>
+      <c r="AP55" s="101"/>
+      <c r="AQ55" s="101"/>
+      <c r="AR55" s="101"/>
+      <c r="AS55" s="101"/>
+      <c r="AT55" s="101"/>
+      <c r="AU55" s="101"/>
+      <c r="AV55" s="101"/>
+      <c r="AW55" s="101"/>
+      <c r="AX55" s="101"/>
+      <c r="AY55" s="101"/>
+      <c r="AZ55" s="101"/>
+      <c r="BA55" s="101"/>
+      <c r="BB55" s="101"/>
+      <c r="BC55" s="101"/>
+      <c r="BD55" s="101"/>
+      <c r="BE55" s="101"/>
+      <c r="BF55" s="101"/>
+      <c r="BG55" s="101"/>
+      <c r="BH55" s="101"/>
+      <c r="BI55" s="101"/>
+      <c r="BJ55" s="101"/>
+      <c r="BK55" s="101"/>
+      <c r="BL55" s="101"/>
+      <c r="BM55" s="101"/>
+      <c r="BN55" s="101"/>
+      <c r="BO55" s="101"/>
+      <c r="BP55" s="101"/>
+      <c r="BQ55" s="101"/>
+      <c r="BR55" s="101"/>
+      <c r="BS55" s="101"/>
+      <c r="BT55" s="101"/>
+      <c r="BU55" s="101"/>
+      <c r="BV55" s="101"/>
+      <c r="BW55" s="101"/>
+      <c r="BX55" s="101"/>
+      <c r="BY55" s="101"/>
+      <c r="BZ55" s="101"/>
+      <c r="CA55" s="101"/>
+      <c r="CB55" s="101"/>
+      <c r="CC55" s="101"/>
+      <c r="CD55" s="101"/>
+      <c r="CE55" s="101"/>
+      <c r="CF55" s="101"/>
+      <c r="CG55" s="101"/>
+      <c r="CH55" s="102"/>
+      <c r="CI55" s="102"/>
+      <c r="CJ55" s="102"/>
+      <c r="CK55" s="102"/>
+      <c r="CL55" s="102"/>
+      <c r="CM55" s="102"/>
+      <c r="CN55" s="102"/>
+      <c r="CO55" s="102"/>
+      <c r="CP55" s="102"/>
+      <c r="CQ55" s="102"/>
+      <c r="CR55" s="102"/>
+      <c r="CS55" s="102"/>
+      <c r="CT55" s="102"/>
+      <c r="CU55" s="102"/>
+      <c r="CV55" s="102"/>
+      <c r="CW55" s="102"/>
+      <c r="CX55" s="102"/>
+      <c r="CY55" s="102"/>
+      <c r="CZ55" s="102"/>
+      <c r="DA55" s="102"/>
+      <c r="DB55" s="102"/>
+      <c r="DC55" s="102"/>
+      <c r="DD55" s="102"/>
+      <c r="DE55" s="102"/>
+      <c r="DF55" s="102"/>
+      <c r="DG55" s="102"/>
+      <c r="DH55" s="102"/>
+      <c r="DI55" s="102"/>
+      <c r="DJ55" s="102"/>
+      <c r="DK55" s="102"/>
+      <c r="DL55" s="102"/>
+      <c r="DM55" s="102"/>
+      <c r="DN55" s="102"/>
+      <c r="DO55" s="102"/>
+      <c r="DP55" s="102"/>
+      <c r="DQ55" s="102"/>
     </row>
     <row r="56" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="40"/>
-      <c r="B56" s="148" t="s">
-        <v>90</v>
-      </c>
-      <c r="C56" s="50"/>
-      <c r="D56" s="21"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="60"/>
-      <c r="G56" s="94"/>
-      <c r="H56" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+      <c r="B56" s="52" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="48"/>
+      <c r="D56" s="18">
+        <v>0</v>
+      </c>
+      <c r="E56" s="65">
+        <v>45960</v>
+      </c>
+      <c r="F56" s="65">
+        <v>45964</v>
+      </c>
+      <c r="G56" s="92"/>
+      <c r="H56" s="14"/>
       <c r="I56" s="26"/>
       <c r="J56" s="26"/>
       <c r="K56" s="26"/>
@@ -9830,18 +9921,21 @@
     </row>
     <row r="57" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="40"/>
-      <c r="B57" s="148" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="50"/>
-      <c r="D57" s="21"/>
-      <c r="E57" s="60"/>
-      <c r="F57" s="60"/>
-      <c r="G57" s="94"/>
-      <c r="H57" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+      <c r="B57" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="48"/>
+      <c r="D57" s="18">
+        <v>0</v>
+      </c>
+      <c r="E57" s="65">
+        <v>45965</v>
+      </c>
+      <c r="F57" s="65">
+        <v>45967</v>
+      </c>
+      <c r="G57" s="92"/>
+      <c r="H57" s="14"/>
       <c r="I57" s="26"/>
       <c r="J57" s="26"/>
       <c r="K57" s="26"/>
@@ -9957,19 +10051,22 @@
       <c r="DQ57"/>
     </row>
     <row r="58" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="40" t="s">
-        <v>8</v>
-      </c>
-      <c r="B58" s="83"/>
-      <c r="C58" s="84"/>
-      <c r="D58" s="85"/>
-      <c r="E58" s="86"/>
-      <c r="F58" s="87"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+      <c r="A58" s="40"/>
+      <c r="B58" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C58" s="48"/>
+      <c r="D58" s="18">
+        <v>0</v>
+      </c>
+      <c r="E58" s="65">
+        <v>45968</v>
+      </c>
+      <c r="F58" s="65">
+        <v>45968</v>
+      </c>
+      <c r="G58" s="92"/>
+      <c r="H58" s="14"/>
       <c r="I58" s="26"/>
       <c r="J58" s="26"/>
       <c r="K58" s="26"/>
@@ -9989,9 +10086,9 @@
       <c r="Y58" s="26"/>
       <c r="Z58" s="26"/>
       <c r="AA58" s="26"/>
-      <c r="AB58" s="67"/>
-      <c r="AC58" s="67"/>
-      <c r="AD58" s="67"/>
+      <c r="AB58" s="26"/>
+      <c r="AC58" s="97"/>
+      <c r="AD58" s="97"/>
       <c r="AE58" s="26"/>
       <c r="AF58" s="26"/>
       <c r="AG58" s="26"/>
@@ -10085,94 +10182,98 @@
       <c r="DQ58"/>
     </row>
     <row r="59" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="40"/>
-      <c r="B59" s="88"/>
-      <c r="C59" s="84"/>
-      <c r="D59" s="85"/>
-      <c r="E59" s="89"/>
-      <c r="F59" s="89"/>
-      <c r="G59" s="14"/>
+      <c r="A59" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B59" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C59" s="49"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="93"/>
       <c r="H59" s="14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I59" s="26"/>
-      <c r="J59" s="26"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="26"/>
-      <c r="M59" s="26"/>
-      <c r="N59" s="26"/>
-      <c r="O59" s="26"/>
-      <c r="P59" s="26"/>
-      <c r="Q59" s="26"/>
-      <c r="R59" s="26"/>
-      <c r="S59" s="26"/>
-      <c r="T59" s="26"/>
-      <c r="U59" s="26"/>
-      <c r="V59" s="26"/>
-      <c r="W59" s="26"/>
-      <c r="X59" s="26"/>
-      <c r="Y59" s="26"/>
-      <c r="Z59" s="26"/>
-      <c r="AA59" s="26"/>
-      <c r="AB59" s="26"/>
-      <c r="AC59" s="26"/>
-      <c r="AD59" s="26"/>
-      <c r="AE59" s="26"/>
-      <c r="AF59" s="26"/>
-      <c r="AG59" s="26"/>
-      <c r="AH59" s="26"/>
-      <c r="AI59" s="26"/>
-      <c r="AJ59" s="26"/>
-      <c r="AK59" s="26"/>
-      <c r="AL59" s="26"/>
-      <c r="AM59" s="26"/>
-      <c r="AN59" s="26"/>
-      <c r="AO59" s="26"/>
-      <c r="AP59" s="26"/>
-      <c r="AQ59" s="26"/>
-      <c r="AR59" s="26"/>
-      <c r="AS59" s="26"/>
-      <c r="AT59" s="26"/>
-      <c r="AU59" s="26"/>
-      <c r="AV59" s="26"/>
-      <c r="AW59" s="26"/>
-      <c r="AX59" s="26"/>
-      <c r="AY59" s="26"/>
-      <c r="AZ59" s="26"/>
-      <c r="BA59" s="26"/>
-      <c r="BB59" s="26"/>
-      <c r="BC59" s="26"/>
-      <c r="BD59" s="26"/>
-      <c r="BE59" s="26"/>
-      <c r="BF59" s="26"/>
-      <c r="BG59" s="26"/>
-      <c r="BH59" s="26"/>
-      <c r="BI59" s="26"/>
-      <c r="BJ59" s="26"/>
-      <c r="BK59" s="26"/>
-      <c r="BL59" s="26"/>
-      <c r="BM59" s="26"/>
-      <c r="BN59" s="26"/>
-      <c r="BO59" s="26"/>
-      <c r="BP59" s="26"/>
-      <c r="BQ59" s="26"/>
-      <c r="BR59" s="26"/>
-      <c r="BS59" s="26"/>
-      <c r="BT59" s="26"/>
-      <c r="BU59" s="26"/>
-      <c r="BV59" s="26"/>
-      <c r="BW59" s="26"/>
-      <c r="BX59" s="26"/>
-      <c r="BY59" s="26"/>
-      <c r="BZ59" s="26"/>
-      <c r="CA59" s="26"/>
-      <c r="CB59" s="26"/>
-      <c r="CC59" s="26"/>
-      <c r="CD59" s="26"/>
-      <c r="CE59" s="26"/>
-      <c r="CF59" s="26"/>
-      <c r="CG59" s="26"/>
+      <c r="I59" s="144"/>
+      <c r="J59" s="145"/>
+      <c r="K59" s="145"/>
+      <c r="L59" s="145"/>
+      <c r="M59" s="145"/>
+      <c r="N59" s="145"/>
+      <c r="O59" s="145"/>
+      <c r="P59" s="145"/>
+      <c r="Q59" s="145"/>
+      <c r="R59" s="145"/>
+      <c r="S59" s="145"/>
+      <c r="T59" s="145"/>
+      <c r="U59" s="145"/>
+      <c r="V59" s="145"/>
+      <c r="W59" s="145"/>
+      <c r="X59" s="145"/>
+      <c r="Y59" s="145"/>
+      <c r="Z59" s="145"/>
+      <c r="AA59" s="145"/>
+      <c r="AB59" s="145"/>
+      <c r="AC59" s="145"/>
+      <c r="AD59" s="145"/>
+      <c r="AE59" s="145"/>
+      <c r="AF59" s="145"/>
+      <c r="AG59" s="145"/>
+      <c r="AH59" s="145"/>
+      <c r="AI59" s="145"/>
+      <c r="AJ59" s="145"/>
+      <c r="AK59" s="145"/>
+      <c r="AL59" s="145"/>
+      <c r="AM59" s="145"/>
+      <c r="AN59" s="145"/>
+      <c r="AO59" s="145"/>
+      <c r="AP59" s="145"/>
+      <c r="AQ59" s="145"/>
+      <c r="AR59" s="145"/>
+      <c r="AS59" s="145"/>
+      <c r="AT59" s="145"/>
+      <c r="AU59" s="145"/>
+      <c r="AV59" s="145"/>
+      <c r="AW59" s="145"/>
+      <c r="AX59" s="145"/>
+      <c r="AY59" s="145"/>
+      <c r="AZ59" s="145"/>
+      <c r="BA59" s="145"/>
+      <c r="BB59" s="145"/>
+      <c r="BC59" s="145"/>
+      <c r="BD59" s="145"/>
+      <c r="BE59" s="145"/>
+      <c r="BF59" s="145"/>
+      <c r="BG59" s="145"/>
+      <c r="BH59" s="145"/>
+      <c r="BI59" s="145"/>
+      <c r="BJ59" s="145"/>
+      <c r="BK59" s="145"/>
+      <c r="BL59" s="145"/>
+      <c r="BM59" s="145"/>
+      <c r="BN59" s="145"/>
+      <c r="BO59" s="145"/>
+      <c r="BP59" s="145"/>
+      <c r="BQ59" s="145"/>
+      <c r="BR59" s="145"/>
+      <c r="BS59" s="145"/>
+      <c r="BT59" s="145"/>
+      <c r="BU59" s="145"/>
+      <c r="BV59" s="145"/>
+      <c r="BW59" s="145"/>
+      <c r="BX59" s="145"/>
+      <c r="BY59" s="145"/>
+      <c r="BZ59" s="145"/>
+      <c r="CA59" s="145"/>
+      <c r="CB59" s="145"/>
+      <c r="CC59" s="145"/>
+      <c r="CD59" s="145"/>
+      <c r="CE59" s="145"/>
+      <c r="CF59" s="145"/>
+      <c r="CG59" s="146"/>
       <c r="CH59"/>
       <c r="CI59"/>
       <c r="CJ59"/>
@@ -10212,14 +10313,16 @@
     </row>
     <row r="60" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="40"/>
-      <c r="B60" s="88"/>
-      <c r="C60" s="84"/>
-      <c r="D60" s="85"/>
-      <c r="E60" s="89"/>
-      <c r="F60" s="89"/>
-      <c r="G60" s="14"/>
+      <c r="B60" s="129" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="50"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="60"/>
+      <c r="G60" s="94"/>
       <c r="H60" s="14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I60" s="26"/>
@@ -10242,8 +10345,8 @@
       <c r="Z60" s="26"/>
       <c r="AA60" s="26"/>
       <c r="AB60" s="26"/>
-      <c r="AC60" s="26"/>
-      <c r="AD60" s="26"/>
+      <c r="AC60" s="97"/>
+      <c r="AD60" s="97"/>
       <c r="AE60" s="26"/>
       <c r="AF60" s="26"/>
       <c r="AG60" s="26"/>
@@ -10279,26 +10382,28 @@
       <c r="BK60" s="26"/>
       <c r="BL60" s="26"/>
       <c r="BM60" s="26"/>
-      <c r="BN60" s="26"/>
+      <c r="BN60" s="26" t="s">
+        <v>89</v>
+      </c>
       <c r="BO60" s="26"/>
       <c r="BP60" s="26"/>
-      <c r="BQ60" s="26"/>
-      <c r="BR60" s="26"/>
-      <c r="BS60" s="26"/>
-      <c r="BT60" s="26"/>
-      <c r="BU60" s="26"/>
-      <c r="BV60" s="26"/>
-      <c r="BW60" s="26"/>
-      <c r="BX60" s="26"/>
-      <c r="BY60" s="26"/>
-      <c r="BZ60" s="26"/>
-      <c r="CA60" s="26"/>
-      <c r="CB60" s="26"/>
-      <c r="CC60" s="26"/>
-      <c r="CD60" s="26"/>
-      <c r="CE60" s="26"/>
-      <c r="CF60" s="26"/>
-      <c r="CG60" s="26"/>
+      <c r="BQ60" s="67"/>
+      <c r="BR60" s="67"/>
+      <c r="BS60" s="67"/>
+      <c r="BT60" s="67"/>
+      <c r="BU60" s="67"/>
+      <c r="BV60" s="67"/>
+      <c r="BW60" s="67"/>
+      <c r="BX60" s="67"/>
+      <c r="BY60" s="67"/>
+      <c r="BZ60" s="67"/>
+      <c r="CA60" s="67"/>
+      <c r="CB60" s="67"/>
+      <c r="CC60" s="67"/>
+      <c r="CD60" s="67"/>
+      <c r="CE60" s="67"/>
+      <c r="CF60" s="67"/>
+      <c r="CG60" s="67"/>
       <c r="CH60"/>
       <c r="CI60"/>
       <c r="CJ60"/>
@@ -10338,14 +10443,16 @@
     </row>
     <row r="61" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="40"/>
-      <c r="B61" s="88"/>
-      <c r="C61" s="84"/>
-      <c r="D61" s="85"/>
-      <c r="E61" s="89"/>
-      <c r="F61" s="89"/>
-      <c r="G61" s="14"/>
+      <c r="B61" s="130" t="s">
+        <v>86</v>
+      </c>
+      <c r="C61" s="50"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="94"/>
       <c r="H61" s="14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I61" s="26"/>
@@ -10368,8 +10475,8 @@
       <c r="Z61" s="26"/>
       <c r="AA61" s="26"/>
       <c r="AB61" s="26"/>
-      <c r="AC61" s="26"/>
-      <c r="AD61" s="26"/>
+      <c r="AC61" s="97"/>
+      <c r="AD61" s="97"/>
       <c r="AE61" s="26"/>
       <c r="AF61" s="26"/>
       <c r="AG61" s="26"/>
@@ -10408,23 +10515,23 @@
       <c r="BN61" s="26"/>
       <c r="BO61" s="26"/>
       <c r="BP61" s="26"/>
-      <c r="BQ61" s="26"/>
-      <c r="BR61" s="26"/>
-      <c r="BS61" s="26"/>
-      <c r="BT61" s="26"/>
-      <c r="BU61" s="26"/>
-      <c r="BV61" s="26"/>
-      <c r="BW61" s="26"/>
-      <c r="BX61" s="26"/>
-      <c r="BY61" s="26"/>
-      <c r="BZ61" s="26"/>
-      <c r="CA61" s="26"/>
-      <c r="CB61" s="26"/>
-      <c r="CC61" s="26"/>
-      <c r="CD61" s="26"/>
-      <c r="CE61" s="26"/>
-      <c r="CF61" s="26"/>
-      <c r="CG61" s="26"/>
+      <c r="BQ61" s="67"/>
+      <c r="BR61" s="67"/>
+      <c r="BS61" s="67"/>
+      <c r="BT61" s="67"/>
+      <c r="BU61" s="67"/>
+      <c r="BV61" s="67"/>
+      <c r="BW61" s="67"/>
+      <c r="BX61" s="67"/>
+      <c r="BY61" s="67"/>
+      <c r="BZ61" s="67"/>
+      <c r="CA61" s="67"/>
+      <c r="CB61" s="67"/>
+      <c r="CC61" s="67"/>
+      <c r="CD61" s="67"/>
+      <c r="CE61" s="67"/>
+      <c r="CF61" s="67"/>
+      <c r="CG61" s="67"/>
       <c r="CH61"/>
       <c r="CI61"/>
       <c r="CJ61"/>
@@ -10464,16 +10571,15 @@
     </row>
     <row r="62" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="40"/>
-      <c r="B62" s="88"/>
-      <c r="C62" s="84"/>
-      <c r="D62" s="85"/>
-      <c r="E62" s="89"/>
-      <c r="F62" s="89"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
+      <c r="B62" s="130" t="s">
+        <v>109</v>
+      </c>
+      <c r="C62" s="50"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="94"/>
+      <c r="H62" s="14"/>
       <c r="I62" s="26"/>
       <c r="J62" s="26"/>
       <c r="K62" s="26"/>
@@ -10494,8 +10600,8 @@
       <c r="Z62" s="26"/>
       <c r="AA62" s="26"/>
       <c r="AB62" s="26"/>
-      <c r="AC62" s="26"/>
-      <c r="AD62" s="26"/>
+      <c r="AC62" s="97"/>
+      <c r="AD62" s="97"/>
       <c r="AE62" s="26"/>
       <c r="AF62" s="26"/>
       <c r="AG62" s="26"/>
@@ -10534,23 +10640,23 @@
       <c r="BN62" s="26"/>
       <c r="BO62" s="26"/>
       <c r="BP62" s="26"/>
-      <c r="BQ62" s="26"/>
-      <c r="BR62" s="26"/>
-      <c r="BS62" s="26"/>
-      <c r="BT62" s="26"/>
-      <c r="BU62" s="26"/>
-      <c r="BV62" s="26"/>
-      <c r="BW62" s="26"/>
-      <c r="BX62" s="26"/>
-      <c r="BY62" s="26"/>
-      <c r="BZ62" s="26"/>
-      <c r="CA62" s="26"/>
-      <c r="CB62" s="26"/>
-      <c r="CC62" s="26"/>
-      <c r="CD62" s="26"/>
-      <c r="CE62" s="26"/>
-      <c r="CF62" s="26"/>
-      <c r="CG62" s="26"/>
+      <c r="BQ62" s="67"/>
+      <c r="BR62" s="67"/>
+      <c r="BS62" s="67"/>
+      <c r="BT62" s="67"/>
+      <c r="BU62" s="67"/>
+      <c r="BV62" s="67"/>
+      <c r="BW62" s="67"/>
+      <c r="BX62" s="67"/>
+      <c r="BY62" s="67"/>
+      <c r="BZ62" s="67"/>
+      <c r="CA62" s="67"/>
+      <c r="CB62" s="67"/>
+      <c r="CC62" s="67"/>
+      <c r="CD62" s="67"/>
+      <c r="CE62" s="67"/>
+      <c r="CF62" s="67"/>
+      <c r="CG62" s="67"/>
       <c r="CH62"/>
       <c r="CI62"/>
       <c r="CJ62"/>
@@ -10590,14 +10696,16 @@
     </row>
     <row r="63" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="40"/>
-      <c r="B63" s="88"/>
-      <c r="C63" s="84"/>
-      <c r="D63" s="85"/>
-      <c r="E63" s="89"/>
-      <c r="F63" s="89"/>
-      <c r="G63" s="14"/>
+      <c r="B63" s="130" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" s="50"/>
+      <c r="D63" s="21"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="94"/>
       <c r="H63" s="14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I63" s="26"/>
@@ -10620,8 +10728,8 @@
       <c r="Z63" s="26"/>
       <c r="AA63" s="26"/>
       <c r="AB63" s="26"/>
-      <c r="AC63" s="26"/>
-      <c r="AD63" s="26"/>
+      <c r="AC63" s="97"/>
+      <c r="AD63" s="97"/>
       <c r="AE63" s="26"/>
       <c r="AF63" s="26"/>
       <c r="AG63" s="26"/>
@@ -10660,23 +10768,23 @@
       <c r="BN63" s="26"/>
       <c r="BO63" s="26"/>
       <c r="BP63" s="26"/>
-      <c r="BQ63" s="26"/>
-      <c r="BR63" s="26"/>
-      <c r="BS63" s="26"/>
-      <c r="BT63" s="26"/>
-      <c r="BU63" s="26"/>
-      <c r="BV63" s="26"/>
-      <c r="BW63" s="26"/>
-      <c r="BX63" s="26"/>
-      <c r="BY63" s="26"/>
-      <c r="BZ63" s="26"/>
-      <c r="CA63" s="26"/>
-      <c r="CB63" s="26"/>
-      <c r="CC63" s="26"/>
-      <c r="CD63" s="26"/>
-      <c r="CE63" s="26"/>
-      <c r="CF63" s="26"/>
-      <c r="CG63" s="26"/>
+      <c r="BQ63" s="67"/>
+      <c r="BR63" s="67"/>
+      <c r="BS63" s="67"/>
+      <c r="BT63" s="67"/>
+      <c r="BU63" s="67"/>
+      <c r="BV63" s="67"/>
+      <c r="BW63" s="67"/>
+      <c r="BX63" s="67"/>
+      <c r="BY63" s="67"/>
+      <c r="BZ63" s="67"/>
+      <c r="CA63" s="67"/>
+      <c r="CB63" s="67"/>
+      <c r="CC63" s="67"/>
+      <c r="CD63" s="67"/>
+      <c r="CE63" s="67"/>
+      <c r="CF63" s="67"/>
+      <c r="CG63" s="67"/>
       <c r="CH63"/>
       <c r="CI63"/>
       <c r="CJ63"/>
@@ -10715,17 +10823,17 @@
       <c r="DQ63"/>
     </row>
     <row r="64" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B64" s="53"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="66"/>
-      <c r="F64" s="66"/>
-      <c r="G64" s="14"/>
+      <c r="A64" s="40"/>
+      <c r="B64" s="130" t="s">
+        <v>108</v>
+      </c>
+      <c r="C64" s="50"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="94"/>
       <c r="H64" s="14" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="I64" s="26"/>
@@ -10748,8 +10856,8 @@
       <c r="Z64" s="26"/>
       <c r="AA64" s="26"/>
       <c r="AB64" s="26"/>
-      <c r="AC64" s="26"/>
-      <c r="AD64" s="26"/>
+      <c r="AC64" s="97"/>
+      <c r="AD64" s="97"/>
       <c r="AE64" s="26"/>
       <c r="AF64" s="26"/>
       <c r="AG64" s="26"/>
@@ -10784,6 +10892,27 @@
       <c r="BJ64" s="26"/>
       <c r="BK64" s="26"/>
       <c r="BL64" s="26"/>
+      <c r="BM64" s="26"/>
+      <c r="BN64" s="26"/>
+      <c r="BO64" s="26"/>
+      <c r="BP64" s="26"/>
+      <c r="BQ64" s="67"/>
+      <c r="BR64" s="67"/>
+      <c r="BS64" s="67"/>
+      <c r="BT64" s="67"/>
+      <c r="BU64" s="67"/>
+      <c r="BV64" s="67"/>
+      <c r="BW64" s="67"/>
+      <c r="BX64" s="67"/>
+      <c r="BY64" s="67"/>
+      <c r="BZ64" s="67"/>
+      <c r="CA64" s="67"/>
+      <c r="CB64" s="67"/>
+      <c r="CC64" s="67"/>
+      <c r="CD64" s="67"/>
+      <c r="CE64" s="67"/>
+      <c r="CF64" s="67"/>
+      <c r="CG64" s="67"/>
       <c r="CH64"/>
       <c r="CI64"/>
       <c r="CJ64"/>
@@ -10822,70 +10951,96 @@
       <c r="DQ64"/>
     </row>
     <row r="65" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="41"/>
-      <c r="B65" s="22"/>
-      <c r="C65" s="23"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="62"/>
-      <c r="G65" s="25"/>
-      <c r="H65" s="25"/>
-      <c r="I65" s="28"/>
-      <c r="J65" s="28"/>
-      <c r="K65" s="28"/>
-      <c r="L65" s="28"/>
-      <c r="M65" s="28"/>
-      <c r="N65" s="28"/>
-      <c r="O65" s="28"/>
-      <c r="P65" s="28"/>
-      <c r="Q65" s="28"/>
-      <c r="R65" s="28"/>
-      <c r="S65" s="28"/>
-      <c r="T65" s="28"/>
-      <c r="U65" s="28"/>
-      <c r="V65" s="28"/>
-      <c r="W65" s="28"/>
-      <c r="X65" s="28"/>
-      <c r="Y65" s="28"/>
-      <c r="Z65" s="28"/>
-      <c r="AA65" s="28"/>
-      <c r="AB65" s="28"/>
-      <c r="AC65" s="28"/>
-      <c r="AD65" s="28"/>
-      <c r="AE65" s="28"/>
-      <c r="AF65" s="28"/>
-      <c r="AG65" s="28"/>
-      <c r="AH65" s="28"/>
-      <c r="AI65" s="28"/>
-      <c r="AJ65" s="28"/>
-      <c r="AK65" s="28"/>
-      <c r="AL65" s="28"/>
-      <c r="AM65" s="28"/>
-      <c r="AN65" s="28"/>
-      <c r="AO65" s="28"/>
-      <c r="AP65" s="28"/>
-      <c r="AQ65" s="28"/>
-      <c r="AR65" s="28"/>
-      <c r="AS65" s="28"/>
-      <c r="AT65" s="28"/>
-      <c r="AU65" s="28"/>
-      <c r="AV65" s="28"/>
-      <c r="AW65" s="28"/>
-      <c r="AX65" s="28"/>
-      <c r="AY65" s="28"/>
-      <c r="AZ65" s="28"/>
-      <c r="BA65" s="28"/>
-      <c r="BB65" s="28"/>
-      <c r="BC65" s="28"/>
-      <c r="BD65" s="28"/>
-      <c r="BE65" s="28"/>
-      <c r="BF65" s="28"/>
-      <c r="BG65" s="28"/>
-      <c r="BH65" s="28"/>
-      <c r="BI65" s="28"/>
-      <c r="BJ65" s="28"/>
-      <c r="BK65" s="28"/>
-      <c r="BL65" s="28"/>
+      <c r="A65" s="40"/>
+      <c r="B65" s="130" t="s">
+        <v>85</v>
+      </c>
+      <c r="C65" s="50"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="94"/>
+      <c r="H65" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="26"/>
+      <c r="S65" s="26"/>
+      <c r="T65" s="26"/>
+      <c r="U65" s="26"/>
+      <c r="V65" s="26"/>
+      <c r="W65" s="26"/>
+      <c r="X65" s="26"/>
+      <c r="Y65" s="26"/>
+      <c r="Z65" s="26"/>
+      <c r="AA65" s="26"/>
+      <c r="AB65" s="26"/>
+      <c r="AC65" s="97"/>
+      <c r="AD65" s="97"/>
+      <c r="AE65" s="26"/>
+      <c r="AF65" s="26"/>
+      <c r="AG65" s="26"/>
+      <c r="AH65" s="26"/>
+      <c r="AI65" s="26"/>
+      <c r="AJ65" s="26"/>
+      <c r="AK65" s="26"/>
+      <c r="AL65" s="26"/>
+      <c r="AM65" s="26"/>
+      <c r="AN65" s="26"/>
+      <c r="AO65" s="26"/>
+      <c r="AP65" s="26"/>
+      <c r="AQ65" s="26"/>
+      <c r="AR65" s="26"/>
+      <c r="AS65" s="26"/>
+      <c r="AT65" s="26"/>
+      <c r="AU65" s="26"/>
+      <c r="AV65" s="26"/>
+      <c r="AW65" s="26"/>
+      <c r="AX65" s="26"/>
+      <c r="AY65" s="26"/>
+      <c r="AZ65" s="26"/>
+      <c r="BA65" s="26"/>
+      <c r="BB65" s="26"/>
+      <c r="BC65" s="26"/>
+      <c r="BD65" s="26"/>
+      <c r="BE65" s="26"/>
+      <c r="BF65" s="26"/>
+      <c r="BG65" s="26"/>
+      <c r="BH65" s="26"/>
+      <c r="BI65" s="26"/>
+      <c r="BJ65" s="26"/>
+      <c r="BK65" s="26"/>
+      <c r="BL65" s="26"/>
+      <c r="BM65" s="26"/>
+      <c r="BN65" s="26"/>
+      <c r="BO65" s="26"/>
+      <c r="BP65" s="26"/>
+      <c r="BQ65" s="67"/>
+      <c r="BR65" s="67"/>
+      <c r="BS65" s="67"/>
+      <c r="BT65" s="67"/>
+      <c r="BU65" s="67"/>
+      <c r="BV65" s="67"/>
+      <c r="BW65" s="67"/>
+      <c r="BX65" s="67"/>
+      <c r="BY65" s="67"/>
+      <c r="BZ65" s="67"/>
+      <c r="CA65" s="67"/>
+      <c r="CB65" s="67"/>
+      <c r="CC65" s="67"/>
+      <c r="CD65" s="67"/>
+      <c r="CE65" s="67"/>
+      <c r="CF65" s="67"/>
+      <c r="CG65" s="67"/>
       <c r="CH65"/>
       <c r="CI65"/>
       <c r="CJ65"/>
@@ -10923,21 +11078,995 @@
       <c r="DP65"/>
       <c r="DQ65"/>
     </row>
-    <row r="66" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G66" s="6"/>
-    </row>
-    <row r="67" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C67" s="11"/>
-      <c r="F67" s="42"/>
-    </row>
-    <row r="68" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C68" s="12"/>
+    <row r="66" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B66" s="83"/>
+      <c r="C66" s="84"/>
+      <c r="D66" s="85"/>
+      <c r="E66" s="86"/>
+      <c r="F66" s="87"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="26"/>
+      <c r="Q66" s="26"/>
+      <c r="R66" s="26"/>
+      <c r="S66" s="26"/>
+      <c r="T66" s="26"/>
+      <c r="U66" s="26"/>
+      <c r="V66" s="26"/>
+      <c r="W66" s="26"/>
+      <c r="X66" s="26"/>
+      <c r="Y66" s="26"/>
+      <c r="Z66" s="26"/>
+      <c r="AA66" s="26"/>
+      <c r="AB66" s="67"/>
+      <c r="AC66" s="67"/>
+      <c r="AD66" s="67"/>
+      <c r="AE66" s="26"/>
+      <c r="AF66" s="26"/>
+      <c r="AG66" s="26"/>
+      <c r="AH66" s="26"/>
+      <c r="AI66" s="26"/>
+      <c r="AJ66" s="26"/>
+      <c r="AK66" s="26"/>
+      <c r="AL66" s="26"/>
+      <c r="AM66" s="26"/>
+      <c r="AN66" s="26"/>
+      <c r="AO66" s="26"/>
+      <c r="AP66" s="26"/>
+      <c r="AQ66" s="26"/>
+      <c r="AR66" s="26"/>
+      <c r="AS66" s="26"/>
+      <c r="AT66" s="26"/>
+      <c r="AU66" s="26"/>
+      <c r="AV66" s="26"/>
+      <c r="AW66" s="26"/>
+      <c r="AX66" s="26"/>
+      <c r="AY66" s="26"/>
+      <c r="AZ66" s="26"/>
+      <c r="BA66" s="26"/>
+      <c r="BB66" s="26"/>
+      <c r="BC66" s="26"/>
+      <c r="BD66" s="26"/>
+      <c r="BE66" s="26"/>
+      <c r="BF66" s="26"/>
+      <c r="BG66" s="26"/>
+      <c r="BH66" s="26"/>
+      <c r="BI66" s="26"/>
+      <c r="BJ66" s="26"/>
+      <c r="BK66" s="26"/>
+      <c r="BL66" s="26"/>
+      <c r="BM66" s="26"/>
+      <c r="BN66" s="26"/>
+      <c r="BO66" s="26"/>
+      <c r="BP66" s="26"/>
+      <c r="BQ66" s="67"/>
+      <c r="BR66" s="67"/>
+      <c r="BS66" s="67"/>
+      <c r="BT66" s="67"/>
+      <c r="BU66" s="67"/>
+      <c r="BV66" s="67"/>
+      <c r="BW66" s="67"/>
+      <c r="BX66" s="67"/>
+      <c r="BY66" s="67"/>
+      <c r="BZ66" s="67"/>
+      <c r="CA66" s="67"/>
+      <c r="CB66" s="67"/>
+      <c r="CC66" s="67"/>
+      <c r="CD66" s="67"/>
+      <c r="CE66" s="67"/>
+      <c r="CF66" s="67"/>
+      <c r="CG66" s="67"/>
+      <c r="CH66"/>
+      <c r="CI66"/>
+      <c r="CJ66"/>
+      <c r="CK66"/>
+      <c r="CL66"/>
+      <c r="CM66"/>
+      <c r="CN66"/>
+      <c r="CO66"/>
+      <c r="CP66"/>
+      <c r="CQ66"/>
+      <c r="CR66"/>
+      <c r="CS66"/>
+      <c r="CT66"/>
+      <c r="CU66"/>
+      <c r="CV66"/>
+      <c r="CW66"/>
+      <c r="CX66"/>
+      <c r="CY66"/>
+      <c r="CZ66"/>
+      <c r="DA66"/>
+      <c r="DB66"/>
+      <c r="DC66"/>
+      <c r="DD66"/>
+      <c r="DE66"/>
+      <c r="DF66"/>
+      <c r="DG66"/>
+      <c r="DH66"/>
+      <c r="DI66"/>
+      <c r="DJ66"/>
+      <c r="DK66"/>
+      <c r="DL66"/>
+      <c r="DM66"/>
+      <c r="DN66"/>
+      <c r="DO66"/>
+      <c r="DP66"/>
+      <c r="DQ66"/>
+    </row>
+    <row r="67" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="40"/>
+      <c r="B67" s="88"/>
+      <c r="C67" s="84"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="89"/>
+      <c r="F67" s="89"/>
+      <c r="G67" s="14"/>
+      <c r="H67" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I67" s="26"/>
+      <c r="J67" s="26"/>
+      <c r="K67" s="26"/>
+      <c r="L67" s="26"/>
+      <c r="M67" s="26"/>
+      <c r="N67" s="26"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="26"/>
+      <c r="Q67" s="26"/>
+      <c r="R67" s="26"/>
+      <c r="S67" s="26"/>
+      <c r="T67" s="26"/>
+      <c r="U67" s="26"/>
+      <c r="V67" s="26"/>
+      <c r="W67" s="26"/>
+      <c r="X67" s="26"/>
+      <c r="Y67" s="26"/>
+      <c r="Z67" s="26"/>
+      <c r="AA67" s="26"/>
+      <c r="AB67" s="26"/>
+      <c r="AC67" s="26"/>
+      <c r="AD67" s="26"/>
+      <c r="AE67" s="26"/>
+      <c r="AF67" s="26"/>
+      <c r="AG67" s="26"/>
+      <c r="AH67" s="26"/>
+      <c r="AI67" s="26"/>
+      <c r="AJ67" s="26"/>
+      <c r="AK67" s="26"/>
+      <c r="AL67" s="26"/>
+      <c r="AM67" s="26"/>
+      <c r="AN67" s="26"/>
+      <c r="AO67" s="26"/>
+      <c r="AP67" s="26"/>
+      <c r="AQ67" s="26"/>
+      <c r="AR67" s="26"/>
+      <c r="AS67" s="26"/>
+      <c r="AT67" s="26"/>
+      <c r="AU67" s="26"/>
+      <c r="AV67" s="26"/>
+      <c r="AW67" s="26"/>
+      <c r="AX67" s="26"/>
+      <c r="AY67" s="26"/>
+      <c r="AZ67" s="26"/>
+      <c r="BA67" s="26"/>
+      <c r="BB67" s="26"/>
+      <c r="BC67" s="26"/>
+      <c r="BD67" s="26"/>
+      <c r="BE67" s="26"/>
+      <c r="BF67" s="26"/>
+      <c r="BG67" s="26"/>
+      <c r="BH67" s="26"/>
+      <c r="BI67" s="26"/>
+      <c r="BJ67" s="26"/>
+      <c r="BK67" s="26"/>
+      <c r="BL67" s="26"/>
+      <c r="BM67" s="26"/>
+      <c r="BN67" s="26"/>
+      <c r="BO67" s="26"/>
+      <c r="BP67" s="26"/>
+      <c r="BQ67" s="26"/>
+      <c r="BR67" s="26"/>
+      <c r="BS67" s="26"/>
+      <c r="BT67" s="26"/>
+      <c r="BU67" s="26"/>
+      <c r="BV67" s="26"/>
+      <c r="BW67" s="26"/>
+      <c r="BX67" s="26"/>
+      <c r="BY67" s="26"/>
+      <c r="BZ67" s="26"/>
+      <c r="CA67" s="26"/>
+      <c r="CB67" s="26"/>
+      <c r="CC67" s="26"/>
+      <c r="CD67" s="26"/>
+      <c r="CE67" s="26"/>
+      <c r="CF67" s="26"/>
+      <c r="CG67" s="26"/>
+      <c r="CH67"/>
+      <c r="CI67"/>
+      <c r="CJ67"/>
+      <c r="CK67"/>
+      <c r="CL67"/>
+      <c r="CM67"/>
+      <c r="CN67"/>
+      <c r="CO67"/>
+      <c r="CP67"/>
+      <c r="CQ67"/>
+      <c r="CR67"/>
+      <c r="CS67"/>
+      <c r="CT67"/>
+      <c r="CU67"/>
+      <c r="CV67"/>
+      <c r="CW67"/>
+      <c r="CX67"/>
+      <c r="CY67"/>
+      <c r="CZ67"/>
+      <c r="DA67"/>
+      <c r="DB67"/>
+      <c r="DC67"/>
+      <c r="DD67"/>
+      <c r="DE67"/>
+      <c r="DF67"/>
+      <c r="DG67"/>
+      <c r="DH67"/>
+      <c r="DI67"/>
+      <c r="DJ67"/>
+      <c r="DK67"/>
+      <c r="DL67"/>
+      <c r="DM67"/>
+      <c r="DN67"/>
+      <c r="DO67"/>
+      <c r="DP67"/>
+      <c r="DQ67"/>
+    </row>
+    <row r="68" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="40"/>
+      <c r="B68" s="88"/>
+      <c r="C68" s="84"/>
+      <c r="D68" s="85"/>
+      <c r="E68" s="89"/>
+      <c r="F68" s="89"/>
+      <c r="G68" s="14"/>
+      <c r="H68" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I68" s="26"/>
+      <c r="J68" s="26"/>
+      <c r="K68" s="26"/>
+      <c r="L68" s="26"/>
+      <c r="M68" s="26"/>
+      <c r="N68" s="26"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="26"/>
+      <c r="Q68" s="26"/>
+      <c r="R68" s="26"/>
+      <c r="S68" s="26"/>
+      <c r="T68" s="26"/>
+      <c r="U68" s="26"/>
+      <c r="V68" s="26"/>
+      <c r="W68" s="26"/>
+      <c r="X68" s="26"/>
+      <c r="Y68" s="26"/>
+      <c r="Z68" s="26"/>
+      <c r="AA68" s="26"/>
+      <c r="AB68" s="26"/>
+      <c r="AC68" s="26"/>
+      <c r="AD68" s="26"/>
+      <c r="AE68" s="26"/>
+      <c r="AF68" s="26"/>
+      <c r="AG68" s="26"/>
+      <c r="AH68" s="26"/>
+      <c r="AI68" s="26"/>
+      <c r="AJ68" s="26"/>
+      <c r="AK68" s="26"/>
+      <c r="AL68" s="26"/>
+      <c r="AM68" s="26"/>
+      <c r="AN68" s="26"/>
+      <c r="AO68" s="26"/>
+      <c r="AP68" s="26"/>
+      <c r="AQ68" s="26"/>
+      <c r="AR68" s="26"/>
+      <c r="AS68" s="26"/>
+      <c r="AT68" s="26"/>
+      <c r="AU68" s="26"/>
+      <c r="AV68" s="26"/>
+      <c r="AW68" s="26"/>
+      <c r="AX68" s="26"/>
+      <c r="AY68" s="26"/>
+      <c r="AZ68" s="26"/>
+      <c r="BA68" s="26"/>
+      <c r="BB68" s="26"/>
+      <c r="BC68" s="26"/>
+      <c r="BD68" s="26"/>
+      <c r="BE68" s="26"/>
+      <c r="BF68" s="26"/>
+      <c r="BG68" s="26"/>
+      <c r="BH68" s="26"/>
+      <c r="BI68" s="26"/>
+      <c r="BJ68" s="26"/>
+      <c r="BK68" s="26"/>
+      <c r="BL68" s="26"/>
+      <c r="BM68" s="26"/>
+      <c r="BN68" s="26"/>
+      <c r="BO68" s="26"/>
+      <c r="BP68" s="26"/>
+      <c r="BQ68" s="26"/>
+      <c r="BR68" s="26"/>
+      <c r="BS68" s="26"/>
+      <c r="BT68" s="26"/>
+      <c r="BU68" s="26"/>
+      <c r="BV68" s="26"/>
+      <c r="BW68" s="26"/>
+      <c r="BX68" s="26"/>
+      <c r="BY68" s="26"/>
+      <c r="BZ68" s="26"/>
+      <c r="CA68" s="26"/>
+      <c r="CB68" s="26"/>
+      <c r="CC68" s="26"/>
+      <c r="CD68" s="26"/>
+      <c r="CE68" s="26"/>
+      <c r="CF68" s="26"/>
+      <c r="CG68" s="26"/>
+      <c r="CH68"/>
+      <c r="CI68"/>
+      <c r="CJ68"/>
+      <c r="CK68"/>
+      <c r="CL68"/>
+      <c r="CM68"/>
+      <c r="CN68"/>
+      <c r="CO68"/>
+      <c r="CP68"/>
+      <c r="CQ68"/>
+      <c r="CR68"/>
+      <c r="CS68"/>
+      <c r="CT68"/>
+      <c r="CU68"/>
+      <c r="CV68"/>
+      <c r="CW68"/>
+      <c r="CX68"/>
+      <c r="CY68"/>
+      <c r="CZ68"/>
+      <c r="DA68"/>
+      <c r="DB68"/>
+      <c r="DC68"/>
+      <c r="DD68"/>
+      <c r="DE68"/>
+      <c r="DF68"/>
+      <c r="DG68"/>
+      <c r="DH68"/>
+      <c r="DI68"/>
+      <c r="DJ68"/>
+      <c r="DK68"/>
+      <c r="DL68"/>
+      <c r="DM68"/>
+      <c r="DN68"/>
+      <c r="DO68"/>
+      <c r="DP68"/>
+      <c r="DQ68"/>
+    </row>
+    <row r="69" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="40"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="84"/>
+      <c r="D69" s="85"/>
+      <c r="E69" s="89"/>
+      <c r="F69" s="89"/>
+      <c r="G69" s="14"/>
+      <c r="H69" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="26"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="26"/>
+      <c r="Q69" s="26"/>
+      <c r="R69" s="26"/>
+      <c r="S69" s="26"/>
+      <c r="T69" s="26"/>
+      <c r="U69" s="26"/>
+      <c r="V69" s="26"/>
+      <c r="W69" s="26"/>
+      <c r="X69" s="26"/>
+      <c r="Y69" s="26"/>
+      <c r="Z69" s="26"/>
+      <c r="AA69" s="26"/>
+      <c r="AB69" s="26"/>
+      <c r="AC69" s="26"/>
+      <c r="AD69" s="26"/>
+      <c r="AE69" s="26"/>
+      <c r="AF69" s="26"/>
+      <c r="AG69" s="26"/>
+      <c r="AH69" s="26"/>
+      <c r="AI69" s="26"/>
+      <c r="AJ69" s="26"/>
+      <c r="AK69" s="26"/>
+      <c r="AL69" s="26"/>
+      <c r="AM69" s="26"/>
+      <c r="AN69" s="26"/>
+      <c r="AO69" s="26"/>
+      <c r="AP69" s="26"/>
+      <c r="AQ69" s="26"/>
+      <c r="AR69" s="26"/>
+      <c r="AS69" s="26"/>
+      <c r="AT69" s="26"/>
+      <c r="AU69" s="26"/>
+      <c r="AV69" s="26"/>
+      <c r="AW69" s="26"/>
+      <c r="AX69" s="26"/>
+      <c r="AY69" s="26"/>
+      <c r="AZ69" s="26"/>
+      <c r="BA69" s="26"/>
+      <c r="BB69" s="26"/>
+      <c r="BC69" s="26"/>
+      <c r="BD69" s="26"/>
+      <c r="BE69" s="26"/>
+      <c r="BF69" s="26"/>
+      <c r="BG69" s="26"/>
+      <c r="BH69" s="26"/>
+      <c r="BI69" s="26"/>
+      <c r="BJ69" s="26"/>
+      <c r="BK69" s="26"/>
+      <c r="BL69" s="26"/>
+      <c r="BM69" s="26"/>
+      <c r="BN69" s="26"/>
+      <c r="BO69" s="26"/>
+      <c r="BP69" s="26"/>
+      <c r="BQ69" s="26"/>
+      <c r="BR69" s="26"/>
+      <c r="BS69" s="26"/>
+      <c r="BT69" s="26"/>
+      <c r="BU69" s="26"/>
+      <c r="BV69" s="26"/>
+      <c r="BW69" s="26"/>
+      <c r="BX69" s="26"/>
+      <c r="BY69" s="26"/>
+      <c r="BZ69" s="26"/>
+      <c r="CA69" s="26"/>
+      <c r="CB69" s="26"/>
+      <c r="CC69" s="26"/>
+      <c r="CD69" s="26"/>
+      <c r="CE69" s="26"/>
+      <c r="CF69" s="26"/>
+      <c r="CG69" s="26"/>
+      <c r="CH69"/>
+      <c r="CI69"/>
+      <c r="CJ69"/>
+      <c r="CK69"/>
+      <c r="CL69"/>
+      <c r="CM69"/>
+      <c r="CN69"/>
+      <c r="CO69"/>
+      <c r="CP69"/>
+      <c r="CQ69"/>
+      <c r="CR69"/>
+      <c r="CS69"/>
+      <c r="CT69"/>
+      <c r="CU69"/>
+      <c r="CV69"/>
+      <c r="CW69"/>
+      <c r="CX69"/>
+      <c r="CY69"/>
+      <c r="CZ69"/>
+      <c r="DA69"/>
+      <c r="DB69"/>
+      <c r="DC69"/>
+      <c r="DD69"/>
+      <c r="DE69"/>
+      <c r="DF69"/>
+      <c r="DG69"/>
+      <c r="DH69"/>
+      <c r="DI69"/>
+      <c r="DJ69"/>
+      <c r="DK69"/>
+      <c r="DL69"/>
+      <c r="DM69"/>
+      <c r="DN69"/>
+      <c r="DO69"/>
+      <c r="DP69"/>
+      <c r="DQ69"/>
+    </row>
+    <row r="70" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="40"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="84"/>
+      <c r="D70" s="85"/>
+      <c r="E70" s="89"/>
+      <c r="F70" s="89"/>
+      <c r="G70" s="14"/>
+      <c r="H70" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="26"/>
+      <c r="S70" s="26"/>
+      <c r="T70" s="26"/>
+      <c r="U70" s="26"/>
+      <c r="V70" s="26"/>
+      <c r="W70" s="26"/>
+      <c r="X70" s="26"/>
+      <c r="Y70" s="26"/>
+      <c r="Z70" s="26"/>
+      <c r="AA70" s="26"/>
+      <c r="AB70" s="26"/>
+      <c r="AC70" s="26"/>
+      <c r="AD70" s="26"/>
+      <c r="AE70" s="26"/>
+      <c r="AF70" s="26"/>
+      <c r="AG70" s="26"/>
+      <c r="AH70" s="26"/>
+      <c r="AI70" s="26"/>
+      <c r="AJ70" s="26"/>
+      <c r="AK70" s="26"/>
+      <c r="AL70" s="26"/>
+      <c r="AM70" s="26"/>
+      <c r="AN70" s="26"/>
+      <c r="AO70" s="26"/>
+      <c r="AP70" s="26"/>
+      <c r="AQ70" s="26"/>
+      <c r="AR70" s="26"/>
+      <c r="AS70" s="26"/>
+      <c r="AT70" s="26"/>
+      <c r="AU70" s="26"/>
+      <c r="AV70" s="26"/>
+      <c r="AW70" s="26"/>
+      <c r="AX70" s="26"/>
+      <c r="AY70" s="26"/>
+      <c r="AZ70" s="26"/>
+      <c r="BA70" s="26"/>
+      <c r="BB70" s="26"/>
+      <c r="BC70" s="26"/>
+      <c r="BD70" s="26"/>
+      <c r="BE70" s="26"/>
+      <c r="BF70" s="26"/>
+      <c r="BG70" s="26"/>
+      <c r="BH70" s="26"/>
+      <c r="BI70" s="26"/>
+      <c r="BJ70" s="26"/>
+      <c r="BK70" s="26"/>
+      <c r="BL70" s="26"/>
+      <c r="BM70" s="26"/>
+      <c r="BN70" s="26"/>
+      <c r="BO70" s="26"/>
+      <c r="BP70" s="26"/>
+      <c r="BQ70" s="26"/>
+      <c r="BR70" s="26"/>
+      <c r="BS70" s="26"/>
+      <c r="BT70" s="26"/>
+      <c r="BU70" s="26"/>
+      <c r="BV70" s="26"/>
+      <c r="BW70" s="26"/>
+      <c r="BX70" s="26"/>
+      <c r="BY70" s="26"/>
+      <c r="BZ70" s="26"/>
+      <c r="CA70" s="26"/>
+      <c r="CB70" s="26"/>
+      <c r="CC70" s="26"/>
+      <c r="CD70" s="26"/>
+      <c r="CE70" s="26"/>
+      <c r="CF70" s="26"/>
+      <c r="CG70" s="26"/>
+      <c r="CH70"/>
+      <c r="CI70"/>
+      <c r="CJ70"/>
+      <c r="CK70"/>
+      <c r="CL70"/>
+      <c r="CM70"/>
+      <c r="CN70"/>
+      <c r="CO70"/>
+      <c r="CP70"/>
+      <c r="CQ70"/>
+      <c r="CR70"/>
+      <c r="CS70"/>
+      <c r="CT70"/>
+      <c r="CU70"/>
+      <c r="CV70"/>
+      <c r="CW70"/>
+      <c r="CX70"/>
+      <c r="CY70"/>
+      <c r="CZ70"/>
+      <c r="DA70"/>
+      <c r="DB70"/>
+      <c r="DC70"/>
+      <c r="DD70"/>
+      <c r="DE70"/>
+      <c r="DF70"/>
+      <c r="DG70"/>
+      <c r="DH70"/>
+      <c r="DI70"/>
+      <c r="DJ70"/>
+      <c r="DK70"/>
+      <c r="DL70"/>
+      <c r="DM70"/>
+      <c r="DN70"/>
+      <c r="DO70"/>
+      <c r="DP70"/>
+      <c r="DQ70"/>
+    </row>
+    <row r="71" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="40"/>
+      <c r="B71" s="88"/>
+      <c r="C71" s="84"/>
+      <c r="D71" s="85"/>
+      <c r="E71" s="89"/>
+      <c r="F71" s="89"/>
+      <c r="G71" s="14"/>
+      <c r="H71" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="26"/>
+      <c r="U71" s="26"/>
+      <c r="V71" s="26"/>
+      <c r="W71" s="26"/>
+      <c r="X71" s="26"/>
+      <c r="Y71" s="26"/>
+      <c r="Z71" s="26"/>
+      <c r="AA71" s="26"/>
+      <c r="AB71" s="26"/>
+      <c r="AC71" s="26"/>
+      <c r="AD71" s="26"/>
+      <c r="AE71" s="26"/>
+      <c r="AF71" s="26"/>
+      <c r="AG71" s="26"/>
+      <c r="AH71" s="26"/>
+      <c r="AI71" s="26"/>
+      <c r="AJ71" s="26"/>
+      <c r="AK71" s="26"/>
+      <c r="AL71" s="26"/>
+      <c r="AM71" s="26"/>
+      <c r="AN71" s="26"/>
+      <c r="AO71" s="26"/>
+      <c r="AP71" s="26"/>
+      <c r="AQ71" s="26"/>
+      <c r="AR71" s="26"/>
+      <c r="AS71" s="26"/>
+      <c r="AT71" s="26"/>
+      <c r="AU71" s="26"/>
+      <c r="AV71" s="26"/>
+      <c r="AW71" s="26"/>
+      <c r="AX71" s="26"/>
+      <c r="AY71" s="26"/>
+      <c r="AZ71" s="26"/>
+      <c r="BA71" s="26"/>
+      <c r="BB71" s="26"/>
+      <c r="BC71" s="26"/>
+      <c r="BD71" s="26"/>
+      <c r="BE71" s="26"/>
+      <c r="BF71" s="26"/>
+      <c r="BG71" s="26"/>
+      <c r="BH71" s="26"/>
+      <c r="BI71" s="26"/>
+      <c r="BJ71" s="26"/>
+      <c r="BK71" s="26"/>
+      <c r="BL71" s="26"/>
+      <c r="BM71" s="26"/>
+      <c r="BN71" s="26"/>
+      <c r="BO71" s="26"/>
+      <c r="BP71" s="26"/>
+      <c r="BQ71" s="26"/>
+      <c r="BR71" s="26"/>
+      <c r="BS71" s="26"/>
+      <c r="BT71" s="26"/>
+      <c r="BU71" s="26"/>
+      <c r="BV71" s="26"/>
+      <c r="BW71" s="26"/>
+      <c r="BX71" s="26"/>
+      <c r="BY71" s="26"/>
+      <c r="BZ71" s="26"/>
+      <c r="CA71" s="26"/>
+      <c r="CB71" s="26"/>
+      <c r="CC71" s="26"/>
+      <c r="CD71" s="26"/>
+      <c r="CE71" s="26"/>
+      <c r="CF71" s="26"/>
+      <c r="CG71" s="26"/>
+      <c r="CH71"/>
+      <c r="CI71"/>
+      <c r="CJ71"/>
+      <c r="CK71"/>
+      <c r="CL71"/>
+      <c r="CM71"/>
+      <c r="CN71"/>
+      <c r="CO71"/>
+      <c r="CP71"/>
+      <c r="CQ71"/>
+      <c r="CR71"/>
+      <c r="CS71"/>
+      <c r="CT71"/>
+      <c r="CU71"/>
+      <c r="CV71"/>
+      <c r="CW71"/>
+      <c r="CX71"/>
+      <c r="CY71"/>
+      <c r="CZ71"/>
+      <c r="DA71"/>
+      <c r="DB71"/>
+      <c r="DC71"/>
+      <c r="DD71"/>
+      <c r="DE71"/>
+      <c r="DF71"/>
+      <c r="DG71"/>
+      <c r="DH71"/>
+      <c r="DI71"/>
+      <c r="DJ71"/>
+      <c r="DK71"/>
+      <c r="DL71"/>
+      <c r="DM71"/>
+      <c r="DN71"/>
+      <c r="DO71"/>
+      <c r="DP71"/>
+      <c r="DQ71"/>
+    </row>
+    <row r="72" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" s="53"/>
+      <c r="C72" s="51"/>
+      <c r="D72" s="13"/>
+      <c r="E72" s="66"/>
+      <c r="F72" s="66"/>
+      <c r="G72" s="14"/>
+      <c r="H72" s="14" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
+      <c r="S72" s="26"/>
+      <c r="T72" s="26"/>
+      <c r="U72" s="26"/>
+      <c r="V72" s="26"/>
+      <c r="W72" s="26"/>
+      <c r="X72" s="26"/>
+      <c r="Y72" s="26"/>
+      <c r="Z72" s="26"/>
+      <c r="AA72" s="26"/>
+      <c r="AB72" s="26"/>
+      <c r="AC72" s="26"/>
+      <c r="AD72" s="26"/>
+      <c r="AE72" s="26"/>
+      <c r="AF72" s="26"/>
+      <c r="AG72" s="26"/>
+      <c r="AH72" s="26"/>
+      <c r="AI72" s="26"/>
+      <c r="AJ72" s="26"/>
+      <c r="AK72" s="26"/>
+      <c r="AL72" s="26"/>
+      <c r="AM72" s="26"/>
+      <c r="AN72" s="26"/>
+      <c r="AO72" s="26"/>
+      <c r="AP72" s="26"/>
+      <c r="AQ72" s="26"/>
+      <c r="AR72" s="26"/>
+      <c r="AS72" s="26"/>
+      <c r="AT72" s="26"/>
+      <c r="AU72" s="26"/>
+      <c r="AV72" s="26"/>
+      <c r="AW72" s="26"/>
+      <c r="AX72" s="26"/>
+      <c r="AY72" s="26"/>
+      <c r="AZ72" s="26"/>
+      <c r="BA72" s="26"/>
+      <c r="BB72" s="26"/>
+      <c r="BC72" s="26"/>
+      <c r="BD72" s="26"/>
+      <c r="BE72" s="26"/>
+      <c r="BF72" s="26"/>
+      <c r="BG72" s="26"/>
+      <c r="BH72" s="26"/>
+      <c r="BI72" s="26"/>
+      <c r="BJ72" s="26"/>
+      <c r="BK72" s="26"/>
+      <c r="BL72" s="26"/>
+      <c r="CH72"/>
+      <c r="CI72"/>
+      <c r="CJ72"/>
+      <c r="CK72"/>
+      <c r="CL72"/>
+      <c r="CM72"/>
+      <c r="CN72"/>
+      <c r="CO72"/>
+      <c r="CP72"/>
+      <c r="CQ72"/>
+      <c r="CR72"/>
+      <c r="CS72"/>
+      <c r="CT72"/>
+      <c r="CU72"/>
+      <c r="CV72"/>
+      <c r="CW72"/>
+      <c r="CX72"/>
+      <c r="CY72"/>
+      <c r="CZ72"/>
+      <c r="DA72"/>
+      <c r="DB72"/>
+      <c r="DC72"/>
+      <c r="DD72"/>
+      <c r="DE72"/>
+      <c r="DF72"/>
+      <c r="DG72"/>
+      <c r="DH72"/>
+      <c r="DI72"/>
+      <c r="DJ72"/>
+      <c r="DK72"/>
+      <c r="DL72"/>
+      <c r="DM72"/>
+      <c r="DN72"/>
+      <c r="DO72"/>
+      <c r="DP72"/>
+      <c r="DQ72"/>
+    </row>
+    <row r="73" spans="1:121" s="3" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="41"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="23"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="61"/>
+      <c r="F73" s="62"/>
+      <c r="G73" s="25"/>
+      <c r="H73" s="25"/>
+      <c r="I73" s="28"/>
+      <c r="J73" s="28"/>
+      <c r="K73" s="28"/>
+      <c r="L73" s="28"/>
+      <c r="M73" s="28"/>
+      <c r="N73" s="28"/>
+      <c r="O73" s="28"/>
+      <c r="P73" s="28"/>
+      <c r="Q73" s="28"/>
+      <c r="R73" s="28"/>
+      <c r="S73" s="28"/>
+      <c r="T73" s="28"/>
+      <c r="U73" s="28"/>
+      <c r="V73" s="28"/>
+      <c r="W73" s="28"/>
+      <c r="X73" s="28"/>
+      <c r="Y73" s="28"/>
+      <c r="Z73" s="28"/>
+      <c r="AA73" s="28"/>
+      <c r="AB73" s="28"/>
+      <c r="AC73" s="28"/>
+      <c r="AD73" s="28"/>
+      <c r="AE73" s="28"/>
+      <c r="AF73" s="28"/>
+      <c r="AG73" s="28"/>
+      <c r="AH73" s="28"/>
+      <c r="AI73" s="28"/>
+      <c r="AJ73" s="28"/>
+      <c r="AK73" s="28"/>
+      <c r="AL73" s="28"/>
+      <c r="AM73" s="28"/>
+      <c r="AN73" s="28"/>
+      <c r="AO73" s="28"/>
+      <c r="AP73" s="28"/>
+      <c r="AQ73" s="28"/>
+      <c r="AR73" s="28"/>
+      <c r="AS73" s="28"/>
+      <c r="AT73" s="28"/>
+      <c r="AU73" s="28"/>
+      <c r="AV73" s="28"/>
+      <c r="AW73" s="28"/>
+      <c r="AX73" s="28"/>
+      <c r="AY73" s="28"/>
+      <c r="AZ73" s="28"/>
+      <c r="BA73" s="28"/>
+      <c r="BB73" s="28"/>
+      <c r="BC73" s="28"/>
+      <c r="BD73" s="28"/>
+      <c r="BE73" s="28"/>
+      <c r="BF73" s="28"/>
+      <c r="BG73" s="28"/>
+      <c r="BH73" s="28"/>
+      <c r="BI73" s="28"/>
+      <c r="BJ73" s="28"/>
+      <c r="BK73" s="28"/>
+      <c r="BL73" s="28"/>
+      <c r="CH73"/>
+      <c r="CI73"/>
+      <c r="CJ73"/>
+      <c r="CK73"/>
+      <c r="CL73"/>
+      <c r="CM73"/>
+      <c r="CN73"/>
+      <c r="CO73"/>
+      <c r="CP73"/>
+      <c r="CQ73"/>
+      <c r="CR73"/>
+      <c r="CS73"/>
+      <c r="CT73"/>
+      <c r="CU73"/>
+      <c r="CV73"/>
+      <c r="CW73"/>
+      <c r="CX73"/>
+      <c r="CY73"/>
+      <c r="CZ73"/>
+      <c r="DA73"/>
+      <c r="DB73"/>
+      <c r="DC73"/>
+      <c r="DD73"/>
+      <c r="DE73"/>
+      <c r="DF73"/>
+      <c r="DG73"/>
+      <c r="DH73"/>
+      <c r="DI73"/>
+      <c r="DJ73"/>
+      <c r="DK73"/>
+      <c r="DL73"/>
+      <c r="DM73"/>
+      <c r="DN73"/>
+      <c r="DO73"/>
+      <c r="DP73"/>
+      <c r="DQ73"/>
+    </row>
+    <row r="74" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G74" s="6"/>
+    </row>
+    <row r="75" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C75" s="11"/>
+      <c r="F75" s="42"/>
+    </row>
+    <row r="76" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C76" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I3:O3"/>
     <mergeCell ref="I7:CG7"/>
-    <mergeCell ref="I31:CG31"/>
-    <mergeCell ref="I52:CG52"/>
+    <mergeCell ref="I36:CG36"/>
+    <mergeCell ref="I59:CG59"/>
     <mergeCell ref="BS3:BW3"/>
     <mergeCell ref="BX3:CB3"/>
     <mergeCell ref="CC3:CG3"/>
@@ -10949,15 +12078,8 @@
     <mergeCell ref="AO3:AS3"/>
     <mergeCell ref="AT3:AX3"/>
     <mergeCell ref="AY3:BC3"/>
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="Z3:AD3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I3:O3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D65">
+  <conditionalFormatting sqref="D6:D73">
     <cfRule type="dataBar" priority="17">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -10971,12 +12093,12 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I4:DP6 I7 CH7:DP7 I31:I32 CH31:DP32 I33:DP51 I52 CH52:DP52 BM53:DP63 I53:BL65 I8:DP30">
+  <conditionalFormatting sqref="I4:DP6 I7 CH7:DP7 I36:I37 CH36:DP37 I38:DP58 I59 CH59:DP59 BM60:DP71 I60:BL73 I8:DP35">
     <cfRule type="expression" dxfId="2" priority="36">
       <formula>AND(TODAY()&gt;=I$4,TODAY()&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I6:DP6 I7 CH7:DP7 I31:I32 CH31:DP32 I33:DP51 I52 CH52:DP52 BM53:DP63 I53:BL65 I8:DP30">
+  <conditionalFormatting sqref="I6:DP6 I7 CH7:DP7 I36:I37 CH36:DP37 I38:DP58 I59 CH59:DP59 BM60:DP71 I60:BL73 I8:DP35">
     <cfRule type="expression" dxfId="1" priority="30">
       <formula>AND(task_start&lt;=I$4,ROUNDDOWN((task_end-task_start+1)*task_progress,0)+task_start-1&gt;=I$4)</formula>
     </cfRule>
@@ -10984,7 +12106,7 @@
       <formula>AND(task_end&gt;=I$4,task_start&lt;J$4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" promptTitle="Mostrar semana" prompt="Al cambiar este número, se desplazará la vista del diagrama de Gantt." sqref="E3" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
     </dataValidation>
@@ -11011,7 +12133,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>D6:D65</xm:sqref>
+          <xm:sqref>D6:D73</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -11030,93 +12152,93 @@
     <row r="1" spans="1:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="75"/>
       <c r="D1" s="81" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="76"/>
       <c r="D2" s="82" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="77"/>
       <c r="D3" s="82" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="78" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D4" s="82" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="81" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" s="82" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D7" s="82" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D8" s="82" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D9" s="82" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D10" s="82" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="82" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="42.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D12" s="81" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D13" s="82" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D14" s="82" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:4" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="79" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -14171,6 +15293,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -14458,36 +15609,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14506,24 +15648,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Capstone/Fase 1/Carta Gantt.xlsx
+++ b/Capstone/Fase 1/Carta Gantt.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFB381AF-FE4D-4D02-930C-1B05A624CA0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A5F67B-6640-40E9-A377-DE20AD1550A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Carta Gatt" sheetId="11" r:id="rId1"/>
@@ -1442,6 +1442,33 @@
     <xf numFmtId="0" fontId="0" fillId="46" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1467,33 +1494,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="8">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="8" applyBorder="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="3" xfId="9">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2101,149 +2101,149 @@
         <v>1</v>
       </c>
       <c r="B2" s="35"/>
-      <c r="C2" s="131" t="s">
+      <c r="C2" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="132"/>
-      <c r="E2" s="133">
+      <c r="D2" s="117"/>
+      <c r="E2" s="121">
         <f>DATE(2025,8,22)</f>
         <v>45891</v>
       </c>
-      <c r="F2" s="133"/>
+      <c r="F2" s="121"/>
     </row>
     <row r="3" spans="1:121" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="131" t="s">
+      <c r="C3" s="116" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="132"/>
+      <c r="D3" s="117"/>
       <c r="E3" s="7">
         <v>1</v>
       </c>
-      <c r="I3" s="128">
+      <c r="I3" s="122">
         <f>I4</f>
         <v>45890</v>
       </c>
-      <c r="J3" s="129"/>
-      <c r="K3" s="129"/>
-      <c r="L3" s="129"/>
-      <c r="M3" s="129"/>
-      <c r="N3" s="129"/>
-      <c r="O3" s="130"/>
-      <c r="P3" s="125">
+      <c r="J3" s="123"/>
+      <c r="K3" s="123"/>
+      <c r="L3" s="123"/>
+      <c r="M3" s="123"/>
+      <c r="N3" s="123"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="118">
         <f>P4</f>
         <v>45901</v>
       </c>
-      <c r="Q3" s="126"/>
-      <c r="R3" s="126"/>
-      <c r="S3" s="126"/>
-      <c r="T3" s="127"/>
-      <c r="U3" s="125">
+      <c r="Q3" s="119"/>
+      <c r="R3" s="119"/>
+      <c r="S3" s="119"/>
+      <c r="T3" s="120"/>
+      <c r="U3" s="118">
         <f>U4</f>
         <v>45908</v>
       </c>
-      <c r="V3" s="126"/>
-      <c r="W3" s="126"/>
-      <c r="X3" s="126"/>
-      <c r="Y3" s="127"/>
-      <c r="Z3" s="125">
+      <c r="V3" s="119"/>
+      <c r="W3" s="119"/>
+      <c r="X3" s="119"/>
+      <c r="Y3" s="120"/>
+      <c r="Z3" s="118">
         <f t="shared" ref="Z3" si="0">Z4</f>
         <v>45915</v>
       </c>
-      <c r="AA3" s="126"/>
-      <c r="AB3" s="126"/>
-      <c r="AC3" s="126"/>
-      <c r="AD3" s="127"/>
-      <c r="AE3" s="128">
+      <c r="AA3" s="119"/>
+      <c r="AB3" s="119"/>
+      <c r="AC3" s="119"/>
+      <c r="AD3" s="120"/>
+      <c r="AE3" s="122">
         <f t="shared" ref="AE3" si="1">AE4</f>
         <v>45922</v>
       </c>
-      <c r="AF3" s="129"/>
-      <c r="AG3" s="129"/>
-      <c r="AH3" s="129"/>
-      <c r="AI3" s="130"/>
-      <c r="AJ3" s="125">
+      <c r="AF3" s="123"/>
+      <c r="AG3" s="123"/>
+      <c r="AH3" s="123"/>
+      <c r="AI3" s="124"/>
+      <c r="AJ3" s="118">
         <f t="shared" ref="AJ3" si="2">AJ4</f>
         <v>45929</v>
       </c>
-      <c r="AK3" s="126"/>
-      <c r="AL3" s="126"/>
-      <c r="AM3" s="126"/>
-      <c r="AN3" s="127"/>
-      <c r="AO3" s="125">
+      <c r="AK3" s="119"/>
+      <c r="AL3" s="119"/>
+      <c r="AM3" s="119"/>
+      <c r="AN3" s="120"/>
+      <c r="AO3" s="118">
         <f>AO4</f>
         <v>45936</v>
       </c>
-      <c r="AP3" s="126"/>
-      <c r="AQ3" s="126"/>
-      <c r="AR3" s="126"/>
-      <c r="AS3" s="127"/>
-      <c r="AT3" s="125">
+      <c r="AP3" s="119"/>
+      <c r="AQ3" s="119"/>
+      <c r="AR3" s="119"/>
+      <c r="AS3" s="120"/>
+      <c r="AT3" s="118">
         <f t="shared" ref="AT3" si="3">AT4</f>
         <v>45943</v>
       </c>
-      <c r="AU3" s="126"/>
-      <c r="AV3" s="126"/>
-      <c r="AW3" s="126"/>
-      <c r="AX3" s="127"/>
-      <c r="AY3" s="125">
+      <c r="AU3" s="119"/>
+      <c r="AV3" s="119"/>
+      <c r="AW3" s="119"/>
+      <c r="AX3" s="120"/>
+      <c r="AY3" s="118">
         <f t="shared" ref="AY3" si="4">AY4</f>
         <v>45950</v>
       </c>
-      <c r="AZ3" s="126"/>
-      <c r="BA3" s="126"/>
-      <c r="BB3" s="126"/>
-      <c r="BC3" s="127"/>
-      <c r="BD3" s="125">
+      <c r="AZ3" s="119"/>
+      <c r="BA3" s="119"/>
+      <c r="BB3" s="119"/>
+      <c r="BC3" s="120"/>
+      <c r="BD3" s="118">
         <f t="shared" ref="BD3" si="5">BD4</f>
         <v>45957</v>
       </c>
-      <c r="BE3" s="126"/>
-      <c r="BF3" s="126"/>
-      <c r="BG3" s="126"/>
-      <c r="BH3" s="127"/>
-      <c r="BI3" s="125">
+      <c r="BE3" s="119"/>
+      <c r="BF3" s="119"/>
+      <c r="BG3" s="119"/>
+      <c r="BH3" s="120"/>
+      <c r="BI3" s="118">
         <f t="shared" ref="BI3" si="6">BI4</f>
         <v>45964</v>
       </c>
-      <c r="BJ3" s="126"/>
-      <c r="BK3" s="126"/>
-      <c r="BL3" s="126"/>
-      <c r="BM3" s="127"/>
-      <c r="BN3" s="125">
+      <c r="BJ3" s="119"/>
+      <c r="BK3" s="119"/>
+      <c r="BL3" s="119"/>
+      <c r="BM3" s="120"/>
+      <c r="BN3" s="118">
         <f t="shared" ref="BN3" si="7">BN4</f>
         <v>45971</v>
       </c>
-      <c r="BO3" s="126"/>
-      <c r="BP3" s="126"/>
-      <c r="BQ3" s="126"/>
-      <c r="BR3" s="127"/>
-      <c r="BS3" s="125">
+      <c r="BO3" s="119"/>
+      <c r="BP3" s="119"/>
+      <c r="BQ3" s="119"/>
+      <c r="BR3" s="120"/>
+      <c r="BS3" s="118">
         <f t="shared" ref="BS3" si="8">BS4</f>
         <v>45978</v>
       </c>
-      <c r="BT3" s="126"/>
-      <c r="BU3" s="126"/>
-      <c r="BV3" s="126"/>
-      <c r="BW3" s="127"/>
-      <c r="BX3" s="125">
+      <c r="BT3" s="119"/>
+      <c r="BU3" s="119"/>
+      <c r="BV3" s="119"/>
+      <c r="BW3" s="120"/>
+      <c r="BX3" s="118">
         <f t="shared" ref="BX3" si="9">BX4</f>
         <v>45985</v>
       </c>
-      <c r="BY3" s="126"/>
-      <c r="BZ3" s="126"/>
-      <c r="CA3" s="126"/>
-      <c r="CB3" s="127"/>
-      <c r="CC3" s="125">
+      <c r="BY3" s="119"/>
+      <c r="BZ3" s="119"/>
+      <c r="CA3" s="119"/>
+      <c r="CB3" s="120"/>
+      <c r="CC3" s="118">
         <f t="shared" ref="CC3" si="10">CC4</f>
         <v>45992</v>
       </c>
-      <c r="CD3" s="126"/>
-      <c r="CE3" s="126"/>
-      <c r="CF3" s="126"/>
-      <c r="CG3" s="127"/>
+      <c r="CD3" s="119"/>
+      <c r="CE3" s="119"/>
+      <c r="CF3" s="119"/>
+      <c r="CG3" s="120"/>
     </row>
     <row r="4" spans="1:121" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="31" t="s">
@@ -3001,83 +3001,83 @@
         <f t="shared" ref="H7:H68" si="17">IF(OR(ISBLANK(task_start),ISBLANK(task_end)),"",task_end-task_start+1)</f>
         <v/>
       </c>
-      <c r="I7" s="116"/>
-      <c r="J7" s="117"/>
-      <c r="K7" s="117"/>
-      <c r="L7" s="117"/>
-      <c r="M7" s="117"/>
-      <c r="N7" s="117"/>
-      <c r="O7" s="117"/>
-      <c r="P7" s="117"/>
-      <c r="Q7" s="117"/>
-      <c r="R7" s="117"/>
-      <c r="S7" s="117"/>
-      <c r="T7" s="117"/>
-      <c r="U7" s="117"/>
-      <c r="V7" s="117"/>
-      <c r="W7" s="117"/>
-      <c r="X7" s="117"/>
-      <c r="Y7" s="117"/>
-      <c r="Z7" s="117"/>
-      <c r="AA7" s="117"/>
-      <c r="AB7" s="117"/>
-      <c r="AC7" s="117"/>
-      <c r="AD7" s="117"/>
-      <c r="AE7" s="117"/>
-      <c r="AF7" s="117"/>
-      <c r="AG7" s="117"/>
-      <c r="AH7" s="117"/>
-      <c r="AI7" s="117"/>
-      <c r="AJ7" s="117"/>
-      <c r="AK7" s="117"/>
-      <c r="AL7" s="117"/>
-      <c r="AM7" s="117"/>
-      <c r="AN7" s="117"/>
-      <c r="AO7" s="117"/>
-      <c r="AP7" s="117"/>
-      <c r="AQ7" s="117"/>
-      <c r="AR7" s="117"/>
-      <c r="AS7" s="117"/>
-      <c r="AT7" s="117"/>
-      <c r="AU7" s="117"/>
-      <c r="AV7" s="117"/>
-      <c r="AW7" s="117"/>
-      <c r="AX7" s="117"/>
-      <c r="AY7" s="117"/>
-      <c r="AZ7" s="117"/>
-      <c r="BA7" s="117"/>
-      <c r="BB7" s="117"/>
-      <c r="BC7" s="117"/>
-      <c r="BD7" s="117"/>
-      <c r="BE7" s="117"/>
-      <c r="BF7" s="117"/>
-      <c r="BG7" s="117"/>
-      <c r="BH7" s="117"/>
-      <c r="BI7" s="117"/>
-      <c r="BJ7" s="117"/>
-      <c r="BK7" s="117"/>
-      <c r="BL7" s="117"/>
-      <c r="BM7" s="117"/>
-      <c r="BN7" s="117"/>
-      <c r="BO7" s="117"/>
-      <c r="BP7" s="117"/>
-      <c r="BQ7" s="117"/>
-      <c r="BR7" s="117"/>
-      <c r="BS7" s="117"/>
-      <c r="BT7" s="117"/>
-      <c r="BU7" s="117"/>
-      <c r="BV7" s="117"/>
-      <c r="BW7" s="117"/>
-      <c r="BX7" s="117"/>
-      <c r="BY7" s="117"/>
-      <c r="BZ7" s="117"/>
-      <c r="CA7" s="117"/>
-      <c r="CB7" s="117"/>
-      <c r="CC7" s="117"/>
-      <c r="CD7" s="117"/>
-      <c r="CE7" s="117"/>
-      <c r="CF7" s="117"/>
-      <c r="CG7" s="118"/>
+      <c r="I7" s="125"/>
+      <c r="J7" s="126"/>
+      <c r="K7" s="126"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
+      <c r="N7" s="126"/>
+      <c r="O7" s="126"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="126"/>
+      <c r="V7" s="126"/>
+      <c r="W7" s="126"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="126"/>
+      <c r="AC7" s="126"/>
+      <c r="AD7" s="126"/>
+      <c r="AE7" s="126"/>
+      <c r="AF7" s="126"/>
+      <c r="AG7" s="126"/>
+      <c r="AH7" s="126"/>
+      <c r="AI7" s="126"/>
+      <c r="AJ7" s="126"/>
+      <c r="AK7" s="126"/>
+      <c r="AL7" s="126"/>
+      <c r="AM7" s="126"/>
+      <c r="AN7" s="126"/>
+      <c r="AO7" s="126"/>
+      <c r="AP7" s="126"/>
+      <c r="AQ7" s="126"/>
+      <c r="AR7" s="126"/>
+      <c r="AS7" s="126"/>
+      <c r="AT7" s="126"/>
+      <c r="AU7" s="126"/>
+      <c r="AV7" s="126"/>
+      <c r="AW7" s="126"/>
+      <c r="AX7" s="126"/>
+      <c r="AY7" s="126"/>
+      <c r="AZ7" s="126"/>
+      <c r="BA7" s="126"/>
+      <c r="BB7" s="126"/>
+      <c r="BC7" s="126"/>
+      <c r="BD7" s="126"/>
+      <c r="BE7" s="126"/>
+      <c r="BF7" s="126"/>
+      <c r="BG7" s="126"/>
+      <c r="BH7" s="126"/>
+      <c r="BI7" s="126"/>
+      <c r="BJ7" s="126"/>
+      <c r="BK7" s="126"/>
+      <c r="BL7" s="126"/>
+      <c r="BM7" s="126"/>
+      <c r="BN7" s="126"/>
+      <c r="BO7" s="126"/>
+      <c r="BP7" s="126"/>
+      <c r="BQ7" s="126"/>
+      <c r="BR7" s="126"/>
+      <c r="BS7" s="126"/>
+      <c r="BT7" s="126"/>
+      <c r="BU7" s="126"/>
+      <c r="BV7" s="126"/>
+      <c r="BW7" s="126"/>
+      <c r="BX7" s="126"/>
+      <c r="BY7" s="126"/>
+      <c r="BZ7" s="126"/>
+      <c r="CA7" s="126"/>
+      <c r="CB7" s="126"/>
+      <c r="CC7" s="126"/>
+      <c r="CD7" s="126"/>
+      <c r="CE7" s="126"/>
+      <c r="CF7" s="126"/>
+      <c r="CG7" s="127"/>
       <c r="CH7" s="98"/>
       <c r="CI7" s="98"/>
       <c r="CJ7" s="98"/>
@@ -6283,83 +6283,83 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I32" s="119"/>
-      <c r="J32" s="120"/>
-      <c r="K32" s="120"/>
-      <c r="L32" s="120"/>
-      <c r="M32" s="120"/>
-      <c r="N32" s="120"/>
-      <c r="O32" s="120"/>
-      <c r="P32" s="120"/>
-      <c r="Q32" s="120"/>
-      <c r="R32" s="120"/>
-      <c r="S32" s="120"/>
-      <c r="T32" s="120"/>
-      <c r="U32" s="120"/>
-      <c r="V32" s="120"/>
-      <c r="W32" s="120"/>
-      <c r="X32" s="120"/>
-      <c r="Y32" s="120"/>
-      <c r="Z32" s="120"/>
-      <c r="AA32" s="120"/>
-      <c r="AB32" s="120"/>
-      <c r="AC32" s="120"/>
-      <c r="AD32" s="120"/>
-      <c r="AE32" s="120"/>
-      <c r="AF32" s="120"/>
-      <c r="AG32" s="120"/>
-      <c r="AH32" s="120"/>
-      <c r="AI32" s="120"/>
-      <c r="AJ32" s="120"/>
-      <c r="AK32" s="120"/>
-      <c r="AL32" s="120"/>
-      <c r="AM32" s="120"/>
-      <c r="AN32" s="120"/>
-      <c r="AO32" s="120"/>
-      <c r="AP32" s="120"/>
-      <c r="AQ32" s="120"/>
-      <c r="AR32" s="120"/>
-      <c r="AS32" s="120"/>
-      <c r="AT32" s="120"/>
-      <c r="AU32" s="120"/>
-      <c r="AV32" s="120"/>
-      <c r="AW32" s="120"/>
-      <c r="AX32" s="120"/>
-      <c r="AY32" s="120"/>
-      <c r="AZ32" s="120"/>
-      <c r="BA32" s="120"/>
-      <c r="BB32" s="120"/>
-      <c r="BC32" s="120"/>
-      <c r="BD32" s="120"/>
-      <c r="BE32" s="120"/>
-      <c r="BF32" s="120"/>
-      <c r="BG32" s="120"/>
-      <c r="BH32" s="120"/>
-      <c r="BI32" s="120"/>
-      <c r="BJ32" s="120"/>
-      <c r="BK32" s="120"/>
-      <c r="BL32" s="120"/>
-      <c r="BM32" s="120"/>
-      <c r="BN32" s="120"/>
-      <c r="BO32" s="120"/>
-      <c r="BP32" s="120"/>
-      <c r="BQ32" s="120"/>
-      <c r="BR32" s="120"/>
-      <c r="BS32" s="120"/>
-      <c r="BT32" s="120"/>
-      <c r="BU32" s="120"/>
-      <c r="BV32" s="120"/>
-      <c r="BW32" s="120"/>
-      <c r="BX32" s="120"/>
-      <c r="BY32" s="120"/>
-      <c r="BZ32" s="120"/>
-      <c r="CA32" s="120"/>
-      <c r="CB32" s="120"/>
-      <c r="CC32" s="120"/>
-      <c r="CD32" s="120"/>
-      <c r="CE32" s="120"/>
-      <c r="CF32" s="120"/>
-      <c r="CG32" s="121"/>
+      <c r="I32" s="128"/>
+      <c r="J32" s="129"/>
+      <c r="K32" s="129"/>
+      <c r="L32" s="129"/>
+      <c r="M32" s="129"/>
+      <c r="N32" s="129"/>
+      <c r="O32" s="129"/>
+      <c r="P32" s="129"/>
+      <c r="Q32" s="129"/>
+      <c r="R32" s="129"/>
+      <c r="S32" s="129"/>
+      <c r="T32" s="129"/>
+      <c r="U32" s="129"/>
+      <c r="V32" s="129"/>
+      <c r="W32" s="129"/>
+      <c r="X32" s="129"/>
+      <c r="Y32" s="129"/>
+      <c r="Z32" s="129"/>
+      <c r="AA32" s="129"/>
+      <c r="AB32" s="129"/>
+      <c r="AC32" s="129"/>
+      <c r="AD32" s="129"/>
+      <c r="AE32" s="129"/>
+      <c r="AF32" s="129"/>
+      <c r="AG32" s="129"/>
+      <c r="AH32" s="129"/>
+      <c r="AI32" s="129"/>
+      <c r="AJ32" s="129"/>
+      <c r="AK32" s="129"/>
+      <c r="AL32" s="129"/>
+      <c r="AM32" s="129"/>
+      <c r="AN32" s="129"/>
+      <c r="AO32" s="129"/>
+      <c r="AP32" s="129"/>
+      <c r="AQ32" s="129"/>
+      <c r="AR32" s="129"/>
+      <c r="AS32" s="129"/>
+      <c r="AT32" s="129"/>
+      <c r="AU32" s="129"/>
+      <c r="AV32" s="129"/>
+      <c r="AW32" s="129"/>
+      <c r="AX32" s="129"/>
+      <c r="AY32" s="129"/>
+      <c r="AZ32" s="129"/>
+      <c r="BA32" s="129"/>
+      <c r="BB32" s="129"/>
+      <c r="BC32" s="129"/>
+      <c r="BD32" s="129"/>
+      <c r="BE32" s="129"/>
+      <c r="BF32" s="129"/>
+      <c r="BG32" s="129"/>
+      <c r="BH32" s="129"/>
+      <c r="BI32" s="129"/>
+      <c r="BJ32" s="129"/>
+      <c r="BK32" s="129"/>
+      <c r="BL32" s="129"/>
+      <c r="BM32" s="129"/>
+      <c r="BN32" s="129"/>
+      <c r="BO32" s="129"/>
+      <c r="BP32" s="129"/>
+      <c r="BQ32" s="129"/>
+      <c r="BR32" s="129"/>
+      <c r="BS32" s="129"/>
+      <c r="BT32" s="129"/>
+      <c r="BU32" s="129"/>
+      <c r="BV32" s="129"/>
+      <c r="BW32" s="129"/>
+      <c r="BX32" s="129"/>
+      <c r="BY32" s="129"/>
+      <c r="BZ32" s="129"/>
+      <c r="CA32" s="129"/>
+      <c r="CB32" s="129"/>
+      <c r="CC32" s="129"/>
+      <c r="CD32" s="129"/>
+      <c r="CE32" s="129"/>
+      <c r="CF32" s="129"/>
+      <c r="CG32" s="130"/>
       <c r="CH32"/>
       <c r="CI32"/>
       <c r="CJ32"/>
@@ -9282,83 +9282,83 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="I55" s="122"/>
-      <c r="J55" s="123"/>
-      <c r="K55" s="123"/>
-      <c r="L55" s="123"/>
-      <c r="M55" s="123"/>
-      <c r="N55" s="123"/>
-      <c r="O55" s="123"/>
-      <c r="P55" s="123"/>
-      <c r="Q55" s="123"/>
-      <c r="R55" s="123"/>
-      <c r="S55" s="123"/>
-      <c r="T55" s="123"/>
-      <c r="U55" s="123"/>
-      <c r="V55" s="123"/>
-      <c r="W55" s="123"/>
-      <c r="X55" s="123"/>
-      <c r="Y55" s="123"/>
-      <c r="Z55" s="123"/>
-      <c r="AA55" s="123"/>
-      <c r="AB55" s="123"/>
-      <c r="AC55" s="123"/>
-      <c r="AD55" s="123"/>
-      <c r="AE55" s="123"/>
-      <c r="AF55" s="123"/>
-      <c r="AG55" s="123"/>
-      <c r="AH55" s="123"/>
-      <c r="AI55" s="123"/>
-      <c r="AJ55" s="123"/>
-      <c r="AK55" s="123"/>
-      <c r="AL55" s="123"/>
-      <c r="AM55" s="123"/>
-      <c r="AN55" s="123"/>
-      <c r="AO55" s="123"/>
-      <c r="AP55" s="123"/>
-      <c r="AQ55" s="123"/>
-      <c r="AR55" s="123"/>
-      <c r="AS55" s="123"/>
-      <c r="AT55" s="123"/>
-      <c r="AU55" s="123"/>
-      <c r="AV55" s="123"/>
-      <c r="AW55" s="123"/>
-      <c r="AX55" s="123"/>
-      <c r="AY55" s="123"/>
-      <c r="AZ55" s="123"/>
-      <c r="BA55" s="123"/>
-      <c r="BB55" s="123"/>
-      <c r="BC55" s="123"/>
-      <c r="BD55" s="123"/>
-      <c r="BE55" s="123"/>
-      <c r="BF55" s="123"/>
-      <c r="BG55" s="123"/>
-      <c r="BH55" s="123"/>
-      <c r="BI55" s="123"/>
-      <c r="BJ55" s="123"/>
-      <c r="BK55" s="123"/>
-      <c r="BL55" s="123"/>
-      <c r="BM55" s="123"/>
-      <c r="BN55" s="123"/>
-      <c r="BO55" s="123"/>
-      <c r="BP55" s="123"/>
-      <c r="BQ55" s="123"/>
-      <c r="BR55" s="123"/>
-      <c r="BS55" s="123"/>
-      <c r="BT55" s="123"/>
-      <c r="BU55" s="123"/>
-      <c r="BV55" s="123"/>
-      <c r="BW55" s="123"/>
-      <c r="BX55" s="123"/>
-      <c r="BY55" s="123"/>
-      <c r="BZ55" s="123"/>
-      <c r="CA55" s="123"/>
-      <c r="CB55" s="123"/>
-      <c r="CC55" s="123"/>
-      <c r="CD55" s="123"/>
-      <c r="CE55" s="123"/>
-      <c r="CF55" s="123"/>
-      <c r="CG55" s="124"/>
+      <c r="I55" s="131"/>
+      <c r="J55" s="132"/>
+      <c r="K55" s="132"/>
+      <c r="L55" s="132"/>
+      <c r="M55" s="132"/>
+      <c r="N55" s="132"/>
+      <c r="O55" s="132"/>
+      <c r="P55" s="132"/>
+      <c r="Q55" s="132"/>
+      <c r="R55" s="132"/>
+      <c r="S55" s="132"/>
+      <c r="T55" s="132"/>
+      <c r="U55" s="132"/>
+      <c r="V55" s="132"/>
+      <c r="W55" s="132"/>
+      <c r="X55" s="132"/>
+      <c r="Y55" s="132"/>
+      <c r="Z55" s="132"/>
+      <c r="AA55" s="132"/>
+      <c r="AB55" s="132"/>
+      <c r="AC55" s="132"/>
+      <c r="AD55" s="132"/>
+      <c r="AE55" s="132"/>
+      <c r="AF55" s="132"/>
+      <c r="AG55" s="132"/>
+      <c r="AH55" s="132"/>
+      <c r="AI55" s="132"/>
+      <c r="AJ55" s="132"/>
+      <c r="AK55" s="132"/>
+      <c r="AL55" s="132"/>
+      <c r="AM55" s="132"/>
+      <c r="AN55" s="132"/>
+      <c r="AO55" s="132"/>
+      <c r="AP55" s="132"/>
+      <c r="AQ55" s="132"/>
+      <c r="AR55" s="132"/>
+      <c r="AS55" s="132"/>
+      <c r="AT55" s="132"/>
+      <c r="AU55" s="132"/>
+      <c r="AV55" s="132"/>
+      <c r="AW55" s="132"/>
+      <c r="AX55" s="132"/>
+      <c r="AY55" s="132"/>
+      <c r="AZ55" s="132"/>
+      <c r="BA55" s="132"/>
+      <c r="BB55" s="132"/>
+      <c r="BC55" s="132"/>
+      <c r="BD55" s="132"/>
+      <c r="BE55" s="132"/>
+      <c r="BF55" s="132"/>
+      <c r="BG55" s="132"/>
+      <c r="BH55" s="132"/>
+      <c r="BI55" s="132"/>
+      <c r="BJ55" s="132"/>
+      <c r="BK55" s="132"/>
+      <c r="BL55" s="132"/>
+      <c r="BM55" s="132"/>
+      <c r="BN55" s="132"/>
+      <c r="BO55" s="132"/>
+      <c r="BP55" s="132"/>
+      <c r="BQ55" s="132"/>
+      <c r="BR55" s="132"/>
+      <c r="BS55" s="132"/>
+      <c r="BT55" s="132"/>
+      <c r="BU55" s="132"/>
+      <c r="BV55" s="132"/>
+      <c r="BW55" s="132"/>
+      <c r="BX55" s="132"/>
+      <c r="BY55" s="132"/>
+      <c r="BZ55" s="132"/>
+      <c r="CA55" s="132"/>
+      <c r="CB55" s="132"/>
+      <c r="CC55" s="132"/>
+      <c r="CD55" s="132"/>
+      <c r="CE55" s="132"/>
+      <c r="CF55" s="132"/>
+      <c r="CG55" s="133"/>
       <c r="CH55"/>
       <c r="CI55"/>
       <c r="CJ55"/>
@@ -11142,13 +11142,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="C2:D2"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="P3:T3"/>
-    <mergeCell ref="U3:Y3"/>
-    <mergeCell ref="Z3:AD3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I3:O3"/>
     <mergeCell ref="I7:CG7"/>
     <mergeCell ref="I32:CG32"/>
     <mergeCell ref="I55:CG55"/>
@@ -11163,6 +11156,13 @@
     <mergeCell ref="AO3:AS3"/>
     <mergeCell ref="AT3:AX3"/>
     <mergeCell ref="AY3:BC3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="P3:T3"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="Z3:AD3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="I3:O3"/>
   </mergeCells>
   <conditionalFormatting sqref="D6:D69">
     <cfRule type="dataBar" priority="17">
@@ -11227,15 +11227,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="24" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2d714a3296df14eba7a100bb665443ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="49549bf45bfbbfb6cffed527380e77e1" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -11523,6 +11514,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -11544,14 +11544,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F80F839-78EF-4FF4-A673-3CC84279C232}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11572,6 +11564,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC3AD2E1-977A-4D4F-8EE8-D64B5FFADF75}">
   <ds:schemaRefs>
